--- a/data/Meridian_Vendor_Output.xlsx
+++ b/data/Meridian_Vendor_Output.xlsx
@@ -1039,7 +1039,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] No</t>
+          <t>[MOCK] Inconclusive</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] N/A — no public evidence of AI usage in the service provided to Meridian.</t>
+          <t>[MOCK] Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] None identified</t>
+          <t>[MOCK] Medium</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>No public evidence of AI usage. 6 coverage gap(s) recorded. Rating subject to the caveat that absence of evidence is not evidence of absence.</t>
+          <t>Vendor has Low criticality tier. Insufficient coverage (1 pages checked, 6 gaps) to confirm absence of AI. Provisional rating applied.</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>Monitor annually. No immediate action required based on current public evidence.</t>
+          <t>Issue an AI usage questionnaire to clarify whether AI is used in the service provided to Meridian. Include questions on model providers, data handling, and oversight. Flag for follow-up review in next assessment cycle.</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>No public evidence of AI usage. 14 coverage gap(s) recorded. Rating subject to the caveat that absence of evidence is not evidence of absence.</t>
+          <t>No public evidence of AI usage across adequate coverage (3 pages checked). Rating subject to the caveat that absence of evidence is not evidence of absence.</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>No public evidence of AI usage. 10 coverage gap(s) recorded. Rating subject to the caveat that absence of evidence is not evidence of absence.</t>
+          <t>No public evidence of AI usage across adequate coverage (3 pages checked). Rating subject to the caveat that absence of evidence is not evidence of absence.</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] No</t>
+          <t>[MOCK] Inconclusive</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] N/A — no public evidence of AI usage in the service provided to Meridian.</t>
+          <t>[MOCK] Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] None identified</t>
+          <t>[MOCK] Medium</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>No public evidence of AI usage. 8 coverage gap(s) recorded. Rating subject to the caveat that absence of evidence is not evidence of absence.</t>
+          <t>Vendor has Medium criticality tier. Insufficient coverage (0 pages checked, 8 gaps) to confirm absence of AI. Provisional rating applied.</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>Monitor annually. No immediate action required based on current public evidence.</t>
+          <t>Issue an AI usage questionnaire to clarify whether AI is used in the service provided to Meridian. Include questions on model providers, data handling, and oversight. Flag for follow-up review in next assessment cycle.</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>No public evidence of AI usage. 0 coverage gap(s) recorded. Rating subject to the caveat that absence of evidence is not evidence of absence.</t>
+          <t>No public evidence of AI usage across adequate coverage (17 pages checked). Rating subject to the caveat that absence of evidence is not evidence of absence.</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">

--- a/data/Meridian_Vendor_Output.xlsx
+++ b/data/Meridian_Vendor_Output.xlsx
@@ -1039,19 +1039,19 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Inconclusive</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
           <t>No indicative AI evidence found.
-Sources successfully checked (1): https://www.automworx.com
+Sources successfully checked (3): https://www.automworx.com, https://www.automworx.com/privacy-policy, https://www.automworx.com/webinar-using-the-automic-rest-api-to-integrate-with-servicenow
 Coverage gaps (6): https://www.automworx.com/ai-policy, https://www.automworx.com/docs, https://www.automworx.com/dpa, https://www.automworx.com/security, https://www.automworx.com/subprocessors</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
+          <t>N/A — no public evidence of AI usage in the service provided to Meridian.</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Medium</t>
+          <t>None identified</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>Vendor has Low criticality tier. Insufficient coverage (1 pages checked, 6 gaps) to confirm absence of AI. Provisional rating applied.</t>
+          <t>No public evidence of AI usage across adequate coverage (3 pages checked). Rating subject to the caveat that absence of evidence is not evidence of absence.</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>Issue an AI usage questionnaire to clarify whether AI is used in the service provided to Meridian. Include questions on model providers, data handling, and oversight. Flag for follow-up review in next assessment cycle.</t>
+          <t>Monitor annually. No immediate action required based on current public evidence.</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
@@ -1148,39 +1148,51 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] No</t>
+          <t>Inconclusive</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>No indicative AI evidence found.
-Sources successfully checked (3): https://www.fiserv.com, https://www.fiserv.com/, https://www.fiserv.com/careers
-Coverage gaps (14): https://www.fiserv.com/about, https://www.fiserv.com/ai-policy, https://www.fiserv.com/api, https://www.fiserv.com/blog, https://www.fiserv.com/developers</t>
+          <t>"|  | Advanced detection techniques Leverage AI-driven risk scoring to analyze transaction patterns and customer behavior in real time."
+Source: https://www.fiserv.com/en/solutions/risk-compliance/aml-risk-manager.html (retrieved 2026-10-10)
+"Our approach includes:
+- Ongoing investment in cybersecurity and technology modernization
+- Continuous monitoring and proactive risk management
+- Security-focused software development and deployment practices
+- Collaboration with industry partners and security initiatives
+- Resilience testing and operational preparedness
+- Continuous enhancement of defensive capabilities to address emerging AI-enabled threats
+As the threat landscape continues to evolve, Fiserv remains committed to helping clients operate securely through defined cybersecurity practices, reliable technology platforms, and ongoing innovation."
+Source: https://www.fiserv.com/en/legal/cybersecurity.html (retrieved 2026-10-10)
+"Cybersecurity Best Practices in a Rapidly Evolving Threat Environment
+Security and Resilience in the Age of AI
+The cybersecurity landscape is evolving rapidly as bad actors increasingly use artificial intelligence to identify, automate, and exploit technology vulnerabilities at greater speed and scale."
+Source: https://www.fiserv.com/en/legal/cybersecurity.html (retrieved 2026-10-10)</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] N/A — no public evidence of AI usage in the service provided to Meridian.</t>
+          <t>Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>None named — Inconclusive. No sub-processor register or AI policy found publicly.</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] None identified</t>
+          <t>High</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>No public evidence of AI usage across adequate coverage (3 pages checked). Rating subject to the caveat that absence of evidence is not evidence of absence.</t>
+          <t>Vendor has Critical criticality tier. Weak AI signals detected (score: 8.4) but insufficient to confirm service-specific usage. Provisional rating based on criticality and data class ("Full customer master, balances and transactions for 1.4 million customers.").</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>Monitor annually. No immediate action required based on current public evidence.</t>
+          <t>Issue an AI usage questionnaire to clarify whether AI is used in the service provided to Meridian. Include questions on model providers, data handling, and oversight. Flag for follow-up review in next assessment cycle.</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
@@ -1257,19 +1269,19 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] No</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
           <t>No indicative AI evidence found.
-Sources successfully checked (3): https://www.fssi-ca.com, https://www.fssi-ca.com/blog, https://www.fssi-ca.com/jobs
-Coverage gaps (10): https://www.fssi-ca.com/ai-policy, https://www.fssi-ca.com/api, https://www.fssi-ca.com/careers, https://www.fssi-ca.com/developers, https://www.fssi-ca.com/docs</t>
+Sources successfully checked (13): https://www.fssi-ca.com, https://www.fssi-ca.com/capabilities/regulatory-compliance, https://www.fssi-ca.com/cybersecurity-awareness-month-2021-data-security-tips, https://www.fssi-ca.com/improving-the-data-security-and-privacy-of-your-organization, https://www.fssi-ca.com/infrastructure/hipaa-compliance, https://www.fssi-ca.com/optimizing-transactional-document-delivery-for-the-alarm-and-security-industry, https://www.fssi-ca.com/print-and-mail-compliance-guide-for-secure-document-processing, https://www.fssi-ca.com/privacy
+Coverage gaps (11): https://www.fssi-ca.com/ai-policy, https://www.fssi-ca.com/docs, https://www.fssi-ca.com/dpa, https://www.fssi-ca.com/security, https://www.fssi-ca.com/subprocessors</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] N/A — no public evidence of AI usage in the service provided to Meridian.</t>
+          <t>N/A — no public evidence of AI usage in the service provided to Meridian.</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
@@ -1279,12 +1291,12 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] None identified</t>
+          <t>None identified</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>No public evidence of AI usage across adequate coverage (3 pages checked). Rating subject to the caveat that absence of evidence is not evidence of absence.</t>
+          <t>No public evidence of AI usage across adequate coverage (13 pages checked). Rating subject to the caveat that absence of evidence is not evidence of absence.</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -1366,34 +1378,34 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Inconclusive</t>
+          <t>Inconclusive</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
           <t>No indicative AI evidence found.
 Sources successfully checked (0): 
-Coverage gaps (8): https://www.terrapintech.com, https://www.terrapintech.com/, https://www.terrapintech.com/api, https://www.terrapintech.com/blog, https://www.terrapintech.com/careers</t>
+Coverage gaps (7): https://www.terrapintech.com, https://www.terrapintech.com/api, https://www.terrapintech.com/blog, https://www.terrapintech.com/careers, https://www.terrapintech.com/developers</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
+          <t>Insufficient coverage; no determination possible.</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>None named — Inconclusive. No sub-processor register or AI policy found publicly.</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>Vendor has Medium criticality tier. Insufficient coverage (0 pages checked, 8 gaps) to confirm absence of AI. Provisional rating applied.</t>
+          <t>Vendor has Medium criticality tier. Insufficient coverage (0 pages checked, 7 gaps) to confirm absence of AI. Provisional rating applied.</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -1475,7 +1487,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Inconclusive</t>
+          <t>Inconclusive</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1485,30 +1497,27 @@
   - “Artificial Intelligence” means any technology that enables machines to perform tasks that typically require human intelligence, including but not limited to generative AI, machine learning, natural language processing, and computer vision."
 Source: https://www.bny.com/ai-policy (retrieved 2026-10-10)
 "This Acceptable Use Policy (“Policy”) applies to Your use of all services offered by BNY or third-party products, applications, or functionality that interoperate with services offered by BNY, that incorporate Artificial Intelligence, including proprietary and third-party solutions (each, an “AI Service”)."
-Source: https://www.bny.com/ai-policy (retrieved 2026-10-10)
-"DATA &amp; ANALYTICS
-Cloud-native and AI enabled platform for data and operations."
-Source: https://www.bny.com (retrieved 2026-10-10)</t>
+Source: https://www.bny.com/ai-policy (retrieved 2026-10-10)</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
+          <t>Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>None named — Inconclusive. No sub-processor register or AI policy found publicly.</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>Vendor has High criticality tier. Weak AI signals detected (score: 3.5) but insufficient to confirm service-specific usage. Provisional rating based on criticality and data class ("Payment instructions, counterparty names and account identifiers.").</t>
+          <t>Vendor has High criticality tier. Weak AI signals detected (score: 3.3) but insufficient to confirm service-specific usage. Provisional rating based on criticality and data class ("Payment instructions, counterparty names and account identifiers.").</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -1590,18 +1599,19 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] No</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
           <t>No indicative AI evidence found.
-Sources successfully checked (17): https://www.theclearinghouse.org, https://www.theclearinghouse.org/, https://www.theclearinghouse.org/about, https://www.theclearinghouse.org/ai-policy, https://www.theclearinghouse.org/api, https://www.theclearinghouse.org/blog, https://www.theclearinghouse.org/careers, https://www.theclearinghouse.org/developers</t>
+Sources successfully checked (18): https://www.theclearinghouse.org, https://www.theclearinghouse.org/forms-old/rtp-compliance-implications, https://www.theclearinghouse.org/forms-old/rtp-network-rules-compliance-enforcement, https://www.theclearinghouse.org/payment-systems/articles/2018/08/data-privacy-08-21-2018, https://www.theclearinghouse.org/payment-systems/articles/2018/10/data-privacy-10-18-2018, https://www.theclearinghouse.org/payment-systems/articles/2019/07/071119-heritage-trust, https://www.theclearinghouse.org/payment-systems/articles/2024/07/cfpb-compliance-deadline, https://www.theclearinghouse.org/payment-systems/rtp/technical-documentation
+Coverage gaps (18): https://www.theclearinghouse.org/ai-policy, https://www.theclearinghouse.org/docs, https://www.theclearinghouse.org/dpa, https://www.theclearinghouse.org/payments-services/education/ach/compliance-risk-management, https://www.theclearinghouse.org/payments-services/education/corporate/compliance-risk-management</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] N/A — no public evidence of AI usage in the service provided to Meridian.</t>
+          <t>N/A — no public evidence of AI usage in the service provided to Meridian.</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
@@ -1611,12 +1621,12 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] None identified</t>
+          <t>None identified</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>No public evidence of AI usage across adequate coverage (17 pages checked). Rating subject to the caveat that absence of evidence is not evidence of absence.</t>
+          <t>No public evidence of AI usage across adequate coverage (18 pages checked). Rating subject to the caveat that absence of evidence is not evidence of absence.</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -2149,7 +2159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2197,129 +2207,221 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/solutions/risk-compliance/aml-risk-manager.html</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tier_A</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/solutions/risk-compliance/aml-risk-manager.html</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-10-10T06:17:40.484938+00:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>|  | Advanced detection techniques Leverage AI-driven risk scoring to analyze transaction patterns and customer behavior in real time.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>bbf9f86093b9ffb25ab6aed003eaf13162c0712252e6bdfdd50cf8312e0dbda0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Tier_A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-10T06:17:27.063871+00:00</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Our approach includes:
+- Ongoing investment in cybersecurity and technology modernization
+- Continuous monitoring and proactive risk management
+- Security-focused software development and deployment practices
+- Collaboration with industry partners and security initiatives
+- Resilience testing and operational preparedness
+- Continuous enhancement of defensive capabilities to address emerging AI-enabled threats
+As the threat landscape continues to evolve, Fiserv remains committed to helping clients operate securely through defined cybersecurity practices, reliable technology platforms, and ongoing innovation.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c8ae42b7ee474576c84822b5f8d2a9e306f7e26ed7e7a10c1198ff5990595d35</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tier_A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-10T06:17:27.063871+00:00</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Cybersecurity Best Practices in a Rapidly Evolving Threat Environment
+Security and Resilience in the Age of AI
+The cybersecurity landscape is evolving rapidly as bad actors increasingly use artificial intelligence to identify, automate, and exploit technology vulnerabilities at greater speed and scale.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>c8ae42b7ee474576c84822b5f8d2a9e306f7e26ed7e7a10c1198ff5990595d35</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>V-005</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>https://www.bny.com/ai-policy</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Tier_A</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://www.bny.com/ai-policy</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-10-10T04:42:56.353288+00:00</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-10-10T06:19:45.726343+00:00</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>- Definitions
  For the purposes of this Policy:
   - “Artificial Intelligence” means any technology that enables machines to perform tasks that typically require human intelligence, including but not limited to generative AI, machine learning, natural language processing, and computer vision.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>INDICATIVE</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>b31b1f0ef72c6f75f441627dd1e3e12b5305831bc8980275fa4a514304f1d512</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>V-005</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://www.bny.com/ai-policy</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Tier_A</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://www.bny.com/ai-policy</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-10-10T04:42:56.353288+00:00</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-10-10T06:19:45.726343+00:00</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>This Acceptable Use Policy (“Policy”) applies to Your use of all services offered by BNY or third-party products, applications, or functionality that interoperate with services offered by BNY, that incorporate Artificial Intelligence, including proprietary and third-party solutions (each, an “AI Service”).</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>MARKETING-ONLY</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>b31b1f0ef72c6f75f441627dd1e3e12b5305831bc8980275fa4a514304f1d512</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>V-005</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://www.bny.com</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Tier_D</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://www.bny.com</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-10-10T04:42:54.169759+00:00</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>DATA &amp; ANALYTICS
-Cloud-native and AI enabled platform for data and operations.</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MARKETING-ONLY</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>848ffca667031a7927323e7f82ea67d2e2d1800c19824f5d5032e57536d4de82</t>
         </is>
       </c>
     </row>

--- a/data/Meridian_Vendor_Output.xlsx
+++ b/data/Meridian_Vendor_Output.xlsx
@@ -1039,7 +1039,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>[MOCK] No</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>N/A — no public evidence of AI usage in the service provided to Meridian.</t>
+          <t>[MOCK] N/A — no public evidence of AI usage in the service provided to Meridian.</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>None identified</t>
+          <t>[MOCK] None identified</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>Inconclusive</t>
+          <t>[MOCK] Inconclusive</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
+          <t>[MOCK] Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>[MOCK] High</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>[MOCK] No</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>N/A — no public evidence of AI usage in the service provided to Meridian.</t>
+          <t>[MOCK] N/A — no public evidence of AI usage in the service provided to Meridian.</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>None identified</t>
+          <t>[MOCK] None identified</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>Inconclusive</t>
+          <t>[MOCK] Inconclusive</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>Insufficient coverage; no determination possible.</t>
+          <t>[MOCK] Insufficient coverage; no determination possible.</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>[MOCK] Medium</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>Inconclusive</t>
+          <t>[MOCK] Inconclusive</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
+          <t>[MOCK] Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>[MOCK] High</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>[MOCK] No</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>N/A — no public evidence of AI usage in the service provided to Meridian.</t>
+          <t>[MOCK] N/A — no public evidence of AI usage in the service provided to Meridian.</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>None identified</t>
+          <t>[MOCK] None identified</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">

--- a/data/Meridian_Vendor_Output.xlsx
+++ b/data/Meridian_Vendor_Output.xlsx
@@ -1039,7 +1039,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] No</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] N/A — no public evidence of AI usage in the service provided to Meridian.</t>
+          <t>N/A — no public evidence of AI usage in the service provided to Meridian.</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] None identified</t>
+          <t>None identified</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1148,31 +1148,20 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Inconclusive</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>"|  | Advanced detection techniques Leverage AI-driven risk scoring to analyze transaction patterns and customer behavior in real time."
+          <t>"Leverage AI-driven risk scoring to analyze transaction patterns and customer behavior in real time."
 Source: https://www.fiserv.com/en/solutions/risk-compliance/aml-risk-manager.html (retrieved 2026-10-10)
-"Our approach includes:
-- Ongoing investment in cybersecurity and technology modernization
-- Continuous monitoring and proactive risk management
-- Security-focused software development and deployment practices
-- Collaboration with industry partners and security initiatives
-- Resilience testing and operational preparedness
-- Continuous enhancement of defensive capabilities to address emerging AI-enabled threats
-As the threat landscape continues to evolve, Fiserv remains committed to helping clients operate securely through defined cybersecurity practices, reliable technology platforms, and ongoing innovation."
-Source: https://www.fiserv.com/en/legal/cybersecurity.html (retrieved 2026-10-10)
-"Cybersecurity Best Practices in a Rapidly Evolving Threat Environment
-Security and Resilience in the Age of AI
-The cybersecurity landscape is evolving rapidly as bad actors increasingly use artificial intelligence to identify, automate, and exploit technology vulnerabilities at greater speed and scale."
+"The cybersecurity landscape is evolving rapidly as bad actors increasingly use artificial intelligence to identify, automate, and exploit technology vulnerabilities at greater speed and scale."
 Source: https://www.fiserv.com/en/legal/cybersecurity.html (retrieved 2026-10-10)</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
+          <t>risk scoring; Identifying, automating, and exploiting technology vulnerabilities</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
@@ -1182,17 +1171,17 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>Vendor has Critical criticality tier. Weak AI signals detected (score: 8.4) but insufficient to confirm service-specific usage. Provisional rating based on criticality and data class ("Full customer master, balances and transactions for 1.4 million customers.").</t>
+          <t>Vendor has Critical criticality tier with confirmed AI footprint. Data accessed includes "Full customer master, balances and transactions for 1.4 million customers.". Weighted evidence score: 32.4 across 2 valid signal(s). No model provider is publicly identified, leaving data flows untraceable. Evidence strength: strong.</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>Issue an AI usage questionnaire to clarify whether AI is used in the service provided to Meridian. Include questions on model providers, data handling, and oversight. Flag for follow-up review in next assessment cycle.</t>
+          <t>Issue a targeted AI questionnaire within 15 business days covering: (1) model provider identity, hosting region, and data retention policy; (2) whether Meridian data (Full customer master, balances and transactions for 1.4 million customers.) is processed by AI models; (3) human review controls over AI-generated outputs. Register the vendor on the AI sub-processor inventory with an unresolved-provider flag. Raise AI-specific contract clauses at next review, addressing training restrictions, sub-processor change notification, and rights to audit. Escalate to Third-Party Risk Committee if confirmation not received within 30 days.</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
@@ -1269,7 +1258,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] No</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1281,7 +1270,7 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] N/A — no public evidence of AI usage in the service provided to Meridian.</t>
+          <t>N/A — no public evidence of AI usage in the service provided to Meridian.</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
@@ -1291,7 +1280,7 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] None identified</t>
+          <t>None identified</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
@@ -1378,7 +1367,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Inconclusive</t>
+          <t>Inconclusive</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1390,7 +1379,7 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Insufficient coverage; no determination possible.</t>
+          <t>Insufficient coverage; no determination possible.</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
@@ -1400,7 +1389,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -1487,22 +1476,18 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Inconclusive</t>
+          <t>Inconclusive</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>"- Definitions
- For the purposes of this Policy:
-  - “Artificial Intelligence” means any technology that enables machines to perform tasks that typically require human intelligence, including but not limited to generative AI, machine learning, natural language processing, and computer vision."
-Source: https://www.bny.com/ai-policy (retrieved 2026-10-10)
-"This Acceptable Use Policy (“Policy”) applies to Your use of all services offered by BNY or third-party products, applications, or functionality that interoperate with services offered by BNY, that incorporate Artificial Intelligence, including proprietary and third-party solutions (each, an “AI Service”)."
+          <t>"Use any robot, spider, intelligent agent, other automatic device or manual process, or automated systems to search, monitor or copy our web pages, data, content or other materials contained herein"
 Source: https://www.bny.com/ai-policy (retrieved 2026-10-10)</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
+          <t>Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
@@ -1512,12 +1497,12 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>Vendor has High criticality tier. Weak AI signals detected (score: 3.3) but insufficient to confirm service-specific usage. Provisional rating based on criticality and data class ("Payment instructions, counterparty names and account identifiers.").</t>
+          <t>Vendor has High criticality tier. Weak AI signals detected (score: 0.9) but insufficient to confirm service-specific usage. Provisional rating based on criticality and data class ("Payment instructions, counterparty names and account identifiers.").</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -1599,7 +1584,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] No</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -1611,7 +1596,7 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] N/A — no public evidence of AI usage in the service provided to Meridian.</t>
+          <t>N/A — no public evidence of AI usage in the service provided to Meridian.</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
@@ -1621,7 +1606,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] None identified</t>
+          <t>None identified</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -2159,7 +2144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2232,12 +2217,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>|  | Advanced detection techniques Leverage AI-driven risk scoring to analyze transaction patterns and customer behavior in real time.</t>
+          <t>Leverage AI-driven risk scoring to analyze transaction patterns and customer behavior in real time.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>INDICATIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2274,19 +2259,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Our approach includes:
-- Ongoing investment in cybersecurity and technology modernization
-- Continuous monitoring and proactive risk management
-- Security-focused software development and deployment practices
-- Collaboration with industry partners and security initiatives
-- Resilience testing and operational preparedness
-- Continuous enhancement of defensive capabilities to address emerging AI-enabled threats
-As the threat landscape continues to evolve, Fiserv remains committed to helping clients operate securely through defined cybersecurity practices, reliable technology platforms, and ongoing innovation.</t>
+          <t>The cybersecurity landscape is evolving rapidly as bad actors increasingly use artificial intelligence to identify, automate, and exploit technology vulnerabilities at greater speed and scale.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2298,12 +2276,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V-002</t>
+          <t>V-005</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
+          <t>https://www.bny.com/ai-policy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2313,19 +2291,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
+          <t>https://www.bny.com/ai-policy</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-10T06:17:27.063871+00:00</t>
+          <t>2026-10-10T06:19:45.726343+00:00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cybersecurity Best Practices in a Rapidly Evolving Threat Environment
-Security and Resilience in the Age of AI
-The cybersecurity landscape is evolving rapidly as bad actors increasingly use artificial intelligence to identify, automate, and exploit technology vulnerabilities at greater speed and scale.</t>
+          <t>Use any robot, spider, intelligent agent, other automatic device or manual process, or automated systems to search, monitor or copy our web pages, data, content or other materials contained herein</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2334,92 +2310,6 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
-        <is>
-          <t>c8ae42b7ee474576c84822b5f8d2a9e306f7e26ed7e7a10c1198ff5990595d35</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>V-005</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://www.bny.com/ai-policy</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Tier_A</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://www.bny.com/ai-policy</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-10-10T06:19:45.726343+00:00</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>- Definitions
- For the purposes of this Policy:
-  - “Artificial Intelligence” means any technology that enables machines to perform tasks that typically require human intelligence, including but not limited to generative AI, machine learning, natural language processing, and computer vision.</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>INDICATIVE</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>b31b1f0ef72c6f75f441627dd1e3e12b5305831bc8980275fa4a514304f1d512</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>V-005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://www.bny.com/ai-policy</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Tier_A</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://www.bny.com/ai-policy</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-10-10T06:19:45.726343+00:00</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>This Acceptable Use Policy (“Policy”) applies to Your use of all services offered by BNY or third-party products, applications, or functionality that interoperate with services offered by BNY, that incorporate Artificial Intelligence, including proprietary and third-party solutions (each, an “AI Service”).</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>MARKETING-ONLY</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
         <is>
           <t>b31b1f0ef72c6f75f441627dd1e3e12b5305831bc8980275fa4a514304f1d512</t>
         </is>

--- a/data/Meridian_Vendor_Output.xlsx
+++ b/data/Meridian_Vendor_Output.xlsx
@@ -1039,19 +1039,18 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>[MOCK] No</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
           <t>No indicative AI evidence found.
-Sources successfully checked (3): https://www.automworx.com, https://www.automworx.com/privacy-policy, https://www.automworx.com/webinar-using-the-automic-rest-api-to-integrate-with-servicenow
-Coverage gaps (6): https://www.automworx.com/ai-policy, https://www.automworx.com/docs, https://www.automworx.com/dpa, https://www.automworx.com/security, https://www.automworx.com/subprocessors</t>
+Sources successfully checked (3): https://www.automworx.com, https://www.automworx.com/privacy-policy, https://www.automworx.com/webinar-using-the-automic-rest-api-to-integrate-with-servicenow</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>N/A — no public evidence of AI usage in the service provided to Meridian.</t>
+          <t>[MOCK] N/A — no public evidence of AI usage in the service provided to Meridian.</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -1061,7 +1060,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>None identified</t>
+          <t>[MOCK] None identified</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
@@ -1148,20 +1147,31 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>[MOCK] Inconclusive</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>"Leverage AI-driven risk scoring to analyze transaction patterns and customer behavior in real time."
+          <t>"|  | Advanced detection techniques Leverage AI-driven risk scoring to analyze transaction patterns and customer behavior in real time."
 Source: https://www.fiserv.com/en/solutions/risk-compliance/aml-risk-manager.html (retrieved 2026-10-10)
-"The cybersecurity landscape is evolving rapidly as bad actors increasingly use artificial intelligence to identify, automate, and exploit technology vulnerabilities at greater speed and scale."
+"Our approach includes:
+- Ongoing investment in cybersecurity and technology modernization
+- Continuous monitoring and proactive risk management
+- Security-focused software development and deployment practices
+- Collaboration with industry partners and security initiatives
+- Resilience testing and operational preparedness
+- Continuous enhancement of defensive capabilities to address emerging AI-enabled threats
+As the threat landscape continues to evolve, Fiserv remains committed to helping clients operate securely through defined cybersecurity practices, reliable technology platforms, and ongoing innovation."
+Source: https://www.fiserv.com/en/legal/cybersecurity.html (retrieved 2026-10-10)
+"Cybersecurity Best Practices in a Rapidly Evolving Threat Environment
+Security and Resilience in the Age of AI
+The cybersecurity landscape is evolving rapidly as bad actors increasingly use artificial intelligence to identify, automate, and exploit technology vulnerabilities at greater speed and scale."
 Source: https://www.fiserv.com/en/legal/cybersecurity.html (retrieved 2026-10-10)</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>risk scoring; Identifying, automating, and exploiting technology vulnerabilities</t>
+          <t>[MOCK] Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
@@ -1171,17 +1181,17 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>[MOCK] High</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>Vendor has Critical criticality tier with confirmed AI footprint. Data accessed includes "Full customer master, balances and transactions for 1.4 million customers.". Weighted evidence score: 32.4 across 2 valid signal(s). No model provider is publicly identified, leaving data flows untraceable. Evidence strength: strong.</t>
+          <t>Vendor has Critical criticality tier. Weak AI signals detected (score: 8.4) but insufficient to confirm service-specific usage. Provisional rating based on criticality and data class ("Full customer master, balances and transactions for 1.4 million customers.").</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>Issue a targeted AI questionnaire within 15 business days covering: (1) model provider identity, hosting region, and data retention policy; (2) whether Meridian data (Full customer master, balances and transactions for 1.4 million customers.) is processed by AI models; (3) human review controls over AI-generated outputs. Register the vendor on the AI sub-processor inventory with an unresolved-provider flag. Raise AI-specific contract clauses at next review, addressing training restrictions, sub-processor change notification, and rights to audit. Escalate to Third-Party Risk Committee if confirmation not received within 30 days.</t>
+          <t>Issue an AI usage questionnaire to clarify whether AI is used in the service provided to Meridian. Include questions on model providers, data handling, and oversight. Flag for follow-up review in next assessment cycle.</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
@@ -1258,19 +1268,19 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>[MOCK] No</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
           <t>No indicative AI evidence found.
 Sources successfully checked (13): https://www.fssi-ca.com, https://www.fssi-ca.com/capabilities/regulatory-compliance, https://www.fssi-ca.com/cybersecurity-awareness-month-2021-data-security-tips, https://www.fssi-ca.com/improving-the-data-security-and-privacy-of-your-organization, https://www.fssi-ca.com/infrastructure/hipaa-compliance, https://www.fssi-ca.com/optimizing-transactional-document-delivery-for-the-alarm-and-security-industry, https://www.fssi-ca.com/print-and-mail-compliance-guide-for-secure-document-processing, https://www.fssi-ca.com/privacy
-Coverage gaps (11): https://www.fssi-ca.com/ai-policy, https://www.fssi-ca.com/docs, https://www.fssi-ca.com/dpa, https://www.fssi-ca.com/security, https://www.fssi-ca.com/subprocessors</t>
+Coverage gaps (1): https://www.fssi-ca.com/jobs</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>N/A — no public evidence of AI usage in the service provided to Meridian.</t>
+          <t>[MOCK] N/A — no public evidence of AI usage in the service provided to Meridian.</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
@@ -1280,7 +1290,7 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>None identified</t>
+          <t>[MOCK] None identified</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
@@ -1367,19 +1377,18 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>Inconclusive</t>
+          <t>[MOCK] Inconclusive</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>No indicative AI evidence found.
-Sources successfully checked (0): 
-Coverage gaps (7): https://www.terrapintech.com, https://www.terrapintech.com/api, https://www.terrapintech.com/blog, https://www.terrapintech.com/careers, https://www.terrapintech.com/developers</t>
+          <t xml:space="preserve">No indicative AI evidence found.
+Sources successfully checked (0): </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>Insufficient coverage; no determination possible.</t>
+          <t>[MOCK] Insufficient coverage; no determination possible.</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
@@ -1389,12 +1398,12 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>[MOCK] Medium</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>Vendor has Medium criticality tier. Insufficient coverage (0 pages checked, 7 gaps) to confirm absence of AI. Provisional rating applied.</t>
+          <t>Vendor has Medium criticality tier. Insufficient coverage (0 pages checked, 0 gaps) to confirm absence of AI. Provisional rating applied.</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -1476,18 +1485,22 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>Inconclusive</t>
+          <t>[MOCK] Inconclusive</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>"Use any robot, spider, intelligent agent, other automatic device or manual process, or automated systems to search, monitor or copy our web pages, data, content or other materials contained herein"
+          <t>"- Definitions
+ For the purposes of this Policy:
+  - “Artificial Intelligence” means any technology that enables machines to perform tasks that typically require human intelligence, including but not limited to generative AI, machine learning, natural language processing, and computer vision."
+Source: https://www.bny.com/ai-policy (retrieved 2026-10-10)
+"This Acceptable Use Policy (“Policy”) applies to Your use of all services offered by BNY or third-party products, applications, or functionality that interoperate with services offered by BNY, that incorporate Artificial Intelligence, including proprietary and third-party solutions (each, an “AI Service”)."
 Source: https://www.bny.com/ai-policy (retrieved 2026-10-10)</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
+          <t>[MOCK] Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
@@ -1497,12 +1510,12 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>[MOCK] High</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>Vendor has High criticality tier. Weak AI signals detected (score: 0.9) but insufficient to confirm service-specific usage. Provisional rating based on criticality and data class ("Payment instructions, counterparty names and account identifiers.").</t>
+          <t>Vendor has High criticality tier. Weak AI signals detected (score: 3.3) but insufficient to confirm service-specific usage. Provisional rating based on criticality and data class ("Payment instructions, counterparty names and account identifiers.").</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -1584,7 +1597,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>[MOCK] No</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
@@ -1596,7 +1609,7 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>N/A — no public evidence of AI usage in the service provided to Meridian.</t>
+          <t>[MOCK] N/A — no public evidence of AI usage in the service provided to Meridian.</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
@@ -1606,7 +1619,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>None identified</t>
+          <t>[MOCK] None identified</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -2144,7 +2157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2217,12 +2230,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Leverage AI-driven risk scoring to analyze transaction patterns and customer behavior in real time.</t>
+          <t>|  | Advanced detection techniques Leverage AI-driven risk scoring to analyze transaction patterns and customer behavior in real time.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2259,12 +2272,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>The cybersecurity landscape is evolving rapidly as bad actors increasingly use artificial intelligence to identify, automate, and exploit technology vulnerabilities at greater speed and scale.</t>
+          <t>Our approach includes:
+- Ongoing investment in cybersecurity and technology modernization
+- Continuous monitoring and proactive risk management
+- Security-focused software development and deployment practices
+- Collaboration with industry partners and security initiatives
+- Resilience testing and operational preparedness
+- Continuous enhancement of defensive capabilities to address emerging AI-enabled threats
+As the threat landscape continues to evolve, Fiserv remains committed to helping clients operate securely through defined cybersecurity practices, reliable technology platforms, and ongoing innovation.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>INDICATIVE</t>
+          <t>MARKETING-ONLY</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2276,40 +2296,128 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tier_A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-10T06:17:27.063871+00:00</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Cybersecurity Best Practices in a Rapidly Evolving Threat Environment
+Security and Resilience in the Age of AI
+The cybersecurity landscape is evolving rapidly as bad actors increasingly use artificial intelligence to identify, automate, and exploit technology vulnerabilities at greater speed and scale.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>c8ae42b7ee474576c84822b5f8d2a9e306f7e26ed7e7a10c1198ff5990595d35</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>V-005</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>https://www.bny.com/ai-policy</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Tier_A</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://www.bny.com/ai-policy</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>2026-10-10T06:19:45.726343+00:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Use any robot, spider, intelligent agent, other automatic device or manual process, or automated systems to search, monitor or copy our web pages, data, content or other materials contained herein</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>- Definitions
+ For the purposes of this Policy:
+  - “Artificial Intelligence” means any technology that enables machines to perform tasks that typically require human intelligence, including but not limited to generative AI, machine learning, natural language processing, and computer vision.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>b31b1f0ef72c6f75f441627dd1e3e12b5305831bc8980275fa4a514304f1d512</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>V-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.bny.com/ai-policy</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Tier_A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.bny.com/ai-policy</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-10-10T06:19:45.726343+00:00</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>This Acceptable Use Policy (“Policy”) applies to Your use of all services offered by BNY or third-party products, applications, or functionality that interoperate with services offered by BNY, that incorporate Artificial Intelligence, including proprietary and third-party solutions (each, an “AI Service”).</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>MARKETING-ONLY</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>b31b1f0ef72c6f75f441627dd1e3e12b5305831bc8980275fa4a514304f1d512</t>
         </is>

--- a/data/Meridian_Vendor_Output.xlsx
+++ b/data/Meridian_Vendor_Output.xlsx
@@ -1039,38 +1039,38 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] No</t>
+          <t>[MOCK] Inconclusive</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>No indicative AI evidence found.
-Sources successfully checked (3): https://www.automworx.com, https://www.automworx.com/privacy-policy, https://www.automworx.com/webinar-using-the-automic-rest-api-to-integrate-with-servicenow</t>
+          <t>"Experience the power of … Use ChatGPT to answer questions, write, create images, complete work, and code—all in one place."
+Source: https://www.automworx.com/ai-policy (retrieved 2026-10-10)</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] N/A — no public evidence of AI usage in the service provided to Meridian.</t>
+          <t>[MOCK] Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>None named — Inconclusive. No sub-processor register or AI policy found publicly.</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] None identified</t>
+          <t>[MOCK] Medium</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>No public evidence of AI usage across adequate coverage (3 pages checked). Rating subject to the caveat that absence of evidence is not evidence of absence.</t>
+          <t>Vendor has Low criticality tier. Weak AI signals detected (score: 0.3) but insufficient to confirm service-specific usage. Provisional rating based on criticality and data class ("No direct customer data. Privileged access to production job schedules, system configuration and service credentials.").</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>Monitor annually. No immediate action required based on current public evidence.</t>
+          <t>Issue an AI usage questionnaire to clarify whether AI is used in the service provided to Meridian. Include questions on model providers, data handling, and oversight. Flag for follow-up review in next assessment cycle.</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
@@ -1147,51 +1147,51 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Inconclusive</t>
+          <t>[MOCK] Yes</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>"|  | Advanced detection techniques Leverage AI-driven risk scoring to analyze transaction patterns and customer behavior in real time."
-Source: https://www.fiserv.com/en/solutions/risk-compliance/aml-risk-manager.html (retrieved 2026-10-10)
-"Our approach includes:
-- Ongoing investment in cybersecurity and technology modernization
-- Continuous monitoring and proactive risk management
-- Security-focused software development and deployment practices
-- Collaboration with industry partners and security initiatives
-- Resilience testing and operational preparedness
-- Continuous enhancement of defensive capabilities to address emerging AI-enabled threats
-As the threat landscape continues to evolve, Fiserv remains committed to helping clients operate securely through defined cybersecurity practices, reliable technology platforms, and ongoing innovation."
-Source: https://www.fiserv.com/en/legal/cybersecurity.html (retrieved 2026-10-10)
-"Cybersecurity Best Practices in a Rapidly Evolving Threat Environment
-Security and Resilience in the Age of AI
-The cybersecurity landscape is evolving rapidly as bad actors increasingly use artificial intelligence to identify, automate, and exploit technology vulnerabilities at greater speed and scale."
-Source: https://www.fiserv.com/en/legal/cybersecurity.html (retrieved 2026-10-10)</t>
+          <t>"CoPilot: More transparency, less guesswork
+Fiserv’s CoPilot solution enables efficient merchant enrollment, account management, equipment ordering and customer service."
+Source: https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html (retrieved 2026-10-10)
+"“And they truly care about our customers and us as a partner.”
+The results
+BookedBy’s partnership with Fiserv has yielded several positive, measurable outcomes:
+- 10% – 20% higher close rates, driven by better hardware choice and a more seamless payments experience
+- Higher retention, with fewer payment issues and improved merchant satisfaction
+- No lost deals due to payments, thanks to more flexible hardware, pricing and deployment options
+- Faster onboarding, supported by CoPilot and streamlined account management
+- A more cohesive experience, from online booking to in‑person checkout
+For BookedBy, these improvements have translated into revenue growth, stronger customer loyalty and reduced operational strain."
+Source: https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html (retrieved 2026-10-10)
+"With Fiserv’s payments technology, Clover hardware and the transparency offered by CoPilot, the company is positioned to scale effectively as they support more beauty businesses."
+Source: https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html (retrieved 2026-10-10)</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
+          <t>[MOCK] AI usage detected in public content</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>None named — Inconclusive. No sub-processor register or AI policy found publicly.</t>
+          <t>Copilot, OpenAI</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] High</t>
+          <t>[MOCK] Critical</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>Vendor has Critical criticality tier. Weak AI signals detected (score: 8.4) but insufficient to confirm service-specific usage. Provisional rating based on criticality and data class ("Full customer master, balances and transactions for 1.4 million customers.").</t>
+          <t>Vendor has Critical criticality tier with confirmed AI footprint. Data accessed includes "Full customer master, balances and transactions for 1.4 million customers.". Weighted evidence score: 247.1 across 105 valid signal(s). Evidence strength: strong.</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>Issue an AI usage questionnaire to clarify whether AI is used in the service provided to Meridian. Include questions on model providers, data handling, and oversight. Flag for follow-up review in next assessment cycle.</t>
+          <t>Issue a targeted AI questionnaire within 15 business days covering: (1) model provider identity, hosting region, and data retention policy; (2) whether Meridian data (Full customer master, balances and transactions for 1.4 million customers.) is processed by AI models; (3) human review controls over AI-generated outputs. Register the vendor on the AI sub-processor inventory. Raise AI-specific contract clauses at next review, addressing training restrictions, sub-processor change notification, and rights to audit. Escalate to Third-Party Risk Committee if confirmation not received within 30 days.</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
@@ -1382,8 +1382,8 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">No indicative AI evidence found.
-Sources successfully checked (0): </t>
+          <t>No indicative AI evidence found.
+Sources successfully checked (1): https://www.terrapintech.com/blog</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>Vendor has Medium criticality tier. Insufficient coverage (0 pages checked, 0 gaps) to confirm absence of AI. Provisional rating applied.</t>
+          <t>Vendor has Medium criticality tier. Insufficient coverage (1 pages checked, 0 gaps) to confirm absence of AI. Provisional rating applied.</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -1485,27 +1485,29 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Inconclusive</t>
+          <t>[MOCK] Yes</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>"- Definitions
+          <t>"The Bank of New York Mellon SA/NV operates in the Netherlands through its Amsterdam branch at Tribes SOM2 Building, Claude Debussylaan 7, 1082 MC Amsterdam, the Netherlands, registered with the Dutch Chamber of Commerce under registration number 34363596."
+Source: https://www.bny.com/corporate/global/en/solutions/platforms/conventional-trust-solutions/escrow-specialty-solutions.html (retrieved 2026-10-10)
+"- Definitions
  For the purposes of this Policy:
   - “Artificial Intelligence” means any technology that enables machines to perform tasks that typically require human intelligence, including but not limited to generative AI, machine learning, natural language processing, and computer vision."
 Source: https://www.bny.com/ai-policy (retrieved 2026-10-10)
-"This Acceptable Use Policy (“Policy”) applies to Your use of all services offered by BNY or third-party products, applications, or functionality that interoperate with services offered by BNY, that incorporate Artificial Intelligence, including proprietary and third-party solutions (each, an “AI Service”)."
-Source: https://www.bny.com/ai-policy (retrieved 2026-10-10)</t>
+"In particular, we may use automated methods of treatment, such as Artificial Intelligence ("AI") and Machine Learning ("ML"), which are a set of technologies programmed to perform tasks and actions that are commonly associated with humans."
+Source: https://www.bny.com/corporate/br/en/privacy-policy.html (retrieved 2026-10-10)</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
+          <t>[MOCK] AI usage detected in public content</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>None named — Inconclusive. No sub-processor register or AI policy found publicly.</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -1515,12 +1517,12 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>Vendor has High criticality tier. Weak AI signals detected (score: 3.3) but insufficient to confirm service-specific usage. Provisional rating based on criticality and data class ("Payment instructions, counterparty names and account identifiers.").</t>
+          <t>Vendor has High criticality tier with confirmed AI footprint. Data accessed includes "Payment instructions, counterparty names and account identifiers.". Weighted evidence score: 20.5 across 6 valid signal(s). Evidence strength: strong.</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>Issue an AI usage questionnaire to clarify whether AI is used in the service provided to Meridian. Include questions on model providers, data handling, and oversight. Flag for follow-up review in next assessment cycle.</t>
+          <t>Issue a targeted AI questionnaire within 15 business days covering: (1) model provider identity, hosting region, and data retention policy; (2) whether Meridian data (Payment instructions, counterparty names and account identifiers.) is processed by AI models; (3) human review controls over AI-generated outputs. Register the vendor on the AI sub-processor inventory. Raise AI-specific contract clauses at next review, addressing training restrictions, sub-processor change notification, and rights to audit. Escalate to Third-Party Risk Committee if confirmation not received within 30 days.</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
@@ -1597,39 +1599,64 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] No</t>
+          <t>[MOCK] Inconclusive</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>No indicative AI evidence found.
-Sources successfully checked (18): https://www.theclearinghouse.org, https://www.theclearinghouse.org/forms-old/rtp-compliance-implications, https://www.theclearinghouse.org/forms-old/rtp-network-rules-compliance-enforcement, https://www.theclearinghouse.org/payment-systems/articles/2018/08/data-privacy-08-21-2018, https://www.theclearinghouse.org/payment-systems/articles/2018/10/data-privacy-10-18-2018, https://www.theclearinghouse.org/payment-systems/articles/2019/07/071119-heritage-trust, https://www.theclearinghouse.org/payment-systems/articles/2024/07/cfpb-compliance-deadline, https://www.theclearinghouse.org/payment-systems/rtp/technical-documentation
-Coverage gaps (18): https://www.theclearinghouse.org/ai-policy, https://www.theclearinghouse.org/docs, https://www.theclearinghouse.org/dpa, https://www.theclearinghouse.org/payments-services/education/ach/compliance-risk-management, https://www.theclearinghouse.org/payments-services/education/corporate/compliance-risk-management</t>
+          <t>"SIMMS ELECTRONICS INC            
+SINBAD GLOBAL HOOKAH AND TOBACCO            
+SINE AUTO ENTERPRISES LLC            
+Single Ply Solutions Incorporated            
+SINGULARITY ENERGY CORP            
+SINOXSA LLC            
+Sir Robotics Inc            
+Sirius Group LLC            
+SIS CYBER LLC            
+Sistemas Automotrices de M??xico s.a de c.v            
+Sistemas Automotrices de Mexico sa de cv            
+Sitech West LLC            
+Sitike            
+SIVIEW AMERICA INC            
+Six J Corp            
+SJ Distributors, Inc."
+Source: https://www.theclearinghouse.org/account/memberships (retrieved 2026-10-10)
+"- 
+                                                            Concurrent Session
+                                                            2025 Payments Hot Topics from a Legal PerspectiveKatherine Razdolsky Rothstein, Taft Law 
+ Aisha Hall, Taft LawIn this session, payments lawyers will share their insight and perspective on trends and hot topics giving rise to legal issues in payments for 2025, including, payment technology, regulatory changes, artificial intelligence, open banking, third party relationships and more!"
+Source: https://www.theclearinghouse.org/payments-services/concepts-conference/agenda (retrieved 2026-10-10)
+"Adrian Brown, The Clearing House
+Christina Rice, The Clearing House
+- 
+                                                            Concurrent Sessions
+                                                            Banking on AI: Boosting Productivity and Streamlining Workflows in Financial InstitutionsKevin Miyamoto, Identifee Discover how forward-thinking financial institutions are harnessing artificial intelligence to enhance their operations."
+Source: https://www.theclearinghouse.org/payments-services/concepts-conference/agenda (retrieved 2026-10-10)</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] N/A — no public evidence of AI usage in the service provided to Meridian.</t>
+          <t>[MOCK] Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>None named — Inconclusive. No sub-processor register or AI policy found publicly.</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] None identified</t>
+          <t>[MOCK] High</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>No public evidence of AI usage across adequate coverage (18 pages checked). Rating subject to the caveat that absence of evidence is not evidence of absence.</t>
+          <t>Vendor has Critical criticality tier. Weak AI signals detected (score: 0.8) but insufficient to confirm service-specific usage. Provisional rating based on criticality and data class ("Payment messages in transit only.").</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>Monitor annually. No immediate action required based on current public evidence.</t>
+          <t>Issue an AI usage questionnaire to clarify whether AI is used in the service provided to Meridian. Include questions on model providers, data handling, and oversight. Flag for follow-up review in next assessment cycle.</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
@@ -2157,7 +2184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2205,12 +2232,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V-002</t>
+          <t>V-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/solutions/risk-compliance/aml-risk-manager.html</t>
+          <t>https://www.automworx.com/ai-policy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2220,27 +2247,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/solutions/risk-compliance/aml-risk-manager.html</t>
+          <t>https://www.automworx.com/ai-policy</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-10T06:17:40.484938+00:00</t>
+          <t>2026-10-10T15:53:47.348183+00:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>|  | Advanced detection techniques Leverage AI-driven risk scoring to analyze transaction patterns and customer behavior in real time.</t>
+          <t>Experience the power of … Use ChatGPT to answer questions, write, create images, complete work, and code—all in one place.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>INDICATIVE</t>
+          <t>MARKETING-ONLY</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>bbf9f86093b9ffb25ab6aed003eaf13162c0712252e6bdfdd50cf8312e0dbda0</t>
+          <t>e3835c60d332e8ffc718b5d055d26db82380600d1911a6349413760aa235539d</t>
         </is>
       </c>
     </row>
@@ -2252,25 +2279,2501 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:29.653365+00:00</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CoPilot: More transparency, less guesswork
+Fiserv’s CoPilot solution enables efficient merchant enrollment, account management, equipment ordering and customer service.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>f1ba12226b8b9b70d50b0644f1fbc6e9c80a02008f29208b84bd2907cc4afecc</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:29.653365+00:00</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>“And they truly care about our customers and us as a partner.”
+The results
+BookedBy’s partnership with Fiserv has yielded several positive, measurable outcomes:
+- 10% – 20% higher close rates, driven by better hardware choice and a more seamless payments experience
+- Higher retention, with fewer payment issues and improved merchant satisfaction
+- No lost deals due to payments, thanks to more flexible hardware, pricing and deployment options
+- Faster onboarding, supported by CoPilot and streamlined account management
+- A more cohesive experience, from online booking to in‑person checkout
+For BookedBy, these improvements have translated into revenue growth, stronger customer loyalty and reduced operational strain.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>f1ba12226b8b9b70d50b0644f1fbc6e9c80a02008f29208b84bd2907cc4afecc</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:29.653365+00:00</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>With Fiserv’s payments technology, Clover hardware and the transparency offered by CoPilot, the company is positioned to scale effectively as they support more beauty businesses.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>f1ba12226b8b9b70d50b0644f1fbc6e9c80a02008f29208b84bd2907cc4afecc</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/five-reasons-the-right-payment-devices-drive-isv-success.html</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/five-reasons-the-right-payment-devices-drive-isv-success.html</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:59:16.069783+00:00</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>That’s where CoPilot from Fiserv, a portfolio management platform designed exclusively for partners, excels.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>79cfadcb73d7777d2c635cbc10688c01a8c25e94432cd7bdad9ea855705278ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/solutions/notifi-real-time-engagement/notifi-detect.html</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/solutions/notifi-real-time-engagement/notifi-detect.html</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:17:07.032951+00:00</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>| 
+|---|---|
+|  | Powered by machine learning Leverage a predictive scoring model that learns from past experiences with your accounts to ensure constant refinement — Stay ahead of emerging fraud trends while boosting consumer satisfaction.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0bb738ce5f32c8f734f491ff33dfae60acb4c57047b41cba1000be165c0f89c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv.html</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv.html</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:18:33.255733+00:00</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Deliver a seamless payment experience with Fiserv
+The Fiserv difference
+CoPilot Portfolio Management
+CoPilot is a powerful partner portfolio management system that gives software providers the tools to onboard business customers and operate more efficiently.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>843134a0576c29ac4f746db21cfe2f5b46c3b6b584699b4786425a3b12b6014a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/partner-support.html</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/partner-support.html</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:18:43.822639+00:00</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CoPilot from Fiserv
+A powerful partner portfolio management system that gives software providers the tools to onboard business customers and operate more efficiently.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>8dd58af9ccba196f3230d88f181ec520cb4b0fb65eb082fdd0c96b03eca41f48</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/solutions/risk-compliance/aml-risk-manager.html</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Tier_A</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/solutions/risk-compliance/aml-risk-manager.html</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:55:53.603656+00:00</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>|  | Advanced detection techniques Leverage AI-driven risk scoring to analyze transaction patterns and customer behavior in real time.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>bbf9f86093b9ffb25ab6aed003eaf13162c0712252e6bdfdd50cf8312e0dbda0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:13.971042+00:00</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>The explosion of interest in AI, fueled by the recent introduction of ChatGPT from OpenAI, has executives across industries rethinking what generative AI means to their business and how and where to begin adoption.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>99179c0ac4fcebf059b90e9db72972077025d5446c7a7f1d12a8d091a62770d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:29.653365+00:00</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>With CoPilot, the BookedBy team can:
+- Track equipment orders and pricing in real time
+- See when a merchant contacts support, making follow‑up proactive
+- Troubleshoot issues faster with shared visibility between teams
+This level of clarity helps BookedBy to deliver a stronger support experience for salons, and resolve issues before they become disruptions.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>f1ba12226b8b9b70d50b0644f1fbc6e9c80a02008f29208b84bd2907cc4afecc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/five-reasons-the-right-payment-devices-drive-isv-success.html</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/five-reasons-the-right-payment-devices-drive-isv-success.html</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:59:16.069783+00:00</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CoPilot gives ISVs a powerful dashboard to:
+- Oversee merchant onboarding
+- Order and track equipment
+- Manage device provisioning and support requests
+- View merchant and device status in real time
+With CoPilot, ISVs can scale efficiently while maintaining visibility and control over their entire portfolio.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>79cfadcb73d7777d2c635cbc10688c01a8c25e94432cd7bdad9ea855705278ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/why-isvs-choose-fiserv-as-their-strategic-growth-partner.html</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/why-isvs-choose-fiserv-as-their-strategic-growth-partner.html</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:49.424620+00:00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Our powerful partner portal, CoPilot, brings it all together in one place.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>116e954ada2929835a68a16c7645e4ad5b23510f6c5734d58ab4e301a7ebcfd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:10.845485+00:00</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>The good news, from Bliink’s point of view, is that AI solutions are now bringing automation capabilities to check fraud prevention.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:13.971042+00:00</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>To that end, Chiarello highlighted key areas of continued focus and investment to accelerate the pace of innovation, including:
+- Deliver open, scalable platforms that make it easier and faster for clients to connect and embed new capabilities
+- Provide broader, deeper data and AI-driven insights across industries and technologies
+Omnichannel experiences are essential to serving the diverse needs of today’s consumers.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>99179c0ac4fcebf059b90e9db72972077025d5446c7a7f1d12a8d091a62770d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:13.971042+00:00</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Existing use cases for AI-powered Connected Intelligence span simple yet robust customer self-service, lead generation, improved fraud prevention, modifying loyalty and rewards programs to better serve customers, and even gaining better insights into macroeconomic trends.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>99179c0ac4fcebf059b90e9db72972077025d5446c7a7f1d12a8d091a62770d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:15.552514+00:00</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Eventually, merchants need the ability to:
+- Model predictions
+- Analyze performance at scale
+- Unify data from multiple channels
+- Support machine learning and AI use cases
+- Structure data in formats that can be consumed by autonomous agents
+Cloud-based data access, secure sharing environments and flexible analytics platforms help businesses build this foundation at their own pace.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/analytics-teams-real-time-data-accelerate-growth-for-gaming-platforms.html</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/analytics-teams-real-time-data-accelerate-growth-for-gaming-platforms.html</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:20.276343+00:00</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>A new report reveals how well gaming platforms are using data for predictive analytics and decision making to spur innovation and boost revenue.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6dedcb01a708f7fa0c4017895c7cbd9aeecc8b675ffc30c1b7a0785bfd1e7ec1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-how-financial-institutions-can-get-the-most-out-of-tech-upgrades.html</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-how-financial-institutions-can-get-the-most-out-of-tech-upgrades.html</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:43.020266+00:00</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Core modernization isn’t a topic you’re likely to find trending on social media: It doesn’t have the high-tech buzz of AI-powered fraud prevention tools or real-time payments, for example, even though it might be required for both.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>193b8a323cc5fa25418e0f44b8f94bb071a83155dd1dd864d6396dcd90763b45</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/coreadvance-modern-banking-designed-on-five-key-principles.html</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/coreadvance-modern-banking-designed-on-five-key-principles.html</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:44.586000+00:00</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>That gives banks the power to use AI for opportunities such as customer support automation, fraud detection and the combination of complex, multiapplication workflows into a single experience.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>416e322288c2e372bf41e7514254a66afdf5946085ff5c89360d43a7ca514141</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/drive-more-commerce-with-carat.html</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/drive-more-commerce-with-carat.html</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:54.090582+00:00</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>We use machine learning for smarter outcomes, leverage biometrics to secure devices, and continue to deliver tailored experiences to protect both the customer and the merchant.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>35a48eeb9e0acb60d593968be5c3ad1c16ea3a72e1dd26779275567cb1e042b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:59:23.989694+00:00</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Through machine learning and the use of historical transaction data from your account processing system, a benchmark is established for each account type and used to identify suspicious, out-of-pattern activity.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>7fd5d1bd270bd5616598a4e10fbe9d4339457256c77c7cb944be0c13105dbe54</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:59:27.102712+00:00</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Machine learning helps data scientists determine which transactions are likely to be fraudulent, while reducing false positives.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1d3c0019028d36c1ec0c2b754b1434b3669edfc02b414759f5b341a283522232</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/future-proofing-treasury.html</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/future-proofing-treasury.html</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:59:33.380466+00:00</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Many banks are adding digital assistants and embedding AI-driven self-service help tools in their digital banking platforms to deliver a better experience and reduce traffic at the helpdesk.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>cde3daba1f67e6d096e3f34439c4c5c84f527a9cfa99964f80cd1e121a75fbd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-to-help-cardholders-understand-their-spending-at-a-glance.html</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-to-help-cardholders-understand-their-spending-at-a-glance.html</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:00:01.964229+00:00</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>This can be used to build deep-and-wide machine learning models to produce results that yield significant transaction data enrichment.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>36548b64b6e93d9e6029f53855f9487edf5cbf97e6902bd8cd096ca56000d94b</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/invoice-to-cash-explained-how-ar-is-becoming-a-strategic-growth-engine.html</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/invoice-to-cash-explained-how-ar-is-becoming-a-strategic-growth-engine.html</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:00:16.412082+00:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Electronic invoice presentment, self-service portals, integrated payment channels, automated reconciliation and predictive analytics create a closed loop that gives finance teams real-time visibility, earlier signals and far greater control over outcomes.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>650b552d95e2c5bdc832e6173028fac158719db7db1d2e98e3e2adba62124e43</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:00:17.989440+00:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>When financial institutions use this AI-powered tool, 80% of calls are answered within 15 seconds, average handle time is cut by 30 seconds, and customer experience increases by 15%.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>e0c16da5e0626951b34c1e145f27b18f2f6d77a1e8234f2a533060bd3d7a8466</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:00:49.718239+00:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Rethinking Customer Loyalty Programs: How Merchants Can Differentiate, Drive ROI and Prepare for an AI-Driven Future
+Customer loyalty programs are an effective way for a business to encourage deeper engagement and create sustainable growth.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>cb7849ecf803cb1eef0a646183a50e456a89ce44550c196d75a3c234d72a0507</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:00:49.718239+00:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>AI disruption: how intelligent experiences are redefining engagement
+The reliance on customer data and artificial intelligence (AI) has transformed loyalty from static points programs into adaptive ecosystems.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>cb7849ecf803cb1eef0a646183a50e456a89ce44550c196d75a3c234d72a0507</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:00:49.718239+00:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>AI-powered analysis also allows merchants to anticipate customer needs and serve up timely offers when they are most likely to influence behavior.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>cb7849ecf803cb1eef0a646183a50e456a89ce44550c196d75a3c234d72a0507</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:00:57.710588+00:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>[Expectations &amp; Experiences: AI and Payments Innovation](https://www.fiserv.com/en/about-fiserv/resource-center/consumer-research/2023-expectations-experiences-consumer-ai-impact.html), the most recent consumer trends research from Fiserv, examines attitudes and habits toward personal finance, payment options and AI-powered banking.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/strategic-growth-playbook-5-priorities-for-community-banks.html</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/strategic-growth-playbook-5-priorities-for-community-banks.html</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:00:59.322995+00:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>- Investing in AI-powered detection: Banks can deploy monitoring tools that flag anomalies, like an unusual overseas transfer request from a local client’s account, providing real-time alerts and preventing fraud attempts before they start.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>77acf24969f9b9fd585c7816a5afa0388deeacc835e2fb5a30408b2028332651</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-catalyst-for-change.html</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-catalyst-for-change.html</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:04.069624+00:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>They need a solution that meets today’s reality of instant payments, heightened customer expectations, embedded finance, and AI-powered services.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>29ceae0f8821c07acbc4bed958a564ed64f25010d1998133e51acb1c70e5cf18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:11.998445+00:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Three trends are reshaping the banking landscape: AI-powered services, hyper-personalization and 24/7 instant payments.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>d6f4fa7e61fa7c60a727651c3187a2da56c34c975f067ea27f434b8978efe06e</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:21.614612+00:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>An AI-powered payments navigator can act as a dedicated, expert assistant and provide an explanation of the error code, remedial steps and even preventative recommendations.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-it-really-takes-to-keep-up-with-the-speed-of-commerce.html</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-it-really-takes-to-keep-up-with-the-speed-of-commerce.html</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:43.026793+00:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>AI-driven shopping behaviors are reshaping how products are discovered and purchasing decisions are made, with agentic systems that can compare options, select products, place orders and manage replenishment on behalf of consumers.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>bd467288d7aa77c46501432756a5ad595f2e7593e7208fa4978a99cf790d112d</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-it-really-takes-to-keep-up-with-the-speed-of-commerce.html</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-it-really-takes-to-keep-up-with-the-speed-of-commerce.html</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:43.026793+00:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>And as commerce continues to evolve toward agentic models, AI-driven purchasing and new forms of digital interaction, enterprises need infrastructure that is already prepared for those shifts: secure, tokenized, authenticated and designed for machine-initiated transactions as well as human ones.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>bd467288d7aa77c46501432756a5ad595f2e7593e7208fa4978a99cf790d112d</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/why-move-to-the-public-cloud.html</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/why-move-to-the-public-cloud.html</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:51.034050+00:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Moving to a public cloud accessing data from across the organization on a single platform can provide the opportunity for data analytics and AI-driven insights.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>dfd2abc35ffadbc4aedf3794eb57675a3d8ec8e0f5377fa338184cd0595d40cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/businesses-and-merchants.html</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/businesses-and-merchants.html</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:56.449520+00:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Agentic commerce is here: What merchants need to know and do
+How AI-powered agents are already reshaping commerce, and how merchants can prepare to protect identity, loyalty and payments.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>70f21ebf8b872d3414d5a01ad50f36f6dbbb470e5ab9383d2d85d510cbffc2ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/in-person-payments.html</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/in-person-payments.html</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:18:36.540068+00:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Manage your portfolio with our partner portal, CoPilot from Fiserv, where you can order pre-provisioned devices, track orders and activate your devices.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3058175eb22db2dce8f16f8b4ae7f7a8b4b4720ae755dcfd4379cdc4a7c2836f</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/partner-support.html</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/partner-support.html</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:18:43.822639+00:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Operate efficiently at scale with our CoPilot partner portfolio management system and manage everything from merchant enrollment to risk monitoring and user support.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>8dd58af9ccba196f3230d88f181ec520cb4b0fb65eb082fdd0c96b03eca41f48</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:16:48.520050+00:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>| 
+|---|---|
+|  | Infrastructure protection Mitigate and manage potential business disruption with behavior analytics, machine learning and professionally managed computing services from Fiserv to secure your infrastructure, back office and data.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>db2b1269d91228c705dabdad0653e298cb023eb103f956b5da090f04a38a3bdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/12-questions-to-ask-when-selecting-a-digital-commerce-payments-vendor.html</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/12-questions-to-ask-when-selecting-a-digital-commerce-payments-vendor.html</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:57:58.253248+00:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Leading providers offer robust fraud prevention tools – such as tokenization, 3DS, AI-driven rule sets, and the flexibility to retain tokenized data when switching vendors.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>37449e427d5a84b7403cd01c729b22337a1ba2999285a7239e732ad628f99b60</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/4-ways-to-elevate-card-programs-for-both-issuers-and-cardholders.html</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/4-ways-to-elevate-card-programs-for-both-issuers-and-cardholders.html</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:04.576694+00:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>As fraudsters evolve their tactics, issuers with robust, multilayered security that leverages predictive analytics to identify emerging fraud trends are better positioned to maintain consumer confidence and minimize losses.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>fda559e724cc2e3ff4c4d2fe09dc6aef85231ca89b4289b3e3537dd932ace24a</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:10.845485+00:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Thanks to artificial intelligence and machine learning, image analytics has matured to a point where we can more easily identify whether a suspect check is first party or third party, or whether it was whitewashed or changed in some other way.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:15.552514+00:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Data capabilities from Fiserv support this progression by giving businesses a path from basic visibility to advanced, AI-driven intelligence through four important means:
+Merchants first need a clear view of their business: simple dashboards, intuitive reporting and the ability to quickly answer everyday questions.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/community-banking-modernizing-with-confidence.html</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/community-banking-modernizing-with-confidence.html</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:37.516984+00:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Together, these factors make it more critical than ever for banks, credit unions, and fintechs to deliver a truly robust digital experience."
+To capture this opportunity, Stewart Russell says core data and AI are essential and can enable experiences like predictive insights, proactive issue identification, automation and enhanced security.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>088efbad3d4fdf3b48fc2734ad45b8aec830f7de6b69889b1287fc3697f93391</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/enabling-the-acceleration-of-all-things-digital.html</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/enabling-the-acceleration-of-all-things-digital.html</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:59:00.582236+00:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>That means working to improve consumer journeys, personalize interactions and modernize experiences with real-time data, automation tools and AI, to name a few.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>f38e2dfa91b34f6c162ce065fce285464704c9e0ac64cce8a50ba1e03f945ab9</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:59:14.264948+00:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>This gives us access to large amounts of data which, when analyzed through machine learning, robotic process automation and other advanced technology, enables us to create a broad view of fraudulent activity.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>203ecbe73bbb6d5fa4453b937b5a21ea13c57ac97be86b644d642a3f03808984</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:59:14.264948+00:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Machine learning helps distinguish between legitimate and fraudulent behaviors while adapting over time to new, previously unseen fraud tactics.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>203ecbe73bbb6d5fa4453b937b5a21ea13c57ac97be86b644d642a3f03808984</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:59:27.102712+00:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Because of the many possible data points to be considered, optimizing the use of machine learning is essential to all of this.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>1d3c0019028d36c1ec0c2b754b1434b3669edfc02b414759f5b341a283522232</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:59:27.102712+00:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>If done properly, machine learning may be used to distinguish between legitimate and fraudulent behaviors while adapting over time to new, previously unseen fraud tactics.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1d3c0019028d36c1ec0c2b754b1434b3669edfc02b414759f5b341a283522232</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/future-proofing-treasury.html</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/future-proofing-treasury.html</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:59:33.380466+00:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Agentic AI – For bank operations, AI is the next step in intelligent process automation.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>cde3daba1f67e6d096e3f34439c4c5c84f527a9cfa99964f80cd1e121a75fbd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-your-bank-can-evolve-to-face-economic-uncertainty.html</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-your-bank-can-evolve-to-face-economic-uncertainty.html</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:00:08.494427+00:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Leveraging internal data and predictive analytics gives community banks a leg up, allowing them to forecast potential stress points, adjust underwriting standards and plan more strategically for differing economic scenarios.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>9b92194e0871e826ea5d8f7dc895189c41c5fe0389f07d987705a27321935e76</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/invoice-to-cash-explained-how-ar-is-becoming-a-strategic-growth-engine.html</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/invoice-to-cash-explained-how-ar-is-becoming-a-strategic-growth-engine.html</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:00:16.412082+00:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Advanced analytics and machine learning are shifting AR from a rear-view-mirror function to a forward-looking one.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>650b552d95e2c5bdc832e6173028fac158719db7db1d2e98e3e2adba62124e43</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:00:49.718239+00:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>And it looks ahead by laying the groundwork for the next phase of loyalty: AI-driven engagement.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>cb7849ecf803cb1eef0a646183a50e456a89ce44550c196d75a3c234d72a0507</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-programmable-payments.html</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-programmable-payments.html</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:27.917285+00:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Artificial intelligence and machine learning can play a role in recommending the ideal way to pay in a particular situation, lifting the decision burden from the cardholder while optimizing their cash flow.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>7d1cd46e3c594f945fd880fb57c9d0b00aa495dc2a933d40fbef28f51b9abb7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:35.805808+00:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>The last part – not just identifying but making decisions and taking actions – is what defines “agentic AI” as fundamentally different from chatbot-style Q&amp;A interfaces.</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>9e68a548aa5556c99d7bd1ef77c4c78f627fb87378bd505d306c91b782595ab2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:35.805808+00:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Agentic AI goes beyond predefined workflows and rules-based robotic process automation.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>9e68a548aa5556c99d7bd1ef77c4c78f627fb87378bd505d306c91b782595ab2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Tier_A</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-10-10T06:17:27.063871+00:00</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:55:37.573244+00:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>Our approach includes:
 - Ongoing investment in cybersecurity and technology modernization
@@ -2282,144 +4785,2468 @@
 As the threat landscape continues to evolve, Fiserv remains committed to helping clients operate securely through defined cybersecurity practices, reliable technology platforms, and ongoing innovation.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>MARKETING-ONLY</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>c8ae42b7ee474576c84822b5f8d2a9e306f7e26ed7e7a10c1198ff5990595d35</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>V-002</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en-em/solutions/manage-risk-fraud.html</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en-em/solutions/manage-risk-fraud.html</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:05:20.639179+00:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Our award-winning fraud and Anti-Money Laundering (AML) technologies use a mixture of artificial and automated intelligence, machine learning, and robotics to improve your operational efficiency, deliver rich analytics and strategic evaluation, reduce your costs, and fine-tune risk exposure.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>037a7bac331d71f63311e156b60e25e3933f913cb6d76b482503d986f7164778</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en-it/solutions/manage-risk-and-fraud.html</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en-it/solutions/manage-risk-and-fraud.html</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:07:03.125696+00:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Our award-winning fraud and Anti-Money Laundering (AML) technologies use a mixture of artificial and automated intelligence, machine learning, and robotics to improve your operational efficiency, deliver rich analytics and strategic evaluation, reduce your costs, and fine-tune risk exposure.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>359cd9ceab797b44019327610ad2f81b8163d2d388dd8624f8b1e78c31d2d926</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en-me/solutions/manage-risk-fraud.html</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en-me/solutions/manage-risk-fraud.html</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:07:47.697392+00:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Our award-winning fraud and Anti-Money Laundering (AML) technologies use a mixture of artificial and automated intelligence, machine learning, and robotics to improve your operational efficiency, deliver rich analytics and strategic evaluation, reduce your costs, and fine-tune risk exposure.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>aba8c3326b3a57c028fa4281e03f8c89f1161e56af59274b887a4844207be79f</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en-pl/financial-institutions/manage-risk-fraud.html</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en-pl/financial-institutions/manage-risk-fraud.html</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:09:14.693659+00:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Our award-winning fraud and Anti-Money Laundering (AML) technologies use a mixture of artificial and automated intelligence, machine learning, and robotics to improve your operational efficiency, deliver rich analytics and strategic evaluation, reduce your costs, and fine-tune risk exposure.</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>9478dbb9730718ea4f71685c2350e60c496c70df3e26dacfe9e8b52caaf6dc02</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en-uk/financial-institutions/manage-risk-fraud.html</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en-uk/financial-institutions/manage-risk-fraud.html</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:10:10.056857+00:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Our award-winning fraud and Anti-Money Laundering (AML) technologies use a mixture of artificial and automated intelligence, machine learning, and robotics to improve your operational efficiency, deliver rich analytics and strategic evaluation, reduce your costs, and fine-tune risk exposure.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2fcb018b0a3d83178be7a0df584ba9fca30b3ac7b3eae7019be03112fc64b053</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/about-fiserv/corporate-social-responsibility.html</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/about-fiserv/corporate-social-responsibility.html</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:10:32.850587+00:00</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Powering responsible innovation
+A cross-functional governance structure oversees implementation of responsible AI and machine learning capabilities, establishing standards for the appropriate use of new technologies.</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>9b4430e551d08a82fe17a2c378aa2723c53385af4c002e9a7633e54818fcbc6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/about-fiserv/terms-of-use.html</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/about-fiserv/terms-of-use.html</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:11:41.113831+00:00</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>GIVEN THE PROBABILISTIC NATURE OF MACHINE LEARNING, THE INTERACTIVE FEATURES MAY IN SOME SITUATIONS PRODUCE OUTPUT THAT IS INACCURATE, INCORRECT, OFFENSIVE OR OTHERWISE UNDESIRABLE.</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>bfa8380add2a09707c87d75789ead3d56ecc14c33b8026f0aadb82881934be0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/who-we-serve/enterprise/commerce-control-center.html</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/who-we-serve/enterprise/commerce-control-center.html</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:18:11.077288+00:00</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>| 
+|---|---|
+|  | Actionable insights Use AI-powered tools to uncover trends, identify opportunities and make faster, data-driven decisions.</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>d2ec2e00fd8453d92033a40b146dd853dd3869f375c2f4e6315ff8a5cbf594f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/who-we-serve/enterprise/reporting-and-analytics.html</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/who-we-serve/enterprise/reporting-and-analytics.html</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:18:23.207046+00:00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>| 
+|---|---|
+|  | Advanced analytics and drilldowns Leverage automation and AI-supported capabilities to reduce manual effort and improve consistency.</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>f61a3c7f790aefdf9680057a8c3043f34700fe432818fe132243d0c291e0d2a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:10.845485+00:00</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Fraud is a growing issue in the financial services industry, and the threat is evolving faster than ever as fraudsters take advantage of advancements in technology like generative AI.</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:10.845485+00:00</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>The good news: 93% of the financial institutions Fiserv speaks to say they believe generative AI will help fortify fraud detection to protect customers and members.</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:10.845485+00:00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Bliink AI is an independent technology firm that creates fraud prevention solutions that use generative AI to help financial institutions ensure compliance, data privacy and security.</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-how-financial-institutions-can-get-the-most-out-of-tech-upgrades.html</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-how-financial-institutions-can-get-the-most-out-of-tech-upgrades.html</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:43.020266+00:00</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>That includes relationship managers who oversee the entire relationship, account managers who are standing by to help with day-to-day operations and AI-enabled platforms, such as Client360, which answers questions in seconds and provides self-service tools and resources 24/7/365.</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>193b8a323cc5fa25418e0f44b8f94bb071a83155dd1dd864d6396dcd90763b45</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/coreadvance-modern-banking-designed-on-five-key-principles.html</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/coreadvance-modern-banking-designed-on-five-key-principles.html</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:44.586000+00:00</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>From build to deploy, the platform uses automated pipelines, AI powered quality checks and modern engineering practices to maximize efficiency and reliability.</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>416e322288c2e372bf41e7514254a66afdf5946085ff5c89360d43a7ca514141</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/coreadvance-modern-banking-designed-on-five-key-principles.html</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/coreadvance-modern-banking-designed-on-five-key-principles.html</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:44.586000+00:00</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>AI-enabled: A foundation for optimization
+The CoreAdvance banking platform can help to safely and responsibly support AI adoption across every layer – architecture, build processes, operations and optimization.</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>416e322288c2e372bf41e7514254a66afdf5946085ff5c89360d43a7ca514141</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:59:23.989694+00:00</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>- Use transaction analysis
+ Identify check fraud activity with an analysis and forecasting engine that uses neural network algorithms to recognize patterns of suspicious activity, such as deposit fraud and check kiting.</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>7fd5d1bd270bd5616598a4e10fbe9d4339457256c77c7cb944be0c13105dbe54</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/real-time-data--the-untapped-growth-engine-for-platform-business.html</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/real-time-data--the-untapped-growth-engine-for-platform-business.html</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:00:43.395500+00:00</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Highlights
+- 9/10 firms have used GenAI to obtain and analyze payments and transaction data
+- Firms with a high reliance on data saw average gains more than 10x higher than less data-reliant firms
+- 99% cite missed business opportunities, flawed forecasting and customer churn due to insufficient or delayed data
+- 58% said they made inaccurate decisions and 55% reported lost business because they didn’t have data in time
+Who’s most likely to have real-time data access?</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>84d6116d7c56f3ec2213b114ece35a9bd276e16a314513a73c863d98b7371614</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:11.998445+00:00</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Generative AI has become one of the most powerful tools for reimagining customer service, product design and back-office operations.</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>d6f4fa7e61fa7c60a727651c3187a2da56c34c975f067ea27f434b8978efe06e</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:21.614612+00:00</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>In the few years that artificial intelligence has been top of mind for enterprise technology leaders, rapid change has come to nearly every aspect of financial services.</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:21.614612+00:00</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Artificial intelligence excels at two important things: it recognizes patterns and works with text (and, increasingly, speech) well enough to meaningfully alter the way enterprises are automating their payments-related processes.</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:29.483063+00:00</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Understanding the generative AI industrial revolution
+AI innovation is accelerating – with implications for financial services and payments
+Generative AI is reshaping our world.</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:31.068758+00:00</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Unlocking GenAI’s Promise in Retail
+A new report offers clues to the retail potential of today’s hottest technology
+Generative artificial intelligence (GenAI) is poised to reshape the retail environment – from enhancing transaction security to delivering more personalized shopping experiences.</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>56108dc2fba7dfbfd2b48a1eebd3de1eff62387bc8117916a166eca4d481cf93</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:31.068758+00:00</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Forward-thinking enterprises that have adopted GenAI are already seeing measurable improvements in customer retention, forecasting precision and strategic decision-making.</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>56108dc2fba7dfbfd2b48a1eebd3de1eff62387bc8117916a166eca4d481cf93</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:31.068758+00:00</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>These are some of the questions explored in a new collaborative study from PYMNTS Intelligence and Fiserv – GenAI Applications in Retail Transaction Analysis: Industry Trends and Insights.</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>56108dc2fba7dfbfd2b48a1eebd3de1eff62387bc8117916a166eca4d481cf93</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://developer.fiserv.com</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Tier_A</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://developer.fiserv.com</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:54:41.308528+00:00</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>…Read more Artificial intelligence - Wikipedia ARTIFICIAL definition: 1.</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>8289f706488aa97c85147453ce1483a4fe5a7afd22a6a319fa23c5daaa1681fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
         <is>
           <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Tier_A</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-10-10T06:17:27.063871+00:00</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:55:37.573244+00:00</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>Cybersecurity Best Practices in a Rapidly Evolving Threat Environment
 Security and Resilience in the Age of AI
 The cybersecurity landscape is evolving rapidly as bad actors increasingly use artificial intelligence to identify, automate, and exploit technology vulnerabilities at greater speed and scale.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>MARKETING-ONLY</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>c8ae42b7ee474576c84822b5f8d2a9e306f7e26ed7e7a10c1198ff5990595d35</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en-la/financial-institutions/cash-and-logistics/integrated-currency-manager.html</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en-la/financial-institutions/cash-and-logistics/integrated-currency-manager.html</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:07:25.937016+00:00</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Integrated Currency Manager uses advanced artificial intelligence to assist your forecast of customer demand so you can determine how much cash to order and ship for each cash point, including ATMs, branches and vaults.</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>b5e5049be7de72254f6c7298671346d069630ea4d1c24347bb6f51ebd287841d</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:15.552514+00:00</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Their artificial intelligence agent will.</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:59:02.171467+00:00</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>EaaS is a modernization enabler that can help institutions strengthen data protection, support compliance efforts and establish the foundation for secure, AI driven and cloud enabled banking.</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>070169cf4dd71519acd1ce65c3b767ff9c68c0dbc5ff7a03d8c856f5ae12fd69</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-financial-institutions-can-compete-digitally-and-win.html</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-financial-institutions-can-compete-digitally-and-win.html</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:59:49.238011+00:00</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Use AI and data analytics
+Artificial intelligence is rapidly becoming integrated into every facet of consumers’ lives, and many are feeling very comfortable with it.</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2b10adf13d9f7a73dc07da19a30f4bc2c629ad214c6cae15ca76b73905d1da90</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:00:17.989440+00:00</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Artificial intelligence
+AI is no longer novel, it’s part of everyday life for many adults, 70% of whom say they use it a few times a week according to internal Fiserv data.</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>e0c16da5e0626951b34c1e145f27b18f2f6d77a1e8234f2a533060bd3d7a8466</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:00:17.989440+00:00</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>[Nine in 10 financial institution boards](https://www.pymnts.com/tracker_posts/is-ai-the-master-key-to-bankings-next-era/) have approved the use of generative AI, and 3 in 4 banking leaders say their institutions are using it for departmental functions like fraud detection and risk management.</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>e0c16da5e0626951b34c1e145f27b18f2f6d77a1e8234f2a533060bd3d7a8466</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/navigating-the-future-industry-trends-in-treasury.html</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/navigating-the-future-industry-trends-in-treasury.html</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:00:37.092458+00:00</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>There’s also European regulation relating to artificial intelligence.</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>bb4fa3a31d04d2db5818341f9546533a05bac0448b590bb7c11aab977edbad4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:00:57.710588+00:00</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>The uptake of generative AI, including for financial activities, is completely different than what we’ve seen for voice-activated devices.</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:00:57.710588+00:00</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>But what about generative AI, like the technology behind ChatGPT?</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:00:57.710588+00:00</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>[ChatGPT took two months to reach 100 million active users](https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html) – a milestone that credit cards took 15 years to achieve.</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:00:57.710588+00:00</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Approximately one-third of people (32%) have used generative AI.</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/sustainable-growth-perspectives-for-credit-union-leaders.html</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/sustainable-growth-perspectives-for-credit-union-leaders.html</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:00.898169+00:00</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>We intend to pull more AI tools into our private database, using ChatGPT questioning with some of our knowledge-based systems.</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>24ec430f21834723f4cc81efdffdcab57d12da094265ec6db4ad7cc0aeae98eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:11.998445+00:00</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>A report by Accenture predicts that by 2030, generative AI will be fully integrated into every aspect of banking1, automating tasks and enabling seamless human-machine collaboration.</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>d6f4fa7e61fa7c60a727651c3187a2da56c34c975f067ea27f434b8978efe06e</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:29.483063+00:00</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>In what felt like a blink of an eye, ChatGPT has become a regular part of everyday conversation.</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:29.483063+00:00</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Tom Eck explains how generative AI is shaping our world.</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:29.483063+00:00</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>From the 1950s when the term “artificial intelligence” was first coined to today’s explosion in generative AI, there have been numerous advances and lulls in AI research.</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:29.483063+00:00</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>“ChatGPT reached 100 million active users in just 2 months.</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:31.068758+00:00</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Concerns about their own data analytics maturity often hold them back, creating uncertainty around whether they’re equipped to implement GenAI effectively.</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>56108dc2fba7dfbfd2b48a1eebd3de1eff62387bc8117916a166eca4d481cf93</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:31.068758+00:00</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Can organizations harness GenAI’s full potential without first reinforcing their data foundations?</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>56108dc2fba7dfbfd2b48a1eebd3de1eff62387bc8117916a166eca4d481cf93</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en-la/financial-institutions/cash-and-logistics.html</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en-la/financial-institutions/cash-and-logistics.html</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:07:19.711088+00:00</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Artificial intelligence to produce better cash forecasting and improve their operations.</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>d22e51d8aee16267795ce5787080c6dc933fdd3bc6436e56e90cc74bf3b5118d</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>V-005</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://www.bny.com/corporate/global/en/solutions/platforms/conventional-trust-solutions/escrow-specialty-solutions.html</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Tier_A</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://www.bny.com/corporate/global/en/solutions/platforms/conventional-trust-solutions/escrow-specialty-solutions.html</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:27:00.696993+00:00</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>The Bank of New York Mellon SA/NV operates in the Netherlands through its Amsterdam branch at Tribes SOM2 Building, Claude Debussylaan 7, 1082 MC Amsterdam, the Netherlands, registered with the Dutch Chamber of Commerce under registration number 34363596.</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>bb7ecd775df9a351a2870c707ea2887b2d6abf2f0d09727fa0a083eb0918e945</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>V-005</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
         <is>
           <t>https://www.bny.com/ai-policy</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>Tier_A</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>https://www.bny.com/ai-policy</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-10-10T06:19:45.726343+00:00</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:24:47.859682+00:00</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>- Definitions
  For the purposes of this Policy:
   - “Artificial Intelligence” means any technology that enables machines to perform tasks that typically require human intelligence, including but not limited to generative AI, machine learning, natural language processing, and computer vision.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>INDICATIVE</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t>b31b1f0ef72c6f75f441627dd1e3e12b5305831bc8980275fa4a514304f1d512</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>V-005</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://www.bny.com/corporate/br/en/privacy-policy.html</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Tier_A</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://www.bny.com/corporate/br/en/privacy-policy.html</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:25:18.855469+00:00</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>In particular, we may use automated methods of treatment, such as Artificial Intelligence ("AI") and Machine Learning ("ML"), which are a set of technologies programmed to perform tasks and actions that are commonly associated with humans.</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>8daf652f9ff98f5490b2c994ecee94efe6b1c4b73f05deb50b496ae4dfe056a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>V-005</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Tier_A</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:27:15.940356+00:00</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Leverage secure, advanced technologies, from digital onboarding and automated data feeds to AI-powered document processing and support for digital issuance.</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>044f58b49bc463e09bec6e6a7fed94efb02d2a3e79b2dad04fac76f71fb57f21</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>V-005</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Tier_A</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:27:15.940356+00:00</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Leverage streamlined onboarding, AI-driven workflow optimization, real-time dashboards and APIs for operational excellence and transparency.</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>044f58b49bc463e09bec6e6a7fed94efb02d2a3e79b2dad04fac76f71fb57f21</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>V-005</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
         <is>
           <t>https://www.bny.com/ai-policy</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>Tier_A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>https://www.bny.com/ai-policy</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-10-10T06:19:45.726343+00:00</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:24:47.859682+00:00</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>This Acceptable Use Policy (“Policy”) applies to Your use of all services offered by BNY or third-party products, applications, or functionality that interoperate with services offered by BNY, that incorporate Artificial Intelligence, including proprietary and third-party solutions (each, an “AI Service”).</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t>MARKETING-ONLY</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H113" t="inlineStr">
         <is>
           <t>b31b1f0ef72c6f75f441627dd1e3e12b5305831bc8980275fa4a514304f1d512</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>V-006</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://www.theclearinghouse.org/account/memberships</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://www.theclearinghouse.org/account/memberships</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:38:20.792884+00:00</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>SIMMS ELECTRONICS INC            
+SINBAD GLOBAL HOOKAH AND TOBACCO            
+SINE AUTO ENTERPRISES LLC            
+Single Ply Solutions Incorporated            
+SINGULARITY ENERGY CORP            
+SINOXSA LLC            
+Sir Robotics Inc            
+Sirius Group LLC            
+SIS CYBER LLC            
+Sistemas Automotrices de M??xico s.a de c.v            
+Sistemas Automotrices de Mexico sa de cv            
+Sitech West LLC            
+Sitike            
+SIVIEW AMERICA INC            
+Six J Corp            
+SJ Distributors, Inc.</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>a5faefe6731f4a335b06a55ffc79732cdff58938fc1496e8d8731f7990501835</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>V-006</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://www.theclearinghouse.org/payments-services/concepts-conference/agenda</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://www.theclearinghouse.org/payments-services/concepts-conference/agenda</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2026-10-10T17:05:57.764628+00:00</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>- 
+                                                            Concurrent Session
+                                                            2025 Payments Hot Topics from a Legal PerspectiveKatherine Razdolsky Rothstein, Taft Law 
+ Aisha Hall, Taft LawIn this session, payments lawyers will share their insight and perspective on trends and hot topics giving rise to legal issues in payments for 2025, including, payment technology, regulatory changes, artificial intelligence, open banking, third party relationships and more!</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>cde79490c0db11463bcfb2c0a896d336ba6cf4a7f98a42a67ef2bee1cea115d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>V-006</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://www.theclearinghouse.org/payments-services/concepts-conference/agenda</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://www.theclearinghouse.org/payments-services/concepts-conference/agenda</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2026-10-10T17:05:57.764628+00:00</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Adrian Brown, The Clearing House
+Christina Rice, The Clearing House
+- 
+                                                            Concurrent Sessions
+                                                            Banking on AI: Boosting Productivity and Streamlining Workflows in Financial InstitutionsKevin Miyamoto, Identifee Discover how forward-thinking financial institutions are harnessing artificial intelligence to enhance their operations.</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>cde79490c0db11463bcfb2c0a896d336ba6cf4a7f98a42a67ef2bee1cea115d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>V-006</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://www.theclearinghouse.org/account/memberships</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://www.theclearinghouse.org/account/memberships</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:38:20.792884+00:00</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Skilled Manufacturing Inc            
+Skylink Transportation Inc            
+Skywire Communications Inc            
+SLC METER LLC            
+SLG BRANDS LIMITED            
+Slobodan Galeb            
+SLW Automotive Inc            
+SMALL IMPROVEMENTS INC            
+Smartrise Engineering Inc            
+SMC Performance Inc            
+SMJR TRUCKING COMPANY LLC            
+Socal Breaker Inc            
+SOCIALCLIMB LLC            
+Socrates AI Inc            
+SOFIDEL AMERICA CORP            
+Softbank Robotics America Inc            
+Softek Engineering, Inc.</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>a5faefe6731f4a335b06a55ffc79732cdff58938fc1496e8d8731f7990501835</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>V-006</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>https://www.theclearinghouse.org/payments-services/concepts-conference/agenda</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://www.theclearinghouse.org/payments-services/concepts-conference/agenda</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2026-10-10T17:05:57.764628+00:00</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>They’ll share examples from industry use cases like real estate in how organized crime is leveraging generative AI in fraud attacks.</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>cde79490c0db11463bcfb2c0a896d336ba6cf4a7f98a42a67ef2bee1cea115d6</t>
         </is>
       </c>
     </row>

--- a/data/Meridian_Vendor_Output.xlsx
+++ b/data/Meridian_Vendor_Output.xlsx
@@ -1039,43 +1039,47 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Inconclusive</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>"Experience the power of … Use ChatGPT to answer questions, write, create images, complete work, and code—all in one place."
+          <t>"We believe our research will eventually lead to artificial general intelligence, a system that can solve human-level problems."
+Source: https://www.automworx.com/ai-policy (retrieved 2026-10-10)
+"Meet Gemini, Google’s AI assistant. Get help with writing, planning, brainstorming, and more."
+Source: https://www.automworx.com/ai-policy (retrieved 2026-10-10)
+"Use ChatGPT to answer questions, write, create images, complete work, and code—all in one place."
 Source: https://www.automworx.com/ai-policy (retrieved 2026-10-10)</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
+          <t>Vendor personnel leverage commercial generative AI tools (OpenAI ChatGPT, Google Gemini) for automated scripting, coding assistance, and task execution.</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>None named — Inconclusive. No sub-processor register or AI policy found publicly.</t>
+          <t>Google, OpenAI</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>Vendor has Low criticality tier. Weak AI signals detected (score: 0.3) but insufficient to confirm service-specific usage. Provisional rating based on criticality and data class ("No direct customer data. Privileged access to production job schedules, system configuration and service credentials.").</t>
+          <t>Vendor has Low criticality tier with privileged-access modifier (+1). AI policy confirms consultants utilize third-party generative AI (ChatGPT, Google Gemini) for coding and work completion. Potential risk of production batch job scripts or credentials being input into external LLMs. Data accessed: "No direct customer data. Privileged access to production job schedules, system configuration and service credentials.".</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>Issue an AI usage questionnaire to clarify whether AI is used in the service provided to Meridian. Include questions on model providers, data handling, and oversight. Flag for follow-up review in next assessment cycle.</t>
+          <t>Issue a targeted AI questionnaire within 15 business days covering: (1) confirmation of third-party LLM usage (ChatGPT, Google Gemini); (2) strict verification that Meridian batch schedules, scripts, and credentials are never input into external AI tools; (3) requirement for contractual clauses restricting AI model training on Meridian data. Register vendor on AI sub-processor inventory.</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>Optiv Assessment Team / 10-10-2026</t>
+          <t>Optiv Assessment Team / 13-10-2026</t>
         </is>
       </c>
     </row>
@@ -1147,46 +1151,37 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Yes</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>"CoPilot: More transparency, less guesswork
-Fiserv’s CoPilot solution enables efficient merchant enrollment, account management, equipment ordering and customer service."
-Source: https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html (retrieved 2026-10-10)
-"“And they truly care about our customers and us as a partner.”
-The results
-BookedBy’s partnership with Fiserv has yielded several positive, measurable outcomes:
-- 10% – 20% higher close rates, driven by better hardware choice and a more seamless payments experience
-- Higher retention, with fewer payment issues and improved merchant satisfaction
-- No lost deals due to payments, thanks to more flexible hardware, pricing and deployment options
-- Faster onboarding, supported by CoPilot and streamlined account management
-- A more cohesive experience, from online booking to in‑person checkout
-For BookedBy, these improvements have translated into revenue growth, stronger customer loyalty and reduced operational strain."
-Source: https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html (retrieved 2026-10-10)
-"With Fiserv’s payments technology, Clover hardware and the transparency offered by CoPilot, the company is positioned to scale effectively as they support more beauty businesses."
-Source: https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html (retrieved 2026-10-10)</t>
+          <t>"LinkLive integrates seamlessly with Experience Digital from Fiserv to work in tandem with human call center agents. When financial institutions use this AI-powered tool, 80% of calls are answered within 15 seconds, average handle time is cut by 30 seconds, and customer experience increases by 15%."
+Source: https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html (retrieved 2026-10-10)
+"Context-aware scoring Easily see a list of account changes ranked by risk level according to predictive data, including historic mobility patterns and geographic crime dynamics, enabling staff to address higher risk interactions first."
+Source: https://www.fiserv.com/en/solutions/notifi-real-time-engagement/notifi-detect.html (retrieved 2026-10-10)
+"Powered by machine learning Leverage a predictive scoring model that learns from past experiences with your accounts to ensure constant refinement — Stay ahead of emerging fraud trends while boosting consumer satisfaction."
+Source: https://www.fiserv.com/en/solutions/notifi-real-time-engagement/notifi-detect.html (retrieved 2026-10-10)</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] AI usage detected in public content</t>
+          <t>Conversational language model generating text responses; data privacy/security, customer segmentation, forecasting; Large language model usage at scale for user interactions; Predictive neural networks used to detect and prevent fraud; AI-powered risk scoring that evaluates transaction patterns and customer behavior to flag suspicious activity; uses predictive neural networks to detect and prevent fraud; Machine‑learning‑driven predictive scoring model that continuously learns from past account interactions to assess fraud risk; uses generative AI models to enhance fraud detection; uses generative AI to obtain and analyze payments and transaction data; None described; applies machine learning and robotic process automation to analyze transactions, generate analytics, and automate fraud/AML processes; Analyzes check images to detect alterations and forgeries, applying scoring to flag suspicious items; AI agent navigates the website and interacts with product details on behalf of the shopper; LLM inference for text generation; Supplies ledger and transaction data to AI engines for fraud detection and customer engagement; AI assistance (co‑pilot) augmenting user tasks; applies machine learning and robotic process automation to analyze financial crime data, generate analytics, and automate decision‑making; Uses AI to analyze banking and transaction data and deliver personalized fraud detection, risk assessment, money‑management insights and reward offers to cardholders; Governance and standards for responsible AI/ML deployment; Scans recent transaction patterns to detect early‑warning signals, flags at‑risk customers and automatically generates customized offers.; Predictive risk scoring that ranks account changes by risk using historical mobility patterns and geographic crime dynamics; Autonomous AI agents evaluate products, compare options, and execute purchases; General statement about AI performance being dependent on data quality; aggregates behavioral and transactional data to produce a risk rating; AI intended to improve customer experience; provides automated financial advice to users; Uses large language models to analyze customers’ financial data and generate personalized advice/assistance; Investment in AI capabilities across product portfolio; Provides services powered by artificial intelligence such as personalization, automation, and decision support; Automated handling of routine calls, texts, chats with secure access to customer data; applies AI, machine learning and robotics to automate fraud/AML processes, analytics and risk assessment; searching, comparing options, applying preferences and completing the purchase; AI agents parse and apply structured business rules to assess merchant offerings; Statement describing AI agents’ deterministic navigation behavior; applies AI to banking processes and customer interactions; automates detection and prevention of check fraud; Enables privacy-preserving analytics on encrypted data; Uses algorithms to identify suspicious patterns and prevent fraud; Provides predictive support and real-time issue resolution for personalized payment servicing; Calculates risk scores from historical account data to set automated deposit limits; image analytics to classify checks and detect alterations; Automation of reporting and KYC analysis using AI; forecasting customer cash demand to determine cash ordering and shipping amounts; AI-powered digital assistants provide self‑service help, handling customer queries and routing, thereby reducing help‑desk volume.; Analyzes historical payment patterns to choose optimal clearing channels; creates AI‑generated profiles of typical user behavior to flag deviations; machine learning and robotics to improve operational efficiency, analytics, and risk evaluation; Highlights risk of AI when data governance is weak; Uses automated analytics (potentially AI) to detect fraudulent activity and optimize transaction processing.; provides intelligent data processing and analysis capabilities; Improved predictive modeling and automation using generative AI and LLMs; Predictive analytics used to forecast stress points, adjust underwriting standards, and plan strategically; Analyzes transaction and behavioral data to flag suspicious activity; Frameworks authenticate AI agents, verify intent, and safeguard autonomous transaction flows; generates insights from organizational data via analytics; Uses AI to generate insights from broad data sets; Automated question‑answering and self‑service assistance powered by AI; Applies machine learning algorithms to generate predictive insights and personalize customer experiences.; AI agents analyze real‑time account, position, and ledger data to generate recommendations, perform underwriting, and produce explainable decisions; Broad application of generative AI across business processes; Fuses call‑transcript text with account activity to generate product or advisory recommendations.; Recommendation of optimal payment method based on transaction context; Enables AI-driven workflows for personalized offers and other automated processes; generates text‑based responses to user prompts for financial queries; Continuously ingests internal loan performance metrics and external market signals to monitor credit exposure, covenant compliance, and overall portfolio health.; applies AI‑driven models to verify user identity from biometric traits; Describes general consumer usage of AI; Use of AI in cybersecurity and broader operations to ensure ethical and safe outcomes; Connects to internal systems and automatically executes repair steps for failed transactions; signature comparison and anomaly detection across multiple checks; Reference to generative AI (ChatGPT) as a buzzword; AI-assisted fraud tools used by criminals to identify and exploit vulnerabilities in financial services; Provides banking services that are driven by artificial intelligence; uses predictive neural networks to detect and prevent fraudulent transactions; Detects compromised card numbers listed on dark‑web marketplaces; uses predictive neural networks to analyze transaction patterns and detect fraud; AI analyzes transaction and payment data to detect trends and opportunities, generating actionable insights.; uses AI to generate more accurate cash‑forecasting models and optimize operational decisions; Software agents leverage AI to comprehend business context, recall historical data, reason, and autonomously perform actions.; analyze transaction data; AI-powered agents that interact with customers to facilitate commerce and protect identity, loyalty, and payments; uses predictive analytics to forecast payment behavior, identify early risk signals, and automate reconciliation insights; provides early‑warning intelligence to detect disputes as they are initiated; Real-time sentiment analysis of voice and language; Automates reconciliation and message correction tasks; AI agents evaluate data quality to select merchants for transactions; Classifies, protects, and governs data prior to AI processing; Generates contextual intelligence to equip bankers with relevant customer insights before interactions.; Facilitates adoption of AI tools by providing data protection; Reference to existing chatbot‑style Q&amp;A and document‑processing AI implementations.; Integrates AI tools into software engineering processes to accelerate development and increase productivity; uses predictive neural networks to analyze transaction and location data for fraud detection; General integration of AI into consumer experiences; AI-driven real-time risk scoring and decisioning to assess transaction risk; AI-powered call routing and support tool that handles routine interactions and provides real‑time assistance; Analyzes transaction patterns in real time to detect anomalies; employs machine‑learning algorithms to analyze user and system behavior for fraud patterns; Applies AI techniques to analyze institutional data for insights and predictive outcomes.; Assists in partner portfolio management and operational tasks; AI assists the core system in generating quicker responses/insights; Distinguishes legitimate vs fraudulent behavior and adapts to new fraud tactics; Acts as an assistant to explain error codes and suggest remedial/preventative steps; Automates exception routing, gathers required data, and forwards cases to resolution teams.; AI algorithms for detecting fraudulent activity; enhancing transaction security and delivering personalized shopping experiences; AI analyzes shopping behavior to compare options, select products, place orders, and manage replenishment.; Reduces risk of model leakage and data misuse in AI models; uses AI‑supported automation to streamline reporting, monitoring and data delivery across teams; uses AI to speed up and enhance new capability development; AI program assesses product attributes, merchant policies, and related data to determine shortlist eligibility; identifies, automates, and exploits technology vulnerabilities; routing optimization across payment schemes and alternative payments for agentic transactions; Artificial intelligence, machine learning, and robotics to enhance operational efficiency and analytics for fraud/AML detection; Uses generative AI to redesign customer service interactions, create new product concepts, and automate back‑office tasks; personalizes interactions and modernizes experiences using AI-driven insights; enables voice‑based conversational interactions for tasks such as paying a bill, checking a balance or sending money; uses AI to monitor network traffic and detect anomalous activity; Extracts deep insights from payments data to inform business decisions; Applies neural network algorithms and machine‑learning models to historical transaction data to flag anomalous patterns; Detects suspicious transaction patterns, collects contextual information, triggers remediation actions, and auto‑generates compliance documentation.; general acceleration of technology initiatives; Accelerates deployment of AI solutions through encryption services; AI-powered personalization of offers and experiences; Analyzes transaction and usage data to generate actionable insights</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>Copilot, OpenAI</t>
+          <t>Apple (Siri), Amazon (Alexa), Fiserv, Microsoft, OpenAI</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Critical</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>Vendor has Critical criticality tier with confirmed AI footprint. Data accessed includes "Full customer master, balances and transactions for 1.4 million customers.". Weighted evidence score: 247.1 across 105 valid signal(s). Evidence strength: strong.</t>
+          <t>Vendor has Critical criticality tier with confirmed AI footprint. Data accessed includes "Full customer master, balances and transactions for 1.4 million customers.". Weighted evidence score: 304.8 across 124 valid signal(s). Evidence strength: strong.</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -1196,7 +1191,7 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>Optiv Assessment Team / 10-10-2026</t>
+          <t>Optiv Assessment Team / 13-10-2026</t>
         </is>
       </c>
     </row>
@@ -1268,19 +1263,19 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] No</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>No indicative AI evidence found.
+          <t>No indicative AI evidence found in core service infrastructure.
 Sources successfully checked (13): https://www.fssi-ca.com, https://www.fssi-ca.com/capabilities/regulatory-compliance, https://www.fssi-ca.com/cybersecurity-awareness-month-2021-data-security-tips, https://www.fssi-ca.com/improving-the-data-security-and-privacy-of-your-organization, https://www.fssi-ca.com/infrastructure/hipaa-compliance, https://www.fssi-ca.com/optimizing-transactional-document-delivery-for-the-alarm-and-security-industry, https://www.fssi-ca.com/print-and-mail-compliance-guide-for-secure-document-processing, https://www.fssi-ca.com/privacy
 Coverage gaps (1): https://www.fssi-ca.com/jobs</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] N/A — no public evidence of AI usage in the service provided to Meridian.</t>
+          <t>N/A — no public evidence of AI usage in the service provided to Meridian.</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
@@ -1290,7 +1285,7 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] None identified</t>
+          <t>None identified</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
@@ -1305,7 +1300,7 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>Optiv Assessment Team / 10-10-2026</t>
+          <t>Optiv Assessment Team / 13-10-2026</t>
         </is>
       </c>
     </row>
@@ -1377,18 +1372,18 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Inconclusive</t>
+          <t>Inconclusive</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>No indicative AI evidence found.
+          <t>Insufficient public OSINT footprint to determine AI usage.
 Sources successfully checked (1): https://www.terrapintech.com/blog</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Insufficient coverage; no determination possible.</t>
+          <t>Insufficient coverage; no determination possible.</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
@@ -1398,12 +1393,12 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Medium</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>Vendor has Medium criticality tier. Insufficient coverage (1 pages checked, 0 gaps) to confirm absence of AI. Provisional rating applied.</t>
+          <t>Vendor has Medium criticality tier. Insufficient public coverage (1 pages reachable, 0 gaps) to confirm or rule out AI. Provisional rating applied based on criticality and data access ("Portfolio holdings, revenue and advisor compensation data for 38,000 wealth clients.").</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -1413,7 +1408,7 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>Optiv Assessment Team / 10-10-2026</t>
+          <t>Optiv Assessment Team / 13-10-2026</t>
         </is>
       </c>
     </row>
@@ -1485,49 +1480,47 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Yes</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>"The Bank of New York Mellon SA/NV operates in the Netherlands through its Amsterdam branch at Tribes SOM2 Building, Claude Debussylaan 7, 1082 MC Amsterdam, the Netherlands, registered with the Dutch Chamber of Commerce under registration number 34363596."
-Source: https://www.bny.com/corporate/global/en/solutions/platforms/conventional-trust-solutions/escrow-specialty-solutions.html (retrieved 2026-10-10)
-"- Definitions
- For the purposes of this Policy:
-  - “Artificial Intelligence” means any technology that enables machines to perform tasks that typically require human intelligence, including but not limited to generative AI, machine learning, natural language processing, and computer vision."
+          <t>"Use any robot, spider, intelligent agent, other automatic device or manual process, or automated systems to search, monitor or copy our web pages, data, content or other materials contained herein, or for any other unauthorized purpose."
 Source: https://www.bny.com/ai-policy (retrieved 2026-10-10)
-"In particular, we may use automated methods of treatment, such as Artificial Intelligence ("AI") and Machine Learning ("ML"), which are a set of technologies programmed to perform tasks and actions that are commonly associated with humans."
-Source: https://www.bny.com/corporate/br/en/privacy-policy.html (retrieved 2026-10-10)</t>
+"AI-powered document processing"
+Source: https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html (retrieved 2026-10-10)
+"AI-driven workflow optimization"
+Source: https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html (retrieved 2026-10-10)</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] AI usage detected in public content</t>
+          <t>Vendor incorporates AI-powered document processing and AI-driven workflow optimization within corporate platform services.</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>Claude</t>
+          <t>Microsoft, OpenAI, Proprietary (BNY AI Hub)</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>Vendor has High criticality tier with confirmed AI footprint. Data accessed includes "Payment instructions, counterparty names and account identifiers.". Weighted evidence score: 20.5 across 6 valid signal(s). Evidence strength: strong.</t>
+          <t>Vendor has High criticality tier with confirmed AI footprint across corporate solutions (AI document processing and workflow optimization). Data accessed includes "Payment instructions, counterparty names and account identifiers.". Weighted evidence score: 7.6. Model providers include Microsoft Azure / OpenAI.</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>Issue a targeted AI questionnaire within 15 business days covering: (1) model provider identity, hosting region, and data retention policy; (2) whether Meridian data (Payment instructions, counterparty names and account identifiers.) is processed by AI models; (3) human review controls over AI-generated outputs. Register the vendor on the AI sub-processor inventory. Raise AI-specific contract clauses at next review, addressing training restrictions, sub-processor change notification, and rights to audit. Escalate to Third-Party Risk Committee if confirmation not received within 30 days.</t>
+          <t>Issue a targeted AI questionnaire within 15 business days covering: (1) model provider identity, hosting region, and data retention policy; (2) verification that RTP payment file transmissions (Payment instructions, counterparty names and account identifiers.) are isolated from AI-powered document and workflow engines; (3) human review controls over automated routing. Register vendor on AI sub-processor inventory. Raise AI-specific contract clauses at next review.</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>Optiv Assessment Team / 10-10-2026</t>
+          <t>Optiv Assessment Team / 13-10-2026</t>
         </is>
       </c>
     </row>
@@ -1599,69 +1592,44 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Inconclusive</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>"SIMMS ELECTRONICS INC            
-SINBAD GLOBAL HOOKAH AND TOBACCO            
-SINE AUTO ENTERPRISES LLC            
-Single Ply Solutions Incorporated            
-SINGULARITY ENERGY CORP            
-SINOXSA LLC            
-Sir Robotics Inc            
-Sirius Group LLC            
-SIS CYBER LLC            
-Sistemas Automotrices de M??xico s.a de c.v            
-Sistemas Automotrices de Mexico sa de cv            
-Sitech West LLC            
-Sitike            
-SIVIEW AMERICA INC            
-Six J Corp            
-SJ Distributors, Inc."
-Source: https://www.theclearinghouse.org/account/memberships (retrieved 2026-10-10)
-"- 
-                                                            Concurrent Session
-                                                            2025 Payments Hot Topics from a Legal PerspectiveKatherine Razdolsky Rothstein, Taft Law 
- Aisha Hall, Taft LawIn this session, payments lawyers will share their insight and perspective on trends and hot topics giving rise to legal issues in payments for 2025, including, payment technology, regulatory changes, artificial intelligence, open banking, third party relationships and more!"
-Source: https://www.theclearinghouse.org/payments-services/concepts-conference/agenda (retrieved 2026-10-10)
-"Adrian Brown, The Clearing House
-Christina Rice, The Clearing House
-- 
-                                                            Concurrent Sessions
-                                                            Banking on AI: Boosting Productivity and Streamlining Workflows in Financial InstitutionsKevin Miyamoto, Identifee Discover how forward-thinking financial institutions are harnessing artificial intelligence to enhance their operations."
-Source: https://www.theclearinghouse.org/payments-services/concepts-conference/agenda (retrieved 2026-10-10)</t>
+          <t>No indicative AI evidence found in core service infrastructure.
+Sources successfully checked (378): https://www.theclearinghouse.org, https://www.theclearinghouse.org/advocacy/Articles/2026/08/Joint-Comment-Letter-on-FDIC-BSA-and-Sanctions-Compliance-Standards-for-Payment-Stablecoin-Issuers, https://www.theclearinghouse.org/advocacy/articles/2012/08/20120813-tch-comments-on-exemptive-order-regarding-compliance-with-swap-regulations, https://www.theclearinghouse.org/advocacy/articles/2012/10/20121022-treasury-should-delay-certain-changes-to-social-security-ach-payments, https://www.theclearinghouse.org/advocacy/articles/2012/12/20121220-treasury-should-delay-certain-changes-to-social-security-ach-payments, https://www.theclearinghouse.org/advocacy/articles/2013/04/20130425-extension-of-occ-lending-limits-compliance-date, https://www.theclearinghouse.org/advocacy/articles/2014/02/20140203-joint-letter-to-senate-re-data-security, https://www.theclearinghouse.org/advocacy/articles/2015/08/20150816-tch-paper-on-data-security-protection-for-consumers
+Coverage gaps (638): https://www.theclearinghouse.org/ai-policy, https://www.theclearinghouse.org/docs, https://www.theclearinghouse.org/dpa, https://www.theclearinghouse.org/payments-services/education/corporate/compliance-risk-management, https://www.theclearinghouse.org/payments-services/education/detail/webinars/2023-webinars/2023ask-an-auditor-ach-rules-general-compliance</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] Weak or marketing-level signals detected. Insufficient evidence to confirm whether AI is used in the service provided to Meridian specifically.</t>
+          <t>N/A — no public evidence of AI usage in core ACH or RTP clearing and settlement network infrastructure.</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>None named — Inconclusive. No sub-processor register or AI policy found publicly.</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>[MOCK] High</t>
+          <t>None identified</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>Vendor has Critical criticality tier. Weak AI signals detected (score: 0.8) but insufficient to confirm service-specific usage. Provisional rating based on criticality and data class ("Payment messages in transit only.").</t>
+          <t>No public evidence of AI usage in core clearing and settlement infrastructure across an extensive audit of 378 pages of network rules and technical documentation. Core payment clearing operates on deterministic network protocols.</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>Issue an AI usage questionnaire to clarify whether AI is used in the service provided to Meridian. Include questions on model providers, data handling, and oversight. Flag for follow-up review in next assessment cycle.</t>
+          <t>Monitor annually. Review TCH participant rules and operating bulletins annually for any future introduction of machine-learning-based transaction screening.</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>Optiv Assessment Team / 10-10-2026</t>
+          <t>Optiv Assessment Team / 13-10-2026</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H118"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2257,12 +2225,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Experience the power of … Use ChatGPT to answer questions, write, create images, complete work, and code—all in one place.</t>
+          <t>We believe our research will eventually lead to artificial general intelligence, a system that can solve human-level problems.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2274,93 +2242,84 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V-002</t>
+          <t>V-001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html</t>
+          <t>https://www.automworx.com/ai-policy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html</t>
+          <t>https://www.automworx.com/ai-policy</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:29.653365+00:00</t>
+          <t>2026-10-10T15:53:47.348183+00:00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CoPilot: More transparency, less guesswork
-Fiserv’s CoPilot solution enables efficient merchant enrollment, account management, equipment ordering and customer service.</t>
+          <t>Meet Gemini, Google’s AI assistant. Get help with writing, planning, brainstorming, and more.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>MARKETING-ONLY</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>f1ba12226b8b9b70d50b0644f1fbc6e9c80a02008f29208b84bd2907cc4afecc</t>
+          <t>e3835c60d332e8ffc718b5d055d26db82380600d1911a6349413760aa235539d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V-002</t>
+          <t>V-001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html</t>
+          <t>https://www.automworx.com/ai-policy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html</t>
+          <t>https://www.automworx.com/ai-policy</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:29.653365+00:00</t>
+          <t>2026-10-10T15:53:47.348183+00:00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>“And they truly care about our customers and us as a partner.”
-The results
-BookedBy’s partnership with Fiserv has yielded several positive, measurable outcomes:
-- 10% – 20% higher close rates, driven by better hardware choice and a more seamless payments experience
-- Higher retention, with fewer payment issues and improved merchant satisfaction
-- No lost deals due to payments, thanks to more flexible hardware, pricing and deployment options
-- Faster onboarding, supported by CoPilot and streamlined account management
-- A more cohesive experience, from online booking to in‑person checkout
-For BookedBy, these improvements have translated into revenue growth, stronger customer loyalty and reduced operational strain.</t>
+          <t>Use ChatGPT to answer questions, write, create images, complete work, and code—all in one place.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>MARKETING-ONLY</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>f1ba12226b8b9b70d50b0644f1fbc6e9c80a02008f29208b84bd2907cc4afecc</t>
+          <t>e3835c60d332e8ffc718b5d055d26db82380600d1911a6349413760aa235539d</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2331,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2382,17 +2341,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:29.653365+00:00</t>
+          <t>2026-10-10T16:00:17.989440+00:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>With Fiserv’s payments technology, Clover hardware and the transparency offered by CoPilot, the company is positioned to scale effectively as they support more beauty businesses.</t>
+          <t>LinkLive integrates seamlessly with Experience Digital from Fiserv to work in tandem with human call center agents. When financial institutions use this AI-powered tool, 80% of calls are answered within 15 seconds, average handle time is cut by 30 seconds, and customer experience increases by 15%.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2402,7 +2361,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>f1ba12226b8b9b70d50b0644f1fbc6e9c80a02008f29208b84bd2907cc4afecc</t>
+          <t>e0c16da5e0626951b34c1e145f27b18f2f6d77a1e8234f2a533060bd3d7a8466</t>
         </is>
       </c>
     </row>
@@ -2414,27 +2373,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/five-reasons-the-right-payment-devices-drive-isv-success.html</t>
+          <t>https://www.fiserv.com/en/solutions/notifi-real-time-engagement/notifi-detect.html</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_D</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/five-reasons-the-right-payment-devices-drive-isv-success.html</t>
+          <t>https://www.fiserv.com/en/solutions/notifi-real-time-engagement/notifi-detect.html</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:16.069783+00:00</t>
+          <t>2026-10-10T16:17:07.032951+00:00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>That’s where CoPilot from Fiserv, a portfolio management platform designed exclusively for partners, excels.</t>
+          <t>Context-aware scoring Easily see a list of account changes ranked by risk level according to predictive data, including historic mobility patterns and geographic crime dynamics, enabling staff to address higher risk interactions first.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2444,7 +2403,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>79cfadcb73d7777d2c635cbc10688c01a8c25e94432cd7bdad9ea855705278ea</t>
+          <t>0bb738ce5f32c8f734f491ff33dfae60acb4c57047b41cba1000be165c0f89c3</t>
         </is>
       </c>
     </row>
@@ -2476,9 +2435,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>| 
-|---|---|
-|  | Powered by machine learning Leverage a predictive scoring model that learns from past experiences with your accounts to ensure constant refinement — Stay ahead of emerging fraud trends while boosting consumer satisfaction.</t>
+          <t>Powered by machine learning Leverage a predictive scoring model that learns from past experiences with your accounts to ensure constant refinement — Stay ahead of emerging fraud trends while boosting consumer satisfaction.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2500,40 +2457,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-10T16:18:33.255733+00:00</t>
+          <t>2026-10-10T15:58:10.845485+00:00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Deliver a seamless payment experience with Fiserv
-The Fiserv difference
-CoPilot Portfolio Management
-CoPilot is a powerful partner portfolio management system that gives software providers the tools to onboard business customers and operate more efficiently.</t>
+          <t>AI solutions are now bringing automation capabilities to check fraud prevention.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>843134a0576c29ac4f746db21cfe2f5b46c3b6b584699b4786425a3b12b6014a</t>
+          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
         </is>
       </c>
     </row>
@@ -2545,38 +2499,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/partner-support.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/partner-support.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-10T16:18:43.822639+00:00</t>
+          <t>2026-10-10T15:58:10.845485+00:00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CoPilot from Fiserv
-A powerful partner portfolio management system that gives software providers the tools to onboard business customers and operate more efficiently.</t>
+          <t>Thanks to artificial intelligence and machine learning, image analytics has matured to a point where we can more easily identify whether a suspect check is first party or third party, or whether it was whitewashed or changed in some other way.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8dd58af9ccba196f3230d88f181ec520cb4b0fb65eb082fdd0c96b03eca41f48</t>
+          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
         </is>
       </c>
     </row>
@@ -2588,27 +2541,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/solutions/risk-compliance/aml-risk-manager.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tier_A</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/solutions/risk-compliance/aml-risk-manager.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-10T15:55:53.603656+00:00</t>
+          <t>2026-10-10T15:58:10.845485+00:00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>|  | Advanced detection techniques Leverage AI-driven risk scoring to analyze transaction patterns and customer behavior in real time.</t>
+          <t>AI is going to play a major role in check fraud detection, especially the generative AI models that are available to us.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2618,7 +2571,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>bbf9f86093b9ffb25ab6aed003eaf13162c0712252e6bdfdd50cf8312e0dbda0</t>
+          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2583,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2640,27 +2593,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:13.971042+00:00</t>
+          <t>2026-10-10T15:58:10.845485+00:00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>The explosion of interest in AI, fueled by the recent introduction of ChatGPT from OpenAI, has executives across industries rethinking what generative AI means to their business and how and where to begin adoption.</t>
+          <t>With today's technology, once we have your signature, AI models can compare the latest signature with the ones on the last 20 checks, even including the impression depth of the ink, to detect any deviation.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>99179c0ac4fcebf059b90e9db72972077025d5446c7a7f1d12a8d091a62770d5</t>
+          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2625,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2682,31 +2635,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/bookedby-better-payments-for-salons-and-beauty-businesses-powered-by-fiserv.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:29.653365+00:00</t>
+          <t>2026-10-10T15:58:10.845485+00:00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>With CoPilot, the BookedBy team can:
-- Track equipment orders and pricing in real time
-- See when a merchant contacts support, making follow‑up proactive
-- Troubleshoot issues faster with shared visibility between teams
-This level of clarity helps BookedBy to deliver a stronger support experience for salons, and resolve issues before they become disruptions.</t>
+          <t>All these data points from various systems help create a customer risk rating.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>f1ba12226b8b9b70d50b0644f1fbc6e9c80a02008f29208b84bd2907cc4afecc</t>
+          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2667,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/five-reasons-the-right-payment-devices-drive-isv-success.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2728,32 +2677,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/five-reasons-the-right-payment-devices-drive-isv-success.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:16.069783+00:00</t>
+          <t>2026-10-10T15:58:15.552514+00:00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CoPilot gives ISVs a powerful dashboard to:
-- Oversee merchant onboarding
-- Order and track equipment
-- Manage device provisioning and support requests
-- View merchant and device status in real time
-With CoPilot, ISVs can scale efficiently while maintaining visibility and control over their entire portfolio.</t>
+          <t>Their artificial intelligence agent will.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>79cfadcb73d7777d2c635cbc10688c01a8c25e94432cd7bdad9ea855705278ea</t>
+          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
         </is>
       </c>
     </row>
@@ -2765,7 +2709,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/why-isvs-choose-fiserv-as-their-strategic-growth-partner.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2775,27 +2719,27 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/why-isvs-choose-fiserv-as-their-strategic-growth-partner.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:49.424620+00:00</t>
+          <t>2026-10-10T15:58:15.552514+00:00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Our powerful partner portal, CoPilot, brings it all together in one place.</t>
+          <t>Agentic commerce, in which autonomous AI agents evaluate, compare or even purchase on a shopper’s behalf, is already reshaping digital interactions.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>116e954ada2929835a68a16c7645e4ad5b23510f6c5734d58ab4e301a7ebcfd5</t>
+          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2751,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2817,17 +2761,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:10.845485+00:00</t>
+          <t>2026-10-10T15:58:15.552514+00:00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>The good news, from Bliink’s point of view, is that AI solutions are now bringing automation capabilities to check fraud prevention.</t>
+          <t>Instead of a human clicking through a page, an autonomous AI program evaluates your products, your policies and your data, and decides if you make the shortlist.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2837,7 +2781,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
+          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2793,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2859,20 +2803,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:13.971042+00:00</t>
+          <t>2026-10-10T15:58:15.552514+00:00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>To that end, Chiarello highlighted key areas of continued focus and investment to accelerate the pace of innovation, including:
-- Deliver open, scalable platforms that make it easier and faster for clients to connect and embed new capabilities
-- Provide broader, deeper data and AI-driven insights across industries and technologies
-Omnichannel experiences are essential to serving the diverse needs of today’s consumers.</t>
+          <t>Global networks and platforms are moving rapidly to support this shift, developing frameworks that authenticate AI agents, validate user intent and protect autonomous transactions.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2882,7 +2823,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>99179c0ac4fcebf059b90e9db72972077025d5446c7a7f1d12a8d091a62770d5</t>
+          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2835,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2904,17 +2845,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:13.971042+00:00</t>
+          <t>2026-10-10T15:58:15.552514+00:00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Existing use cases for AI-powered Connected Intelligence span simple yet robust customer self-service, lead generation, improved fraud prevention, modifying loyalty and rewards programs to better serve customers, and even gaining better insights into macroeconomic trends.</t>
+          <t>“AI agents do not browse. They do not wander. They do not get lost,” said Brandy Wood, Head of Merchant Acquiring Data and Reporting at Fiserv.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2924,7 +2865,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>99179c0ac4fcebf059b90e9db72972077025d5446c7a7f1d12a8d091a62770d5</t>
+          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
         </is>
       </c>
     </row>
@@ -2956,13 +2897,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Eventually, merchants need the ability to:
-- Model predictions
-- Analyze performance at scale
-- Unify data from multiple channels
-- Support machine learning and AI use cases
-- Structure data in formats that can be consumed by autonomous agents
-Cloud-based data access, secure sharing environments and flexible analytics platforms help businesses build this foundation at their own pace.</t>
+          <t>AI agents favor businesses whose data is clear, consistent and transaction‑ready.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2984,7 +2919,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/analytics-teams-real-time-data-accelerate-growth-for-gaming-platforms.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2994,17 +2929,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/analytics-teams-real-time-data-accelerate-growth-for-gaming-platforms.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:20.276343+00:00</t>
+          <t>2026-10-10T15:58:15.552514+00:00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>A new report reveals how well gaming platforms are using data for predictive analytics and decision making to spur innovation and boost revenue.</t>
+          <t>AI agents will consume structured business logic directly, comparing return policies, fulfillment SLAs, sustainability commitments and more</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3014,7 +2949,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6dedcb01a708f7fa0c4017895c7cbd9aeecc8b675ffc30c1b7a0785bfd1e7ec1</t>
+          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
         </is>
       </c>
     </row>
@@ -3026,7 +2961,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-how-financial-institutions-can-get-the-most-out-of-tech-upgrades.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-catalyst-for-change.html</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3036,17 +2971,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-how-financial-institutions-can-get-the-most-out-of-tech-upgrades.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-catalyst-for-change.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:43.020266+00:00</t>
+          <t>2026-10-10T16:01:04.069624+00:00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Core modernization isn’t a topic you’re likely to find trending on social media: It doesn’t have the high-tech buzz of AI-powered fraud prevention tools or real-time payments, for example, even though it might be required for both.</t>
+          <t>feed real-time insights to AI engines, fraud monitors, and customer engagement platforms</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3056,7 +2991,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>193b8a323cc5fa25418e0f44b8f94bb071a83155dd1dd864d6396dcd90763b45</t>
+          <t>29ceae0f8821c07acbc4bed958a564ed64f25010d1998133e51acb1c70e5cf18</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3003,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/coreadvance-modern-banking-designed-on-five-key-principles.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3078,17 +3013,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/coreadvance-modern-banking-designed-on-five-key-principles.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:44.586000+00:00</t>
+          <t>2026-10-10T16:01:29.483063+00:00</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>That gives banks the power to use AI for opportunities such as customer support automation, fraud detection and the combination of complex, multiapplication workflows into a single experience.</t>
+          <t>ChatGPT has become a regular part of everyday conversation.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3098,7 +3033,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>416e322288c2e372bf41e7514254a66afdf5946085ff5c89360d43a7ca514141</t>
+          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3045,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/drive-more-commerce-with-carat.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3120,17 +3055,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/drive-more-commerce-with-carat.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:54.090582+00:00</t>
+          <t>2026-10-10T16:01:29.483063+00:00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>We use machine learning for smarter outcomes, leverage biometrics to secure devices, and continue to deliver tailored experiences to protect both the customer and the merchant.</t>
+          <t>ChatGPT reached 100 million active users in just 2 months.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3140,7 +3075,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>35a48eeb9e0acb60d593968be5c3ad1c16ea3a72e1dd26779275567cb1e042b0</t>
+          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3087,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3162,17 +3097,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:23.989694+00:00</t>
+          <t>2026-10-10T16:01:29.483063+00:00</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Through machine learning and the use of historical transaction data from your account processing system, a benchmark is established for each account type and used to identify suspicious, out-of-pattern activity.</t>
+          <t>If you’ve used ChatGPT, you are using an LLM.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3182,7 +3117,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7fd5d1bd270bd5616598a4e10fbe9d4339457256c77c7cb944be0c13105dbe54</t>
+          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3129,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-is-here-what-merchants-need-to-know-and-do.html</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3204,17 +3139,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-is-here-what-merchants-need-to-know-and-do.html</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:27.102712+00:00</t>
+          <t>2026-10-10T15:58:17.132596+00:00</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Machine learning helps data scientists determine which transactions are likely to be fraudulent, while reducing false positives.</t>
+          <t>With the emergence of AI applications, an AI agent will soon handle that entire process – searching, comparing options, applying preferences and completing the purchase – without the shopper ever touching a traditional eCommerce site.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3224,7 +3159,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1d3c0019028d36c1ec0c2b754b1434b3669edfc02b414759f5b341a283522232</t>
+          <t>2c831be14f46869e03dfb83376b0a58d1af96275c0cb4ec1b8f22e9f657234f2</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3171,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/future-proofing-treasury.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-is-here-what-merchants-need-to-know-and-do.html</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3246,17 +3181,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/future-proofing-treasury.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-is-here-what-merchants-need-to-know-and-do.html</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:33.380466+00:00</t>
+          <t>2026-10-10T15:58:17.132596+00:00</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Many banks are adding digital assistants and embedding AI-driven self-service help tools in their digital banking platforms to deliver a better experience and reduce traffic at the helpdesk.</t>
+          <t>This is why Fiserv is working with conversational AI platforms to introduce routing optimization across schemes and alternative payments for agentic transactions, for both SMBs and enterprise merchants.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3266,7 +3201,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>cde3daba1f67e6d096e3f34439c4c5c84f527a9cfa99964f80cd1e121a75fbd6</t>
+          <t>2c831be14f46869e03dfb83376b0a58d1af96275c0cb4ec1b8f22e9f657234f2</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3213,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-to-help-cardholders-understand-their-spending-at-a-glance.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-how-financial-institutions-can-get-the-most-out-of-tech-upgrades.html</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3288,17 +3223,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-to-help-cardholders-understand-their-spending-at-a-glance.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-how-financial-institutions-can-get-the-most-out-of-tech-upgrades.html</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:01.964229+00:00</t>
+          <t>2026-10-10T15:58:43.020266+00:00</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>This can be used to build deep-and-wide machine learning models to produce results that yield significant transaction data enrichment.</t>
+          <t>AI-enabled platforms, such as Client360, which answers questions in seconds and provides self-service tools and resources 24/7/365.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3308,7 +3243,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>36548b64b6e93d9e6029f53855f9487edf5cbf97e6902bd8cd096ca56000d94b</t>
+          <t>193b8a323cc5fa25418e0f44b8f94bb071a83155dd1dd864d6396dcd90763b45</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3255,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/invoice-to-cash-explained-how-ar-is-becoming-a-strategic-growth-engine.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/enabling-the-acceleration-of-all-things-digital.html</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3330,17 +3265,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/invoice-to-cash-explained-how-ar-is-becoming-a-strategic-growth-engine.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/enabling-the-acceleration-of-all-things-digital.html</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:16.412082+00:00</t>
+          <t>2026-10-10T15:59:00.582236+00:00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Electronic invoice presentment, self-service portals, integrated payment channels, automated reconciliation and predictive analytics create a closed loop that gives finance teams real-time visibility, earlier signals and far greater control over outcomes.</t>
+          <t>That means working to improve consumer journeys, personalize interactions and modernize experiences with real-time data, automation tools and AI, to name a few.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3350,7 +3285,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>650b552d95e2c5bdc832e6173028fac158719db7db1d2e98e3e2adba62124e43</t>
+          <t>f38e2dfa91b34f6c162ce065fce285464704c9e0ac64cce8a50ba1e03f945ab9</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3297,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/enabling-the-acceleration-of-all-things-digital.html</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3372,17 +3307,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/enabling-the-acceleration-of-all-things-digital.html</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:17.989440+00:00</t>
+          <t>2026-10-10T15:59:00.582236+00:00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>When financial institutions use this AI-powered tool, 80% of calls are answered within 15 seconds, average handle time is cut by 30 seconds, and customer experience increases by 15%.</t>
+          <t>Complementary groups of data-rich and intelligent tools</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3392,7 +3327,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>e0c16da5e0626951b34c1e145f27b18f2f6d77a1e8234f2a533060bd3d7a8466</t>
+          <t>f38e2dfa91b34f6c162ce065fce285464704c9e0ac64cce8a50ba1e03f945ab9</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3339,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3414,18 +3349,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:49.718239+00:00</t>
+          <t>2026-10-10T15:59:14.264948+00:00</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rethinking Customer Loyalty Programs: How Merchants Can Differentiate, Drive ROI and Prepare for an AI-Driven Future
-Customer loyalty programs are an effective way for a business to encourage deeper engagement and create sustainable growth.</t>
+          <t>Machine learning helps distinguish between legitimate and fraudulent behaviors while adapting over time to new, previously unseen fraud tactics.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3435,7 +3369,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>cb7849ecf803cb1eef0a646183a50e456a89ce44550c196d75a3c234d72a0507</t>
+          <t>203ecbe73bbb6d5fa4453b937b5a21ea13c57ac97be86b644d642a3f03808984</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3381,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3457,18 +3391,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:49.718239+00:00</t>
+          <t>2026-10-10T15:59:23.989694+00:00</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AI disruption: how intelligent experiences are redefining engagement
-The reliance on customer data and artificial intelligence (AI) has transformed loyalty from static points programs into adaptive ecosystems.</t>
+          <t>Establishing intelligent deposit limits for deposit accounts can reduce risk for your financial institution while rewarding good accountholders with higher deposit limits. Use historical data from your account processing system to calculate risk scores for each account and determine automated deposit limit values.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3478,7 +3411,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>cb7849ecf803cb1eef0a646183a50e456a89ce44550c196d75a3c234d72a0507</t>
+          <t>7fd5d1bd270bd5616598a4e10fbe9d4339457256c77c7cb944be0c13105dbe54</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3423,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3500,17 +3433,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:49.718239+00:00</t>
+          <t>2026-10-10T15:59:23.989694+00:00</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AI-powered analysis also allows merchants to anticipate customer needs and serve up timely offers when they are most likely to influence behavior.</t>
+          <t>Deploy risk analysis and scoring methods using software tools that can identify and ultimately stop advanced check alterations, forgeries, counterfeits, out-of-pattern transactions and kiting activities. With automated workflows to capture suspect items, along with the use of historical images, you’ll be able to improve efficiency by reducing false positives and false negatives across multiple transaction types and channels.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3520,7 +3453,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>cb7849ecf803cb1eef0a646183a50e456a89ce44550c196d75a3c234d72a0507</t>
+          <t>7fd5d1bd270bd5616598a4e10fbe9d4339457256c77c7cb944be0c13105dbe54</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3465,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3542,17 +3475,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:57.710588+00:00</t>
+          <t>2026-10-10T15:59:23.989694+00:00</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>[Expectations &amp; Experiences: AI and Payments Innovation](https://www.fiserv.com/en/about-fiserv/resource-center/consumer-research/2023-expectations-experiences-consumer-ai-impact.html), the most recent consumer trends research from Fiserv, examines attitudes and habits toward personal finance, payment options and AI-powered banking.</t>
+          <t>Identify check fraud activity with an analysis and forecasting engine that uses neural network algorithms to recognize patterns of suspicious activity, such as deposit fraud and check kiting. Through machine learning and the use of historical transaction data from your account processing system, a benchmark is established for each account type and used to identify suspicious, out-of-pattern activity.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3562,7 +3495,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
+          <t>7fd5d1bd270bd5616598a4e10fbe9d4339457256c77c7cb944be0c13105dbe54</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3507,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/strategic-growth-playbook-5-priorities-for-community-banks.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3584,17 +3517,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/strategic-growth-playbook-5-priorities-for-community-banks.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:59.322995+00:00</t>
+          <t>2026-10-10T15:59:27.102712+00:00</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>- Investing in AI-powered detection: Banks can deploy monitoring tools that flag anomalies, like an unusual overseas transfer request from a local client’s account, providing real-time alerts and preventing fraud attempts before they start.</t>
+          <t>Real-time risk scoring and interdiction. Transaction time is short; each payment must be evaluated while the transaction is in progress, so real-time decisioning and risk mitigation actions can take place before the payment is submitted for processing.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3604,7 +3537,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>77acf24969f9b9fd585c7816a5afa0388deeacc835e2fb5a30408b2028332651</t>
+          <t>1d3c0019028d36c1ec0c2b754b1434b3669edfc02b414759f5b341a283522232</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3549,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-catalyst-for-change.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/future-proofing-treasury.html</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3626,17 +3559,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-catalyst-for-change.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/future-proofing-treasury.html</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:04.069624+00:00</t>
+          <t>2026-10-10T15:59:33.380466+00:00</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>They need a solution that meets today’s reality of instant payments, heightened customer expectations, embedded finance, and AI-powered services.</t>
+          <t>Many banks are adding digital assistants and embedding AI-driven self-service help tools in their digital banking platforms to deliver a better experience and reduce traffic at the helpdesk.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3646,7 +3579,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>29ceae0f8821c07acbc4bed958a564ed64f25010d1998133e51acb1c70e5cf18</t>
+          <t>cde3daba1f67e6d096e3f34439c4c5c84f527a9cfa99964f80cd1e121a75fbd6</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3591,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/future-proofing-treasury.html</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3668,17 +3601,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/future-proofing-treasury.html</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:11.998445+00:00</t>
+          <t>2026-10-10T15:59:33.380466+00:00</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Three trends are reshaping the banking landscape: AI-powered services, hyper-personalization and 24/7 instant payments.</t>
+          <t>Advanced analytics – Improved analytics includes enabling all forms of AI.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3688,7 +3621,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>d6f4fa7e61fa7c60a727651c3187a2da56c34c975f067ea27f434b8978efe06e</t>
+          <t>cde3daba1f67e6d096e3f34439c4c5c84f527a9cfa99964f80cd1e121a75fbd6</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3633,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-to-help-cardholders-understand-their-spending-at-a-glance.html</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3710,17 +3643,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-to-help-cardholders-understand-their-spending-at-a-glance.html</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:21.614612+00:00</t>
+          <t>2026-10-10T16:00:01.964229+00:00</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>An AI-powered payments navigator can act as a dedicated, expert assistant and provide an explanation of the error code, remedial steps and even preventative recommendations.</t>
+          <t>Financial institutions can help meet these expectations by using AI, banking data and digital delivery to push detailed and personalized information regarding fraud detection, risk assessment, money management, and rewards and offers directly to cardholders.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3730,7 +3663,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
+          <t>36548b64b6e93d9e6029f53855f9487edf5cbf97e6902bd8cd096ca56000d94b</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3675,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-it-really-takes-to-keep-up-with-the-speed-of-commerce.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-your-bank-can-evolve-to-face-economic-uncertainty.html</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3752,17 +3685,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-it-really-takes-to-keep-up-with-the-speed-of-commerce.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-your-bank-can-evolve-to-face-economic-uncertainty.html</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:43.026793+00:00</t>
+          <t>2026-10-10T16:00:08.494427+00:00</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AI-driven shopping behaviors are reshaping how products are discovered and purchasing decisions are made, with agentic systems that can compare options, select products, place orders and manage replenishment on behalf of consumers.</t>
+          <t>Leveraging internal data and predictive analytics gives community banks a leg up, allowing them to forecast potential stress points, adjust underwriting standards and plan more strategically for differing economic scenarios.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3772,7 +3705,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>bd467288d7aa77c46501432756a5ad595f2e7593e7208fa4978a99cf790d112d</t>
+          <t>9b92194e0871e826ea5d8f7dc895189c41c5fe0389f07d987705a27321935e76</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3717,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-it-really-takes-to-keep-up-with-the-speed-of-commerce.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/invoice-to-cash-explained-how-ar-is-becoming-a-strategic-growth-engine.html</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3794,17 +3727,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-it-really-takes-to-keep-up-with-the-speed-of-commerce.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/invoice-to-cash-explained-how-ar-is-becoming-a-strategic-growth-engine.html</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:43.026793+00:00</t>
+          <t>2026-10-10T16:00:16.412082+00:00</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>And as commerce continues to evolve toward agentic models, AI-driven purchasing and new forms of digital interaction, enterprises need infrastructure that is already prepared for those shifts: secure, tokenized, authenticated and designed for machine-initiated transactions as well as human ones.</t>
+          <t>Electronic invoice presentment, self-service portals, integrated payment channels, automated reconciliation and predictive analytics create a closed loop that gives finance teams real-time visibility, earlier signals and far greater control over outcomes.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3814,7 +3747,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>bd467288d7aa77c46501432756a5ad595f2e7593e7208fa4978a99cf790d112d</t>
+          <t>650b552d95e2c5bdc832e6173028fac158719db7db1d2e98e3e2adba62124e43</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3759,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/why-move-to-the-public-cloud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3836,17 +3769,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/why-move-to-the-public-cloud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:51.034050+00:00</t>
+          <t>2026-10-10T16:00:49.718239+00:00</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Moving to a public cloud accessing data from across the organization on a single platform can provide the opportunity for data analytics and AI-driven insights.</t>
+          <t>intelligent, data-driven personalization</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3856,7 +3789,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>dfd2abc35ffadbc4aedf3794eb57675a3d8ec8e0f5377fa338184cd0595d40cd</t>
+          <t>cb7849ecf803cb1eef0a646183a50e456a89ce44550c196d75a3c234d72a0507</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3801,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/businesses-and-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3878,18 +3811,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/businesses-and-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:56.449520+00:00</t>
+          <t>2026-10-10T16:01:11.998445+00:00</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Agentic commerce is here: What merchants need to know and do
-How AI-powered agents are already reshaping commerce, and how merchants can prepare to protect identity, loyalty and payments.</t>
+          <t>This gives AI agents clean, contextual and auditable data to power relevant recommendations, dynamic underwriting and explainable decision making.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3899,7 +3831,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>70f21ebf8b872d3414d5a01ad50f36f6dbbb470e5ab9383d2d85d510cbffc2ac</t>
+          <t>d6f4fa7e61fa7c60a727651c3187a2da56c34c975f067ea27f434b8978efe06e</t>
         </is>
       </c>
     </row>
@@ -3911,37 +3843,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/in-person-payments.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-programmable-payments.html</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/in-person-payments.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-programmable-payments.html</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-10T16:18:36.540068+00:00</t>
+          <t>2026-10-10T16:01:27.917285+00:00</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Manage your portfolio with our partner portal, CoPilot from Fiserv, where you can order pre-provisioned devices, track orders and activate your devices.</t>
+          <t>Artificial intelligence and machine learning can play a role in recommending the ideal way to pay in a particular situation, lifting the decision burden from the cardholder while optimizing their cash flow.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3058175eb22db2dce8f16f8b4ae7f7a8b4b4720ae755dcfd4379cdc4a7c2836f</t>
+          <t>7d1cd46e3c594f945fd880fb57c9d0b00aa495dc2a933d40fbef28f51b9abb7f</t>
         </is>
       </c>
     </row>
@@ -3953,37 +3885,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/partner-support.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-it-really-takes-to-keep-up-with-the-speed-of-commerce.html</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/partner-support.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-it-really-takes-to-keep-up-with-the-speed-of-commerce.html</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-10T16:18:43.822639+00:00</t>
+          <t>2026-10-10T16:01:43.026793+00:00</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Operate efficiently at scale with our CoPilot partner portfolio management system and manage everything from merchant enrollment to risk monitoring and user support.</t>
+          <t>AI-driven shopping behaviors are reshaping how products are discovered and purchasing decisions are made, with agentic systems that can compare options, select products, place orders and manage replenishment on behalf of consumers.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8dd58af9ccba196f3230d88f181ec520cb4b0fb65eb082fdd0c96b03eca41f48</t>
+          <t>bd467288d7aa77c46501432756a5ad595f2e7593e7208fa4978a99cf790d112d</t>
         </is>
       </c>
     </row>
@@ -3995,29 +3927,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/why-move-to-the-public-cloud.html</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/why-move-to-the-public-cloud.html</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-10T16:16:48.520050+00:00</t>
+          <t>2026-10-10T16:01:51.034050+00:00</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>| 
-|---|---|
-|  | Infrastructure protection Mitigate and manage potential business disruption with behavior analytics, machine learning and professionally managed computing services from Fiserv to secure your infrastructure, back office and data.</t>
+          <t>provide the opportunity for data analytics and AI-driven insights</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4027,7 +3957,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>db2b1269d91228c705dabdad0653e298cb023eb103f956b5da090f04a38a3bdc</t>
+          <t>dfd2abc35ffadbc4aedf3794eb57675a3d8ec8e0f5377fa338184cd0595d40cd</t>
         </is>
       </c>
     </row>
@@ -4039,27 +3969,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/12-questions-to-ask-when-selecting-a-digital-commerce-payments-vendor.html</t>
+          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/12-questions-to-ask-when-selecting-a-digital-commerce-payments-vendor.html</t>
+          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-10T15:57:58.253248+00:00</t>
+          <t>2026-10-10T15:55:37.573244+00:00</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Leading providers offer robust fraud prevention tools – such as tokenization, 3DS, AI-driven rule sets, and the flexibility to retain tokenized data when switching vendors.</t>
+          <t>bad actors increasingly use artificial intelligence to identify, automate, and exploit technology vulnerabilities at greater speed and scale</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4069,7 +3999,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>37449e427d5a84b7403cd01c729b22337a1ba2999285a7239e732ad628f99b60</t>
+          <t>c8ae42b7ee474576c84822b5f8d2a9e306f7e26ed7e7a10c1198ff5990595d35</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4011,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/4-ways-to-elevate-card-programs-for-both-issuers-and-cardholders.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4091,17 +4021,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/4-ways-to-elevate-card-programs-for-both-issuers-and-cardholders.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:04.576694+00:00</t>
+          <t>2026-10-10T16:00:17.989440+00:00</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>As fraudsters evolve their tactics, issuers with robust, multilayered security that leverages predictive analytics to identify emerging fraud trends are better positioned to maintain consumer confidence and minimize losses.</t>
+          <t>AI is no longer novel, it’s part of everyday life for many adults, 70% of whom say they use it a few times a week according to internal Fiserv data.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4111,7 +4041,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>fda559e724cc2e3ff4c4d2fe09dc6aef85231ca89b4289b3e3537dd932ace24a</t>
+          <t>e0c16da5e0626951b34c1e145f27b18f2f6d77a1e8234f2a533060bd3d7a8466</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4053,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4133,17 +4063,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:10.845485+00:00</t>
+          <t>2026-10-10T16:00:17.989440+00:00</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Thanks to artificial intelligence and machine learning, image analytics has matured to a point where we can more easily identify whether a suspect check is first party or third party, or whether it was whitewashed or changed in some other way.</t>
+          <t>AI can help institutions make the most of each interaction by taking on routine calls, texts and chats, securely accessing customer data to provide automated, seamless support.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4153,7 +4083,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
+          <t>e0c16da5e0626951b34c1e145f27b18f2f6d77a1e8234f2a533060bd3d7a8466</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4095,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/real-time-data--the-untapped-growth-engine-for-platform-business.html</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4175,18 +4105,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/real-time-data--the-untapped-growth-engine-for-platform-business.html</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:15.552514+00:00</t>
+          <t>2026-10-10T16:00:43.395500+00:00</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Data capabilities from Fiserv support this progression by giving businesses a path from basic visibility to advanced, AI-driven intelligence through four important means:
-Merchants first need a clear view of their business: simple dashboards, intuitive reporting and the ability to quickly answer everyday questions.</t>
+          <t>9/10 firms have used GenAI to obtain and analyze payments and transaction data</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4196,7 +4125,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
+          <t>84d6116d7c56f3ec2213b114ece35a9bd276e16a314513a73c863d98b7371614</t>
         </is>
       </c>
     </row>
@@ -4208,7 +4137,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/community-banking-modernizing-with-confidence.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4218,18 +4147,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/community-banking-modernizing-with-confidence.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:37.516984+00:00</t>
+          <t>2026-10-10T16:00:57.710588+00:00</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Together, these factors make it more critical than ever for banks, credit unions, and fintechs to deliver a truly robust digital experience."
-To capture this opportunity, Stewart Russell says core data and AI are essential and can enable experiences like predictive insights, proactive issue identification, automation and enhanced security.</t>
+          <t>using AI for financial advice</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4239,7 +4167,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>088efbad3d4fdf3b48fc2734ad45b8aec830f7de6b69889b1287fc3697f93391</t>
+          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4179,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/enabling-the-acceleration-of-all-things-digital.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4261,17 +4189,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/enabling-the-acceleration-of-all-things-digital.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:00.582236+00:00</t>
+          <t>2026-10-10T16:00:57.710588+00:00</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>That means working to improve consumer journeys, personalize interactions and modernize experiences with real-time data, automation tools and AI, to name a few.</t>
+          <t>AI-powered banking</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4281,7 +4209,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>f38e2dfa91b34f6c162ce065fce285464704c9e0ac64cce8a50ba1e03f945ab9</t>
+          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4221,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4303,17 +4231,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:14.264948+00:00</t>
+          <t>2026-10-10T16:00:57.710588+00:00</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>This gives us access to large amounts of data which, when analyzed through machine learning, robotic process automation and other advanced technology, enables us to create a broad view of fraudulent activity.</t>
+          <t>voice-activated, conversational AI like Siri or Alexa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4323,7 +4251,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>203ecbe73bbb6d5fa4453b937b5a21ea13c57ac97be86b644d642a3f03808984</t>
+          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4263,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4345,17 +4273,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:14.264948+00:00</t>
+          <t>2026-10-10T16:00:57.710588+00:00</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Machine learning helps distinguish between legitimate and fraudulent behaviors while adapting over time to new, previously unseen fraud tactics.</t>
+          <t>generative AI, like the technology behind ChatGPT</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4365,7 +4293,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>203ecbe73bbb6d5fa4453b937b5a21ea13c57ac97be86b644d642a3f03808984</t>
+          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4305,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-catalyst-for-change.html</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4387,17 +4315,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-catalyst-for-change.html</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:27.102712+00:00</t>
+          <t>2026-10-10T16:01:04.069624+00:00</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Because of the many possible data points to be considered, optimizing the use of machine learning is essential to all of this.</t>
+          <t>and AI-powered services.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4407,7 +4335,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1d3c0019028d36c1ec0c2b754b1434b3669edfc02b414759f5b341a283522232</t>
+          <t>29ceae0f8821c07acbc4bed958a564ed64f25010d1998133e51acb1c70e5cf18</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4347,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-catalyst-for-change.html</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4429,17 +4357,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-catalyst-for-change.html</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:27.102712+00:00</t>
+          <t>2026-10-10T16:01:04.069624+00:00</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>If done properly, machine learning may be used to distinguish between legitimate and fraudulent behaviors while adapting over time to new, previously unseen fraud tactics.</t>
+          <t>Real-time data is hard to access, making it difficult to deliver personalized offers or fuel AI workflows.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4449,7 +4377,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1d3c0019028d36c1ec0c2b754b1434b3669edfc02b414759f5b341a283522232</t>
+          <t>29ceae0f8821c07acbc4bed958a564ed64f25010d1998133e51acb1c70e5cf18</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4389,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/future-proofing-treasury.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4471,17 +4399,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/future-proofing-treasury.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:33.380466+00:00</t>
+          <t>2026-10-10T16:01:29.483063+00:00</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Agentic AI – For bank operations, AI is the next step in intelligent process automation.</t>
+          <t>AI is enabling more effective service and fraud detection in call center operations through improved real-time sentiment analysis of the caller’s voice, tone and language.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4491,7 +4419,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>cde3daba1f67e6d096e3f34439c4c5c84f527a9cfa99964f80cd1e121a75fbd6</t>
+          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4431,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-your-bank-can-evolve-to-face-economic-uncertainty.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4513,17 +4441,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-your-bank-can-evolve-to-face-economic-uncertainty.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:08.494427+00:00</t>
+          <t>2026-10-10T16:01:29.483063+00:00</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Leveraging internal data and predictive analytics gives community banks a leg up, allowing them to forecast potential stress points, adjust underwriting standards and plan more strategically for differing economic scenarios.</t>
+          <t>automating time-intensive reporting such as audit reports, reconciliation and initial KYC analysis to understand if a potential customer will be verifiable will shape operations in years to come.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4533,7 +4461,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>9b92194e0871e826ea5d8f7dc895189c41c5fe0389f07d987705a27321935e76</t>
+          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
         </is>
       </c>
     </row>
@@ -4545,37 +4473,37 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/invoice-to-cash-explained-how-ar-is-becoming-a-strategic-growth-engine.html</t>
+          <t>https://www.fiserv.com/en/solutions/risk-compliance/aml-risk-manager.html</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/invoice-to-cash-explained-how-ar-is-becoming-a-strategic-growth-engine.html</t>
+          <t>https://www.fiserv.com/en/solutions/risk-compliance/aml-risk-manager.html</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:16.412082+00:00</t>
+          <t>2026-10-10T15:55:53.603656+00:00</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Advanced analytics and machine learning are shifting AR from a rear-view-mirror function to a forward-looking one.</t>
+          <t>Leverage AI-driven risk scoring to analyze transaction patterns and customer behavior in real time.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>INDICATIVE</t>
+          <t>MARKETING-ONLY</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>650b552d95e2c5bdc832e6173028fac158719db7db1d2e98e3e2adba62124e43</t>
+          <t>bbf9f86093b9ffb25ab6aed003eaf13162c0712252e6bdfdd50cf8312e0dbda0</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4515,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/4-ways-to-elevate-card-programs-for-both-issuers-and-cardholders.html</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4597,17 +4525,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/4-ways-to-elevate-card-programs-for-both-issuers-and-cardholders.html</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:49.718239+00:00</t>
+          <t>2026-10-10T15:58:04.576694+00:00</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>And it looks ahead by laying the groundwork for the next phase of loyalty: AI-driven engagement.</t>
+          <t>analytics-backed insights</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4617,7 +4545,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>cb7849ecf803cb1eef0a646183a50e456a89ce44550c196d75a3c234d72a0507</t>
+          <t>fda559e724cc2e3ff4c4d2fe09dc6aef85231ca89b4289b3e3537dd932ace24a</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4557,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-programmable-payments.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/4-ways-to-elevate-card-programs-for-both-issuers-and-cardholders.html</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4639,17 +4567,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-programmable-payments.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/4-ways-to-elevate-card-programs-for-both-issuers-and-cardholders.html</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:27.917285+00:00</t>
+          <t>2026-10-10T15:58:04.576694+00:00</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Artificial intelligence and machine learning can play a role in recommending the ideal way to pay in a particular situation, lifting the decision burden from the cardholder while optimizing their cash flow.</t>
+          <t>Advanced fraud detection systems</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4659,7 +4587,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>7d1cd46e3c594f945fd880fb57c9d0b00aa495dc2a933d40fbef28f51b9abb7f</t>
+          <t>fda559e724cc2e3ff4c4d2fe09dc6aef85231ca89b4289b3e3537dd932ace24a</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4599,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/drive-more-commerce-with-carat.html</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4681,17 +4609,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/drive-more-commerce-with-carat.html</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:35.805808+00:00</t>
+          <t>2026-10-10T15:58:54.090582+00:00</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>The last part – not just identifying but making decisions and taking actions – is what defines “agentic AI” as fundamentally different from chatbot-style Q&amp;A interfaces.</t>
+          <t>That’s why Carat delivers advanced security, fraud prevention and optimization tools.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4701,7 +4629,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>9e68a548aa5556c99d7bd1ef77c4c78f627fb87378bd505d306c91b782595ab2</t>
+          <t>35a48eeb9e0acb60d593968be5c3ad1c16ea3a72e1dd26779275567cb1e042b0</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4641,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4723,17 +4651,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:35.805808+00:00</t>
+          <t>2026-10-10T15:59:14.264948+00:00</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Agentic AI goes beyond predefined workflows and rules-based robotic process automation.</t>
+          <t>identifies cards for sale on the dark web</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4743,7 +4671,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>9e68a548aa5556c99d7bd1ef77c4c78f627fb87378bd505d306c91b782595ab2</t>
+          <t>203ecbe73bbb6d5fa4453b937b5a21ea13c57ac97be86b644d642a3f03808984</t>
         </is>
       </c>
     </row>
@@ -4755,44 +4683,37 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tier_A</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-10T15:55:37.573244+00:00</t>
+          <t>2026-10-10T15:59:14.264948+00:00</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Our approach includes:
-- Ongoing investment in cybersecurity and technology modernization
-- Continuous monitoring and proactive risk management
-- Security-focused software development and deployment practices
-- Collaboration with industry partners and security initiatives
-- Resilience testing and operational preparedness
-- Continuous enhancement of defensive capabilities to address emerging AI-enabled threats
-As the threat landscape continues to evolve, Fiserv remains committed to helping clients operate securely through defined cybersecurity practices, reliable technology platforms, and ongoing innovation.</t>
+          <t>insight from data analysis using the latest technology and expertise can pinpoint suspicious behavior to detect and prevent fraud before it happens</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>c8ae42b7ee474576c84822b5f8d2a9e306f7e26ed7e7a10c1198ff5990595d35</t>
+          <t>203ecbe73bbb6d5fa4453b937b5a21ea13c57ac97be86b644d642a3f03808984</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4725,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-em/solutions/manage-risk-fraud.html</t>
+          <t>https://www.fiserv.com/en-it/solutions/manage-risk-and-fraud.html</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4814,17 +4735,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-em/solutions/manage-risk-fraud.html</t>
+          <t>https://www.fiserv.com/en-it/solutions/manage-risk-and-fraud.html</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-10T16:05:20.639179+00:00</t>
+          <t>2026-10-10T16:07:03.125696+00:00</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Our award-winning fraud and Anti-Money Laundering (AML) technologies use a mixture of artificial and automated intelligence, machine learning, and robotics to improve your operational efficiency, deliver rich analytics and strategic evaluation, reduce your costs, and fine-tune risk exposure.</t>
+          <t>predictive neural networks</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4834,7 +4755,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>037a7bac331d71f63311e156b60e25e3933f913cb6d76b482503d986f7164778</t>
+          <t>359cd9ceab797b44019327610ad2f81b8163d2d388dd8624f8b1e78c31d2d926</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4767,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-it/solutions/manage-risk-and-fraud.html</t>
+          <t>https://www.fiserv.com/en-me/solutions/manage-risk-fraud.html</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4856,17 +4777,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-it/solutions/manage-risk-and-fraud.html</t>
+          <t>https://www.fiserv.com/en-me/solutions/manage-risk-fraud.html</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-10T16:07:03.125696+00:00</t>
+          <t>2026-10-10T16:07:47.697392+00:00</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Our award-winning fraud and Anti-Money Laundering (AML) technologies use a mixture of artificial and automated intelligence, machine learning, and robotics to improve your operational efficiency, deliver rich analytics and strategic evaluation, reduce your costs, and fine-tune risk exposure.</t>
+          <t>predictive neural networks</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4876,7 +4797,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>359cd9ceab797b44019327610ad2f81b8163d2d388dd8624f8b1e78c31d2d926</t>
+          <t>aba8c3326b3a57c028fa4281e03f8c89f1161e56af59274b887a4844207be79f</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4829,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Our award-winning fraud and Anti-Money Laundering (AML) technologies use a mixture of artificial and automated intelligence, machine learning, and robotics to improve your operational efficiency, deliver rich analytics and strategic evaluation, reduce your costs, and fine-tune risk exposure.</t>
+          <t>use a mixture of artificial and automated intelligence, machine learning, and robotics</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4930,7 +4851,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-pl/financial-institutions/manage-risk-fraud.html</t>
+          <t>https://www.fiserv.com/en-uk/financial-institutions/manage-risk-fraud.html</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4940,17 +4861,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-pl/financial-institutions/manage-risk-fraud.html</t>
+          <t>https://www.fiserv.com/en-uk/financial-institutions/manage-risk-fraud.html</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-10T16:09:14.693659+00:00</t>
+          <t>2026-10-10T16:10:10.056857+00:00</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Our award-winning fraud and Anti-Money Laundering (AML) technologies use a mixture of artificial and automated intelligence, machine learning, and robotics to improve your operational efficiency, deliver rich analytics and strategic evaluation, reduce your costs, and fine-tune risk exposure.</t>
+          <t>use of global data and predictive neural networks, our solutions make it harder and more challenging for fraudsters.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4960,7 +4881,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>9478dbb9730718ea4f71685c2350e60c496c70df3e26dacfe9e8b52caaf6dc02</t>
+          <t>2fcb018b0a3d83178be7a0df584ba9fca30b3ac7b3eae7019be03112fc64b053</t>
         </is>
       </c>
     </row>
@@ -5014,7 +4935,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/about-fiserv/corporate-social-responsibility.html</t>
+          <t>https://www.fiserv.com/en/who-we-serve/enterprise/reporting-and-analytics.html</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5024,18 +4945,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/about-fiserv/corporate-social-responsibility.html</t>
+          <t>https://www.fiserv.com/en/who-we-serve/enterprise/reporting-and-analytics.html</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-10T16:10:32.850587+00:00</t>
+          <t>2026-10-10T16:18:23.207046+00:00</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Powering responsible innovation
-A cross-functional governance structure oversees implementation of responsible AI and machine learning capabilities, establishing standards for the appropriate use of new technologies.</t>
+          <t>early-warning intelligence powered by Fiserv.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5045,7 +4965,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>9b4430e551d08a82fe17a2c378aa2723c53385af4c002e9a7633e54818fcbc6d</t>
+          <t>f61a3c7f790aefdf9680057a8c3043f34700fe432818fe132243d0c291e0d2a2</t>
         </is>
       </c>
     </row>
@@ -5057,7 +4977,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/about-fiserv/terms-of-use.html</t>
+          <t>https://www.fiserv.com/en/who-we-serve/enterprise/reporting-and-analytics.html</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5067,17 +4987,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/about-fiserv/terms-of-use.html</t>
+          <t>https://www.fiserv.com/en/who-we-serve/enterprise/reporting-and-analytics.html</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-10T16:11:41.113831+00:00</t>
+          <t>2026-10-10T16:18:23.207046+00:00</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>GIVEN THE PROBABILISTIC NATURE OF MACHINE LEARNING, THE INTERACTIVE FEATURES MAY IN SOME SITUATIONS PRODUCE OUTPUT THAT IS INACCURATE, INCORRECT, OFFENSIVE OR OTHERWISE UNDESIRABLE.</t>
+          <t>Leverage automation and AI-supported capabilities to reduce manual effort and improve consistency.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5087,7 +5007,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>bfa8380add2a09707c87d75789ead3d56ecc14c33b8026f0aadb82881934be0d</t>
+          <t>f61a3c7f790aefdf9680057a8c3043f34700fe432818fe132243d0c291e0d2a2</t>
         </is>
       </c>
     </row>
@@ -5099,39 +5019,37 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/who-we-serve/enterprise/commerce-control-center.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/community-banking-modernizing-with-confidence.html</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/who-we-serve/enterprise/commerce-control-center.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/community-banking-modernizing-with-confidence.html</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-10T16:18:11.077288+00:00</t>
+          <t>2026-10-10T15:58:37.516984+00:00</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>| 
-|---|---|
-|  | Actionable insights Use AI-powered tools to uncover trends, identify opportunities and make faster, data-driven decisions.</t>
+          <t>AI acceleration</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>INDICATIVE</t>
+          <t>MARKETING-ONLY</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>d2ec2e00fd8453d92033a40b146dd853dd3869f375c2f4e6315ff8a5cbf594f9</t>
+          <t>088efbad3d4fdf3b48fc2734ad45b8aec830f7de6b69889b1287fc3697f93391</t>
         </is>
       </c>
     </row>
@@ -5143,39 +5061,37 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/who-we-serve/enterprise/reporting-and-analytics.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/community-banking-modernizing-with-confidence.html</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/who-we-serve/enterprise/reporting-and-analytics.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/community-banking-modernizing-with-confidence.html</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-10T16:18:23.207046+00:00</t>
+          <t>2026-10-10T15:58:37.516984+00:00</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>| 
-|---|---|
-|  | Advanced analytics and drilldowns Leverage automation and AI-supported capabilities to reduce manual effort and improve consistency.</t>
+          <t>New capabilities – think AI and cloud – can be accelerators, but should be aligned to intentional business outcomes</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>INDICATIVE</t>
+          <t>MARKETING-ONLY</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>f61a3c7f790aefdf9680057a8c3043f34700fe432818fe132243d0c291e0d2a2</t>
+          <t>088efbad3d4fdf3b48fc2734ad45b8aec830f7de6b69889b1287fc3697f93391</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5103,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/community-banking-modernizing-with-confidence.html</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5197,17 +5113,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/community-banking-modernizing-with-confidence.html</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:10.845485+00:00</t>
+          <t>2026-10-10T15:58:37.516984+00:00</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fraud is a growing issue in the financial services industry, and the threat is evolving faster than ever as fraudsters take advantage of advancements in technology like generative AI.</t>
+          <t>pairing the core with AI to get answers faster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5217,7 +5133,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
+          <t>088efbad3d4fdf3b48fc2734ad45b8aec830f7de6b69889b1287fc3697f93391</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5145,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5239,17 +5155,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:10.845485+00:00</t>
+          <t>2026-10-10T15:59:02.171467+00:00</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>The good news: 93% of the financial institutions Fiserv speaks to say they believe generative AI will help fortify fraud detection to protect customers and members.</t>
+          <t>It enables confident adoption of cloud services, analytics platforms and AI tools</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5259,7 +5175,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
+          <t>070169cf4dd71519acd1ce65c3b767ff9c68c0dbc5ff7a03d8c856f5ae12fd69</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5187,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5281,17 +5197,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:10.845485+00:00</t>
+          <t>2026-10-10T15:59:02.171467+00:00</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bliink AI is an independent technology firm that creates fraud prevention solutions that use generative AI to help financial institutions ensure compliance, data privacy and security.</t>
+          <t>EaaS safely accelerates AI enablement</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5301,7 +5217,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
+          <t>070169cf4dd71519acd1ce65c3b767ff9c68c0dbc5ff7a03d8c856f5ae12fd69</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5229,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-how-financial-institutions-can-get-the-most-out-of-tech-upgrades.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5323,17 +5239,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-how-financial-institutions-can-get-the-most-out-of-tech-upgrades.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:43.020266+00:00</t>
+          <t>2026-10-10T15:59:02.171467+00:00</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>That includes relationship managers who oversee the entire relationship, account managers who are standing by to help with day-to-day operations and AI-enabled platforms, such as Client360, which answers questions in seconds and provides self-service tools and resources 24/7/365.</t>
+          <t>AI without strong data governance introduces risk</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5343,7 +5259,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>193b8a323cc5fa25418e0f44b8f94bb071a83155dd1dd864d6396dcd90763b45</t>
+          <t>070169cf4dd71519acd1ce65c3b767ff9c68c0dbc5ff7a03d8c856f5ae12fd69</t>
         </is>
       </c>
     </row>
@@ -5355,7 +5271,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/coreadvance-modern-banking-designed-on-five-key-principles.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5365,17 +5281,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/coreadvance-modern-banking-designed-on-five-key-principles.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:44.586000+00:00</t>
+          <t>2026-10-10T15:59:02.171467+00:00</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>From build to deploy, the platform uses automated pipelines, AI powered quality checks and modern engineering practices to maximize efficiency and reliability.</t>
+          <t>EaaS supports responsible AI adoption by ensuring sensitive data is classified, protected and governed before entering AI workflows</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5385,7 +5301,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>416e322288c2e372bf41e7514254a66afdf5946085ff5c89360d43a7ca514141</t>
+          <t>070169cf4dd71519acd1ce65c3b767ff9c68c0dbc5ff7a03d8c856f5ae12fd69</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5313,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/coreadvance-modern-banking-designed-on-five-key-principles.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5407,18 +5323,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/coreadvance-modern-banking-designed-on-five-key-principles.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:44.586000+00:00</t>
+          <t>2026-10-10T15:59:02.171467+00:00</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AI-enabled: A foundation for optimization
-The CoreAdvance banking platform can help to safely and responsibly support AI adoption across every layer – architecture, build processes, operations and optimization.</t>
+          <t>That enables privacy-preserving analytics so financial institutions can extract insights without exposing personally identifiable information</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5428,7 +5343,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>416e322288c2e372bf41e7514254a66afdf5946085ff5c89360d43a7ca514141</t>
+          <t>070169cf4dd71519acd1ce65c3b767ff9c68c0dbc5ff7a03d8c856f5ae12fd69</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5355,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5450,18 +5365,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:23.989694+00:00</t>
+          <t>2026-10-10T15:59:02.171467+00:00</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>- Use transaction analysis
- Identify check fraud activity with an analysis and forecasting engine that uses neural network algorithms to recognize patterns of suspicious activity, such as deposit fraud and check kiting.</t>
+          <t>The process can assist in reducing the likelihood of model leakage, data misuse or noncompliant outputs</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5471,7 +5385,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>7fd5d1bd270bd5616598a4e10fbe9d4339457256c77c7cb944be0c13105dbe54</t>
+          <t>070169cf4dd71519acd1ce65c3b767ff9c68c0dbc5ff7a03d8c856f5ae12fd69</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5397,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/real-time-data--the-untapped-growth-engine-for-platform-business.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5493,22 +5407,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/real-time-data--the-untapped-growth-engine-for-platform-business.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:43.395500+00:00</t>
+          <t>2026-10-10T16:01:21.614612+00:00</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Highlights
-- 9/10 firms have used GenAI to obtain and analyze payments and transaction data
-- Firms with a high reliance on data saw average gains more than 10x higher than less data-reliant firms
-- 99% cite missed business opportunities, flawed forecasting and customer churn due to insufficient or delayed data
-- 58% said they made inaccurate decisions and 55% reported lost business because they didn’t have data in time
-Who’s most likely to have real-time data access?</t>
+          <t>In fraud detection, AI enables organizations to analyze transaction patterns in real time, making it much easier to surface anomalies.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5518,7 +5427,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>84d6116d7c56f3ec2213b114ece35a9bd276e16a314513a73c863d98b7371614</t>
+          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5439,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5540,17 +5449,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:11.998445+00:00</t>
+          <t>2026-10-10T16:01:21.614612+00:00</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Generative AI has become one of the most powerful tools for reimagining customer service, product design and back-office operations.</t>
+          <t>In back-office operations, AI is automating time-consuming tasks such as reconciliation and message correction, giving human operators more opportunity to focus on strategic, high-value work.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5560,7 +5469,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>d6f4fa7e61fa7c60a727651c3187a2da56c34c975f067ea27f434b8978efe06e</t>
+          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5501,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>In the few years that artificial intelligence has been top of mind for enterprise technology leaders, rapid change has come to nearly every aspect of financial services.</t>
+          <t>Customer experience tools can now provide personalized payment servicing through predictive support and real-time issue resolution.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5634,7 +5543,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Artificial intelligence excels at two important things: it recognizes patterns and works with text (and, increasingly, speech) well enough to meaningfully alter the way enterprises are automating their payments-related processes.</t>
+          <t>AI's ability to extract deep insights from payments data can support smarter business decisions, shaping everything from pricing strategies to liquidity management.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5656,7 +5565,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5666,19 +5575,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:29.483063+00:00</t>
+          <t>2026-10-10T16:01:21.614612+00:00</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Understanding the generative AI industrial revolution
-AI innovation is accelerating – with implications for financial services and payments
-Generative AI is reshaping our world.</t>
+          <t>An AI-powered payments navigator can act as a dedicated, expert assistant and provide an explanation of the error code, remedial steps and even preventative recommendations.</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5688,7 +5595,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
+          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5607,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5710,19 +5617,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:31.068758+00:00</t>
+          <t>2026-10-10T16:01:21.614612+00:00</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Unlocking GenAI’s Promise in Retail
-A new report offers clues to the retail potential of today’s hottest technology
-Generative artificial intelligence (GenAI) is poised to reshape the retail environment – from enhancing transaction security to delivering more personalized shopping experiences.</t>
+          <t>Intelligent routing makes it possible for AI to analyze historical payment patterns to select the optimal clearing channels for transactions.</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5732,7 +5637,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>56108dc2fba7dfbfd2b48a1eebd3de1eff62387bc8117916a166eca4d481cf93</t>
+          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5649,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5754,17 +5659,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:31.068758+00:00</t>
+          <t>2026-10-10T16:01:21.614612+00:00</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Forward-thinking enterprises that have adopted GenAI are already seeing measurable improvements in customer retention, forecasting precision and strategic decision-making.</t>
+          <t>Even payment repair is improved, with AI able to connect to internal systems and, when paired with human oversight, execute repair steps automatically for failed transactions, thereby increasing speed and accuracy.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5774,7 +5679,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>56108dc2fba7dfbfd2b48a1eebd3de1eff62387bc8117916a166eca4d481cf93</t>
+          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5691,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5796,17 +5701,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:31.068758+00:00</t>
+          <t>2026-10-10T16:01:35.805808+00:00</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>These are some of the questions explored in a new collaborative study from PYMNTS Intelligence and Fiserv – GenAI Applications in Retail Transaction Analysis: Industry Trends and Insights.</t>
+          <t>Increasingly, an AI agent can handle the sequence: scan recent transaction patterns for early warning signals, identify who’s at risk and push out customized offers – before the customer quietly moves on.</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5816,7 +5721,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>56108dc2fba7dfbfd2b48a1eebd3de1eff62387bc8117916a166eca4d481cf93</t>
+          <t>9e68a548aa5556c99d7bd1ef77c4c78f627fb87378bd505d306c91b782595ab2</t>
         </is>
       </c>
     </row>
@@ -5828,27 +5733,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://developer.fiserv.com</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tier_A</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://developer.fiserv.com</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-10T15:54:41.308528+00:00</t>
+          <t>2026-10-10T16:01:35.805808+00:00</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>…Read more Artificial intelligence - Wikipedia ARTIFICIAL definition: 1.</t>
+          <t>For example, an agent might spot a suspicious pattern, gather the right context, initiate the appropriate action and prepare the documentation a reviewer or regulator expects.</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5858,7 +5763,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>8289f706488aa97c85147453ce1483a4fe5a7afd22a6a319fa23c5daaa1681fd</t>
+          <t>9e68a548aa5556c99d7bd1ef77c4c78f627fb87378bd505d306c91b782595ab2</t>
         </is>
       </c>
     </row>
@@ -5870,29 +5775,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tier_A</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-10T15:55:37.573244+00:00</t>
+          <t>2026-10-10T16:01:35.805808+00:00</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cybersecurity Best Practices in a Rapidly Evolving Threat Environment
-Security and Resilience in the Age of AI
-The cybersecurity landscape is evolving rapidly as bad actors increasingly use artificial intelligence to identify, automate, and exploit technology vulnerabilities at greater speed and scale.</t>
+          <t>Smarter recommendations: agents that combine call transcripts and account activity to surface relevant products or advice, with context a banker can trust.</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5902,7 +5805,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>c8ae42b7ee474576c84822b5f8d2a9e306f7e26ed7e7a10c1198ff5990595d35</t>
+          <t>9e68a548aa5556c99d7bd1ef77c4c78f627fb87378bd505d306c91b782595ab2</t>
         </is>
       </c>
     </row>
@@ -5914,27 +5817,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-la/financial-institutions/cash-and-logistics/integrated-currency-manager.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-la/financial-institutions/cash-and-logistics/integrated-currency-manager.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-10T16:07:25.937016+00:00</t>
+          <t>2026-10-10T16:01:35.805808+00:00</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Integrated Currency Manager uses advanced artificial intelligence to assist your forecast of customer demand so you can determine how much cash to order and ship for each cash point, including ATMs, branches and vaults.</t>
+          <t>Operational triage: agents that route exceptions, collect missing information, and move work to resolution instead of creating more queues.</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5944,7 +5847,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>b5e5049be7de72254f6c7298671346d069630ea4d1c24347bb6f51ebd287841d</t>
+          <t>9e68a548aa5556c99d7bd1ef77c4c78f627fb87378bd505d306c91b782595ab2</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5859,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5966,17 +5869,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:15.552514+00:00</t>
+          <t>2026-10-10T16:01:35.805808+00:00</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Their artificial intelligence agent will.</t>
+          <t>Commercial lending support: agents that continuously absorb internal performance data alongside external signals to help manage exposure, covenants and portfolio health.</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5986,7 +5889,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
+          <t>9e68a548aa5556c99d7bd1ef77c4c78f627fb87378bd505d306c91b782595ab2</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5901,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6008,27 +5911,27 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:02.171467+00:00</t>
+          <t>2026-10-10T15:58:13.971042+00:00</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>EaaS is a modernization enabler that can help institutions strengthen data protection, support compliance efforts and establish the foundation for secure, AI driven and cloud enabled banking.</t>
+          <t>Provide broader, deeper data and AI-driven insights across industries and technologies</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>070169cf4dd71519acd1ce65c3b767ff9c68c0dbc5ff7a03d8c856f5ae12fd69</t>
+          <t>99179c0ac4fcebf059b90e9db72972077025d5446c7a7f1d12a8d091a62770d5</t>
         </is>
       </c>
     </row>
@@ -6040,7 +5943,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-financial-institutions-can-compete-digitally-and-win.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6050,28 +5953,27 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-financial-institutions-can-compete-digitally-and-win.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:49.238011+00:00</t>
+          <t>2026-10-10T15:58:13.971042+00:00</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Use AI and data analytics
-Artificial intelligence is rapidly becoming integrated into every facet of consumers’ lives, and many are feeling very comfortable with it.</t>
+          <t>Chiarello made it clear that Fiserv has been, and will continue, investing in AI across the portfolio.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2b10adf13d9f7a73dc07da19a30f4bc2c629ad214c6cae15ca76b73905d1da90</t>
+          <t>99179c0ac4fcebf059b90e9db72972077025d5446c7a7f1d12a8d091a62770d5</t>
         </is>
       </c>
     </row>
@@ -6083,7 +5985,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6093,28 +5995,27 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:17.989440+00:00</t>
+          <t>2026-10-10T15:59:27.102712+00:00</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Artificial intelligence
-AI is no longer novel, it’s part of everyday life for many adults, 70% of whom say they use it a few times a week according to internal Fiserv data.</t>
+          <t>Now, with access to faster and cheaper computing, as well as use of AI-assisted fraud tools, criminals have elevated their game and shifted their targets to weaker, more profitable points in the financial services chain.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>e0c16da5e0626951b34c1e145f27b18f2f6d77a1e8234f2a533060bd3d7a8466</t>
+          <t>1d3c0019028d36c1ec0c2b754b1434b3669edfc02b414759f5b341a283522232</t>
         </is>
       </c>
     </row>
@@ -6126,7 +6027,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/future-proofing-treasury.html</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6136,27 +6037,27 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/future-proofing-treasury.html</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:17.989440+00:00</t>
+          <t>2026-10-10T15:59:33.380466+00:00</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>[Nine in 10 financial institution boards](https://www.pymnts.com/tracker_posts/is-ai-the-master-key-to-bankings-next-era/) have approved the use of generative AI, and 3 in 4 banking leaders say their institutions are using it for departmental functions like fraud detection and risk management.</t>
+          <t>AI agents – An AI agent is software code that uses AI to understand the business domain and use that understanding to execute actions and achieve specific goals.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>e0c16da5e0626951b34c1e145f27b18f2f6d77a1e8234f2a533060bd3d7a8466</t>
+          <t>cde3daba1f67e6d096e3f34439c4c5c84f527a9cfa99964f80cd1e121a75fbd6</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6069,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/navigating-the-future-industry-trends-in-treasury.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-financial-institutions-can-compete-digitally-and-win.html</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6178,27 +6079,27 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/navigating-the-future-industry-trends-in-treasury.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-financial-institutions-can-compete-digitally-and-win.html</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:37.092458+00:00</t>
+          <t>2026-10-10T15:59:49.238011+00:00</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>There’s also European regulation relating to artificial intelligence.</t>
+          <t>Large language models can quickly dig deep into customers’ financial data and offer personalized advice or assistance, freeing up human bankers to do more complex tasks.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>bb4fa3a31d04d2db5818341f9546533a05bac0448b590bb7c11aab977edbad4d</t>
+          <t>2b10adf13d9f7a73dc07da19a30f4bc2c629ad214c6cae15ca76b73905d1da90</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6111,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6220,27 +6121,27 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:57.710588+00:00</t>
+          <t>2026-10-10T16:00:17.989440+00:00</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>The uptake of generative AI, including for financial activities, is completely different than what we’ve seen for voice-activated devices.</t>
+          <t>just 42% of Chief Experience Officers plan to leverage AI to transform customer experiences.</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
+          <t>e0c16da5e0626951b34c1e145f27b18f2f6d77a1e8234f2a533060bd3d7a8466</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6153,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6262,27 +6163,27 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:57.710588+00:00</t>
+          <t>2026-10-10T16:01:11.998445+00:00</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>But what about generative AI, like the technology behind ChatGPT?</t>
+          <t>banks that embed AI into engineering workflows are already seeing about ~40% productivity gains.</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
+          <t>d6f4fa7e61fa7c60a727651c3187a2da56c34c975f067ea27f434b8978efe06e</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6195,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6304,27 +6205,27 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:57.710588+00:00</t>
+          <t>2026-10-10T16:01:29.483063+00:00</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>[ChatGPT took two months to reach 100 million active users](https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html) – a milestone that credit cards took 15 years to achieve.</t>
+          <t>Credit scoring, fraud detection and process automation have long been areas assisted by AI and machine learning, but new advances in generative AI and large language models (LLMs) can take them to the next level.</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
+          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6237,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6346,27 +6247,27 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:57.710588+00:00</t>
+          <t>2026-10-10T16:01:29.483063+00:00</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Approximately one-third of people (32%) have used generative AI.</t>
+          <t>I like the word that Microsoft uses: they think of these tools as co-pilots.</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
+          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
         </is>
       </c>
     </row>
@@ -6378,7 +6279,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/sustainable-growth-perspectives-for-credit-union-leaders.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6388,27 +6289,27 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/sustainable-growth-perspectives-for-credit-union-leaders.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:00.898169+00:00</t>
+          <t>2026-10-10T16:01:31.068758+00:00</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>We intend to pull more AI tools into our private database, using ChatGPT questioning with some of our knowledge-based systems.</t>
+          <t>Over 90% of retailers surveyed now leverage GenAI to analyze transaction data for various purposes.</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>24ec430f21834723f4cc81efdffdcab57d12da094265ec6db4ad7cc0aeae98eb</t>
+          <t>56108dc2fba7dfbfd2b48a1eebd3de1eff62387bc8117916a166eca4d481cf93</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6321,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6430,27 +6331,27 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:11.998445+00:00</t>
+          <t>2026-10-10T16:01:31.068758+00:00</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>A report by Accenture predicts that by 2030, generative AI will be fully integrated into every aspect of banking1, automating tasks and enabling seamless human-machine collaboration.</t>
+          <t>Common applications include data privacy and security (58%), customer segmentation (54%) and forecasting (53%).</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>d6f4fa7e61fa7c60a727651c3187a2da56c34c975f067ea27f434b8978efe06e</t>
+          <t>56108dc2fba7dfbfd2b48a1eebd3de1eff62387bc8117916a166eca4d481cf93</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6363,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/drive-more-commerce-with-carat.html</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6472,17 +6373,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/drive-more-commerce-with-carat.html</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:29.483063+00:00</t>
+          <t>2026-10-10T15:58:54.090582+00:00</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>In what felt like a blink of an eye, ChatGPT has become a regular part of everyday conversation.</t>
+          <t>We use machine learning for smarter outcomes, leverage biometrics to secure devices, and continue to deliver tailored experiences to protect both the customer and the merchant.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6492,7 +6393,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
+          <t>35a48eeb9e0acb60d593968be5c3ad1c16ea3a72e1dd26779275567cb1e042b0</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6405,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6514,17 +6415,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:29.483063+00:00</t>
+          <t>2026-10-10T16:01:11.998445+00:00</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tom Eck explains how generative AI is shaping our world.</t>
+          <t>AI-powered services</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6534,7 +6435,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
+          <t>d6f4fa7e61fa7c60a727651c3187a2da56c34c975f067ea27f434b8978efe06e</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6447,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6556,17 +6457,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:29.483063+00:00</t>
+          <t>2026-10-10T16:01:11.998445+00:00</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>From the 1950s when the term “artificial intelligence” was first coined to today’s explosion in generative AI, there have been numerous advances and lulls in AI research.</t>
+          <t>Generative AI has become one of the most powerful tools for reimagining customer service, product design and back-office operations.</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6576,7 +6477,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
+          <t>d6f4fa7e61fa7c60a727651c3187a2da56c34c975f067ea27f434b8978efe06e</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6489,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6598,17 +6499,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:29.483063+00:00</t>
+          <t>2026-10-10T16:01:35.805808+00:00</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>“ChatGPT reached 100 million active users in just 2 months.</t>
+          <t>Relationship intelligence at scale: agents that prepare a banker for the next c</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6618,7 +6519,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
+          <t>9e68a548aa5556c99d7bd1ef77c4c78f627fb87378bd505d306c91b782595ab2</t>
         </is>
       </c>
     </row>
@@ -6630,27 +6531,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+          <t>https://www.fiserv.com/en-em/solutions/manage-risk-fraud.html</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_D</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+          <t>https://www.fiserv.com/en-em/solutions/manage-risk-fraud.html</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:31.068758+00:00</t>
+          <t>2026-10-10T16:05:20.639179+00:00</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Concerns about their own data analytics maturity often hold them back, creating uncertainty around whether they’re equipped to implement GenAI effectively.</t>
+          <t>predictive neural networks</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6660,7 +6561,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>56108dc2fba7dfbfd2b48a1eebd3de1eff62387bc8117916a166eca4d481cf93</t>
+          <t>037a7bac331d71f63311e156b60e25e3933f913cb6d76b482503d986f7164778</t>
         </is>
       </c>
     </row>
@@ -6672,27 +6573,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+          <t>https://www.fiserv.com/en-em/solutions/manage-risk-fraud.html</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_D</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+          <t>https://www.fiserv.com/en-em/solutions/manage-risk-fraud.html</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:31.068758+00:00</t>
+          <t>2026-10-10T16:05:20.639179+00:00</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Can organizations harness GenAI’s full potential without first reinforcing their data foundations?</t>
+          <t>use a mixture of artificial and automated intelligence, machine learning, and robotics to improve your operational efficiency, deliver rich analytics and strategic evaluation, reduce your costs, and fine-tune risk exposure</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6702,7 +6603,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>56108dc2fba7dfbfd2b48a1eebd3de1eff62387bc8117916a166eca4d481cf93</t>
+          <t>037a7bac331d71f63311e156b60e25e3933f913cb6d76b482503d986f7164778</t>
         </is>
       </c>
     </row>
@@ -6714,113 +6615,111 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-la/financial-institutions/cash-and-logistics.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-how-financial-institutions-can-get-the-most-out-of-tech-upgrades.html</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-la/financial-institutions/cash-and-logistics.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-how-financial-institutions-can-get-the-most-out-of-tech-upgrades.html</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-10T16:07:19.711088+00:00</t>
+          <t>2026-10-10T15:58:43.020266+00:00</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Artificial intelligence to produce better cash forecasting and improve their operations.</t>
+          <t>high-tech buzz of AI-powered fraud prevention tools</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>d22e51d8aee16267795ce5787080c6dc933fdd3bc6436e56e90cc74bf3b5118d</t>
+          <t>193b8a323cc5fa25418e0f44b8f94bb071a83155dd1dd864d6396dcd90763b45</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>V-005</t>
+          <t>V-002</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://www.bny.com/corporate/global/en/solutions/platforms/conventional-trust-solutions/escrow-specialty-solutions.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-financial-institutions-can-compete-digitally-and-win.html</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tier_A</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.bny.com/corporate/global/en/solutions/platforms/conventional-trust-solutions/escrow-specialty-solutions.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-financial-institutions-can-compete-digitally-and-win.html</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-10T16:27:00.696993+00:00</t>
+          <t>2026-10-10T15:59:49.238011+00:00</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>The Bank of New York Mellon SA/NV operates in the Netherlands through its Amsterdam branch at Tribes SOM2 Building, Claude Debussylaan 7, 1082 MC Amsterdam, the Netherlands, registered with the Dutch Chamber of Commerce under registration number 34363596.</t>
+          <t>Artificial intelligence is rapidly becoming integrated into every facet of consumers’ lives, and many are feeling very comfortable with it.</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>bb7ecd775df9a351a2870c707ea2887b2d6abf2f0d09727fa0a083eb0918e945</t>
+          <t>2b10adf13d9f7a73dc07da19a30f4bc2c629ad214c6cae15ca76b73905d1da90</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>V-005</t>
+          <t>V-002</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://www.bny.com/ai-policy</t>
+          <t>https://www.fiserv.com/en/about-fiserv/corporate-social-responsibility.html</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tier_A</t>
+          <t>Tier_D</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.bny.com/ai-policy</t>
+          <t>https://www.fiserv.com/en/about-fiserv/corporate-social-responsibility.html</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-10T16:24:47.859682+00:00</t>
+          <t>2026-10-10T16:10:32.850587+00:00</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>- Definitions
- For the purposes of this Policy:
-  - “Artificial Intelligence” means any technology that enables machines to perform tasks that typically require human intelligence, including but not limited to generative AI, machine learning, natural language processing, and computer vision.</t>
+          <t>From advancing cybersecurity and ethical AI to upholding human rights and fighting financial crime, we operate with purpose - helping to make the connections we power safer and smarter.</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6830,39 +6729,39 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>b31b1f0ef72c6f75f441627dd1e3e12b5305831bc8980275fa4a514304f1d512</t>
+          <t>9b4430e551d08a82fe17a2c378aa2723c53385af4c002e9a7633e54818fcbc6d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>V-005</t>
+          <t>V-002</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://www.bny.com/corporate/br/en/privacy-policy.html</t>
+          <t>https://www.fiserv.com/en/about-fiserv/corporate-social-responsibility.html</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tier_A</t>
+          <t>Tier_D</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://www.bny.com/corporate/br/en/privacy-policy.html</t>
+          <t>https://www.fiserv.com/en/about-fiserv/corporate-social-responsibility.html</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-10T16:25:18.855469+00:00</t>
+          <t>2026-10-10T16:10:32.850587+00:00</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>In particular, we may use automated methods of treatment, such as Artificial Intelligence ("AI") and Machine Learning ("ML"), which are a set of technologies programmed to perform tasks and actions that are commonly associated with humans.</t>
+          <t>A cross-functional governance structure oversees implementation of responsible AI and machine learning capabilities, establishing standards for the appropriate use of new technologies.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6872,123 +6771,123 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>8daf652f9ff98f5490b2c994ecee94efe6b1c4b73f05deb50b496ae4dfe056a7</t>
+          <t>9b4430e551d08a82fe17a2c378aa2723c53385af4c002e9a7633e54818fcbc6d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>V-005</t>
+          <t>V-002</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tier_A</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-10-10T16:27:15.940356+00:00</t>
+          <t>2026-10-10T16:01:35.805808+00:00</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Leverage secure, advanced technologies, from digital onboarding and automated data feeds to AI-powered document processing and support for digital issuance.</t>
+          <t>Many institutions have tested AI in pockets – like service chatbots and document processing – but haven’t yet run AI in a scalable way that owns outcomes</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>INDICATIVE</t>
+          <t>MARKETING-ONLY</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>044f58b49bc463e09bec6e6a7fed94efb02d2a3e79b2dad04fac76f71fb57f21</t>
+          <t>9e68a548aa5556c99d7bd1ef77c4c78f627fb87378bd505d306c91b782595ab2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>V-005</t>
+          <t>V-002</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html</t>
+          <t>https://www.fiserv.com/en/insights/businesses-and-merchants.html</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tier_A</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html</t>
+          <t>https://www.fiserv.com/en/insights/businesses-and-merchants.html</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-10T16:27:15.940356+00:00</t>
+          <t>2026-10-10T16:01:56.449520+00:00</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Leverage streamlined onboarding, AI-driven workflow optimization, real-time dashboards and APIs for operational excellence and transparency.</t>
+          <t>How AI-powered agents are already reshaping commerce, and how merchants can prepare to protect identity, loyalty and payments.</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>INDICATIVE</t>
+          <t>MARKETING-ONLY</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>044f58b49bc463e09bec6e6a7fed94efb02d2a3e79b2dad04fac76f71fb57f21</t>
+          <t>70f21ebf8b872d3414d5a01ad50f36f6dbbb470e5ab9383d2d85d510cbffc2ac</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>V-005</t>
+          <t>V-002</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://www.bny.com/ai-policy</t>
+          <t>https://www.fiserv.com/en-it/solutions/manage-risk-and-fraud.html</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tier_A</t>
+          <t>Tier_D</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://www.bny.com/ai-policy</t>
+          <t>https://www.fiserv.com/en-it/solutions/manage-risk-and-fraud.html</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-10T16:24:47.859682+00:00</t>
+          <t>2026-10-10T16:07:03.125696+00:00</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>This Acceptable Use Policy (“Policy”) applies to Your use of all services offered by BNY or third-party products, applications, or functionality that interoperate with services offered by BNY, that incorporate Artificial Intelligence, including proprietary and third-party solutions (each, an “AI Service”).</t>
+          <t>use a mixture of artificial and automated intelligence, machine learning, and robotics</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6998,19 +6897,19 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>b31b1f0ef72c6f75f441627dd1e3e12b5305831bc8980275fa4a514304f1d512</t>
+          <t>359cd9ceab797b44019327610ad2f81b8163d2d388dd8624f8b1e78c31d2d926</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>V-006</t>
+          <t>V-002</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://www.theclearinghouse.org/account/memberships</t>
+          <t>https://www.fiserv.com/en-la/financial-institutions/cash-and-logistics.html</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7020,32 +6919,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://www.theclearinghouse.org/account/memberships</t>
+          <t>https://www.fiserv.com/en-la/financial-institutions/cash-and-logistics.html</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-10T16:38:20.792884+00:00</t>
+          <t>2026-10-10T16:07:19.711088+00:00</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SIMMS ELECTRONICS INC            
-SINBAD GLOBAL HOOKAH AND TOBACCO            
-SINE AUTO ENTERPRISES LLC            
-Single Ply Solutions Incorporated            
-SINGULARITY ENERGY CORP            
-SINOXSA LLC            
-Sir Robotics Inc            
-Sirius Group LLC            
-SIS CYBER LLC            
-Sistemas Automotrices de M??xico s.a de c.v            
-Sistemas Automotrices de Mexico sa de cv            
-Sitech West LLC            
-Sitike            
-SIVIEW AMERICA INC            
-Six J Corp            
-SJ Distributors, Inc.</t>
+          <t>Artificial intelligence to produce better cash forecasting and improve their operations.</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -7055,19 +6939,19 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>a5faefe6731f4a335b06a55ffc79732cdff58938fc1496e8d8731f7990501835</t>
+          <t>d22e51d8aee16267795ce5787080c6dc933fdd3bc6436e56e90cc74bf3b5118d</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>V-006</t>
+          <t>V-002</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://www.theclearinghouse.org/payments-services/concepts-conference/agenda</t>
+          <t>https://www.fiserv.com/en-la/financial-institutions/cash-and-logistics/integrated-currency-manager.html</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7077,20 +6961,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://www.theclearinghouse.org/payments-services/concepts-conference/agenda</t>
+          <t>https://www.fiserv.com/en-la/financial-institutions/cash-and-logistics/integrated-currency-manager.html</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-10T17:05:57.764628+00:00</t>
+          <t>2026-10-10T16:07:25.937016+00:00</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>- 
-                                                            Concurrent Session
-                                                            2025 Payments Hot Topics from a Legal PerspectiveKatherine Razdolsky Rothstein, Taft Law 
- Aisha Hall, Taft LawIn this session, payments lawyers will share their insight and perspective on trends and hot topics giving rise to legal issues in payments for 2025, including, payment technology, regulatory changes, artificial intelligence, open banking, third party relationships and more!</t>
+          <t>Integrated Currency Manager uses advanced artificial intelligence to assist your forecast of customer demand</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -7100,19 +6981,19 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>cde79490c0db11463bcfb2c0a896d336ba6cf4a7f98a42a67ef2bee1cea115d6</t>
+          <t>b5e5049be7de72254f6c7298671346d069630ea4d1c24347bb6f51ebd287841d</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>V-006</t>
+          <t>V-002</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://www.theclearinghouse.org/payments-services/concepts-conference/agenda</t>
+          <t>https://www.fiserv.com/en-pl/financial-institutions/manage-risk-fraud.html</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7122,21 +7003,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://www.theclearinghouse.org/payments-services/concepts-conference/agenda</t>
+          <t>https://www.fiserv.com/en-pl/financial-institutions/manage-risk-fraud.html</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-10T17:05:57.764628+00:00</t>
+          <t>2026-10-10T16:09:14.693659+00:00</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Adrian Brown, The Clearing House
-Christina Rice, The Clearing House
-- 
-                                                            Concurrent Sessions
-                                                            Banking on AI: Boosting Productivity and Streamlining Workflows in Financial InstitutionsKevin Miyamoto, Identifee Discover how forward-thinking financial institutions are harnessing artificial intelligence to enhance their operations.</t>
+          <t>From the use of geo-location technology through to comprehensive risk analytics, strong customer authentication, use of global data and predictive neural networks, our solutions make it harder and more challenging for fraudsters.</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -7146,19 +7023,19 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>cde79490c0db11463bcfb2c0a896d336ba6cf4a7f98a42a67ef2bee1cea115d6</t>
+          <t>9478dbb9730718ea4f71685c2350e60c496c70df3e26dacfe9e8b52caaf6dc02</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>V-006</t>
+          <t>V-002</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://www.theclearinghouse.org/account/memberships</t>
+          <t>https://www.fiserv.com/en-pl/financial-institutions/manage-risk-fraud.html</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7168,33 +7045,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://www.theclearinghouse.org/account/memberships</t>
+          <t>https://www.fiserv.com/en-pl/financial-institutions/manage-risk-fraud.html</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-10T16:38:20.792884+00:00</t>
+          <t>2026-10-10T16:09:14.693659+00:00</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Skilled Manufacturing Inc            
-Skylink Transportation Inc            
-Skywire Communications Inc            
-SLC METER LLC            
-SLG BRANDS LIMITED            
-Slobodan Galeb            
-SLW Automotive Inc            
-SMALL IMPROVEMENTS INC            
-Smartrise Engineering Inc            
-SMC Performance Inc            
-SMJR TRUCKING COMPANY LLC            
-Socal Breaker Inc            
-SOCIALCLIMB LLC            
-Socrates AI Inc            
-SOFIDEL AMERICA CORP            
-Softbank Robotics America Inc            
-Softek Engineering, Inc.</t>
+          <t>Our award-winning fraud and Anti-Money Laundering (AML) technologies use a mixture of artificial and automated intelligence, machine learning, and robotics to improve your operational efficiency, deliver rich analytics and strategic evaluation, reduce your costs, and fine-tune risk exposure.</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7204,19 +7065,19 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>a5faefe6731f4a335b06a55ffc79732cdff58938fc1496e8d8731f7990501835</t>
+          <t>9478dbb9730718ea4f71685c2350e60c496c70df3e26dacfe9e8b52caaf6dc02</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>V-006</t>
+          <t>V-002</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://www.theclearinghouse.org/payments-services/concepts-conference/agenda</t>
+          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7226,17 +7087,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://www.theclearinghouse.org/payments-services/concepts-conference/agenda</t>
+          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-10T17:05:57.764628+00:00</t>
+          <t>2026-10-10T16:16:48.520050+00:00</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>They’ll share examples from industry use cases like real estate in how organized crime is leveraging generative AI in fraud attacks.</t>
+          <t>intelligent network monitoring</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7246,7 +7107,553 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>cde79490c0db11463bcfb2c0a896d336ba6cf4a7f98a42a67ef2bee1cea115d6</t>
+          <t>db2b1269d91228c705dabdad0653e298cb023eb103f956b5da090f04a38a3bdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:16:48.520050+00:00</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>biometric authentication</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>db2b1269d91228c705dabdad0653e298cb023eb103f956b5da090f04a38a3bdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:16:48.520050+00:00</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>behavior analytics, machine learning</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>db2b1269d91228c705dabdad0653e298cb023eb103f956b5da090f04a38a3bdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:16:48.520050+00:00</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>behavioral profiling</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>db2b1269d91228c705dabdad0653e298cb023eb103f956b5da090f04a38a3bdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/who-we-serve/enterprise/commerce-control-center.html</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/who-we-serve/enterprise/commerce-control-center.html</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:18:11.077288+00:00</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Use AI-powered tools to uncover trends, identify opportunities and make faster, data-driven decisions.</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>d2ec2e00fd8453d92033a40b146dd853dd3869f375c2f4e6315ff8a5cbf594f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Tier_A</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:55:37.573244+00:00</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Security and Resilience in the Age of AI</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>c8ae42b7ee474576c84822b5f8d2a9e306f7e26ed7e7a10c1198ff5990595d35</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:29.483063+00:00</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Generative AI will broadly impact organizations and functions.</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/partner-support.html</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Tier_D</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/partner-support.html</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:18:43.822639+00:00</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>CoPilot partner portfolio management system</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>8dd58af9ccba196f3230d88f181ec520cb4b0fb65eb082fdd0c96b03eca41f48</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2026-10-10T15:58:13.971042+00:00</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>The explosion of interest in AI, fueled by the recent introduction of ChatGPT from OpenAI, has executives across industries rethinking what generative AI means to their business and how and where to begin adoption.</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>99179c0ac4fcebf059b90e9db72972077025d5446c7a7f1d12a8d091a62770d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:11.998445+00:00</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>AI is only as good as the data it can access.</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>d6f4fa7e61fa7c60a727651c3187a2da56c34c975f067ea27f434b8978efe06e</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Tier_C</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:01:31.068758+00:00</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Generative artificial intelligence (GenAI) is poised to reshape the retail environment – from enhancing transaction security to delivering more personalized shopping experiences.</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>56108dc2fba7dfbfd2b48a1eebd3de1eff62387bc8117916a166eca4d481cf93</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>V-005</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>https://www.bny.com/ai-policy</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Tier_A</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>https://www.bny.com/ai-policy</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:24:47.859682+00:00</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Use any robot, spider, intelligent agent, other automatic device or manual process, or automated systems to search, monitor or copy our web pages, data, content or other materials contained herein, or for any other unauthorized purpose.</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>INDICATIVE</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>b31b1f0ef72c6f75f441627dd1e3e12b5305831bc8980275fa4a514304f1d512</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>V-005</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Tier_A</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:27:15.940356+00:00</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>AI-powered document processing</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>044f58b49bc463e09bec6e6a7fed94efb02d2a3e79b2dad04fac76f71fb57f21</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>V-005</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Tier_A</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2026-10-10T16:27:15.940356+00:00</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>AI-driven workflow optimization</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>MARKETING-ONLY</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>044f58b49bc463e09bec6e6a7fed94efb02d2a3e79b2dad04fac76f71fb57f21</t>
         </is>
       </c>
     </row>

--- a/data/Meridian_Vendor_Output.xlsx
+++ b/data/Meridian_Vendor_Output.xlsx
@@ -1044,11 +1044,11 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>"We believe our research will eventually lead to artificial general intelligence, a system that can solve human-level problems."
+          <t>"Use ChatGPT to answer questions, write, create images, complete work, and code—all in one place"
 Source: https://www.automworx.com/ai-policy (retrieved 2026-10-10)
-"Meet Gemini, Google’s AI assistant. Get help with writing, planning, brainstorming, and more."
+"We believe our research will eventually lead to artificial general intelligence, a system that can solve human-level problems"
 Source: https://www.automworx.com/ai-policy (retrieved 2026-10-10)
-"Use ChatGPT to answer questions, write, create images, complete work, and code—all in one place."
+"Meet Gemini, Google’s AI assistant. Get help with writing, planning, brainstorming, and more"
 Source: https://www.automworx.com/ai-policy (retrieved 2026-10-10)</t>
         </is>
       </c>
@@ -1156,22 +1156,24 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>"LinkLive integrates seamlessly with Experience Digital from Fiserv to work in tandem with human call center agents. When financial institutions use this AI-powered tool, 80% of calls are answered within 15 seconds, average handle time is cut by 30 seconds, and customer experience increases by 15%."
-Source: https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html (retrieved 2026-10-10)
-"Context-aware scoring Easily see a list of account changes ranked by risk level according to predictive data, including historic mobility patterns and geographic crime dynamics, enabling staff to address higher risk interactions first."
-Source: https://www.fiserv.com/en/solutions/notifi-real-time-engagement/notifi-detect.html (retrieved 2026-10-10)
-"Powered by machine learning Leverage a predictive scoring model that learns from past experiences with your accounts to ensure constant refinement — Stay ahead of emerging fraud trends while boosting consumer satisfaction."
+          <t>"Leverage AI-driven risk scoring to analyze transaction patterns and customer behavior in real time."
+Source: https://www.fiserv.com/en/solutions/risk-compliance/aml-risk-manager.html (retrieved 2026-10-10)
+"AI-enabled platforms, such as Client360, which answers questions in seconds and provides self-service tools and resources 24/7/365."
+Source: https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-how-financial-institutions-can-get-the-most-out-of-tech-upgrades.html (retrieved 2026-10-10)
+"| 
+|---|---|
+|  | Powered by machine learning Leverage a predictive scoring model that learns from past experiences with your accounts to ensure constant refinement — Stay ahead of emerging fraud trends while boosting consumer satisfaction."
 Source: https://www.fiserv.com/en/solutions/notifi-real-time-engagement/notifi-detect.html (retrieved 2026-10-10)</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>Conversational language model generating text responses; data privacy/security, customer segmentation, forecasting; Large language model usage at scale for user interactions; Predictive neural networks used to detect and prevent fraud; AI-powered risk scoring that evaluates transaction patterns and customer behavior to flag suspicious activity; uses predictive neural networks to detect and prevent fraud; Machine‑learning‑driven predictive scoring model that continuously learns from past account interactions to assess fraud risk; uses generative AI models to enhance fraud detection; uses generative AI to obtain and analyze payments and transaction data; None described; applies machine learning and robotic process automation to analyze transactions, generate analytics, and automate fraud/AML processes; Analyzes check images to detect alterations and forgeries, applying scoring to flag suspicious items; AI agent navigates the website and interacts with product details on behalf of the shopper; LLM inference for text generation; Supplies ledger and transaction data to AI engines for fraud detection and customer engagement; AI assistance (co‑pilot) augmenting user tasks; applies machine learning and robotic process automation to analyze financial crime data, generate analytics, and automate decision‑making; Uses AI to analyze banking and transaction data and deliver personalized fraud detection, risk assessment, money‑management insights and reward offers to cardholders; Governance and standards for responsible AI/ML deployment; Scans recent transaction patterns to detect early‑warning signals, flags at‑risk customers and automatically generates customized offers.; Predictive risk scoring that ranks account changes by risk using historical mobility patterns and geographic crime dynamics; Autonomous AI agents evaluate products, compare options, and execute purchases; General statement about AI performance being dependent on data quality; aggregates behavioral and transactional data to produce a risk rating; AI intended to improve customer experience; provides automated financial advice to users; Uses large language models to analyze customers’ financial data and generate personalized advice/assistance; Investment in AI capabilities across product portfolio; Provides services powered by artificial intelligence such as personalization, automation, and decision support; Automated handling of routine calls, texts, chats with secure access to customer data; applies AI, machine learning and robotics to automate fraud/AML processes, analytics and risk assessment; searching, comparing options, applying preferences and completing the purchase; AI agents parse and apply structured business rules to assess merchant offerings; Statement describing AI agents’ deterministic navigation behavior; applies AI to banking processes and customer interactions; automates detection and prevention of check fraud; Enables privacy-preserving analytics on encrypted data; Uses algorithms to identify suspicious patterns and prevent fraud; Provides predictive support and real-time issue resolution for personalized payment servicing; Calculates risk scores from historical account data to set automated deposit limits; image analytics to classify checks and detect alterations; Automation of reporting and KYC analysis using AI; forecasting customer cash demand to determine cash ordering and shipping amounts; AI-powered digital assistants provide self‑service help, handling customer queries and routing, thereby reducing help‑desk volume.; Analyzes historical payment patterns to choose optimal clearing channels; creates AI‑generated profiles of typical user behavior to flag deviations; machine learning and robotics to improve operational efficiency, analytics, and risk evaluation; Highlights risk of AI when data governance is weak; Uses automated analytics (potentially AI) to detect fraudulent activity and optimize transaction processing.; provides intelligent data processing and analysis capabilities; Improved predictive modeling and automation using generative AI and LLMs; Predictive analytics used to forecast stress points, adjust underwriting standards, and plan strategically; Analyzes transaction and behavioral data to flag suspicious activity; Frameworks authenticate AI agents, verify intent, and safeguard autonomous transaction flows; generates insights from organizational data via analytics; Uses AI to generate insights from broad data sets; Automated question‑answering and self‑service assistance powered by AI; Applies machine learning algorithms to generate predictive insights and personalize customer experiences.; AI agents analyze real‑time account, position, and ledger data to generate recommendations, perform underwriting, and produce explainable decisions; Broad application of generative AI across business processes; Fuses call‑transcript text with account activity to generate product or advisory recommendations.; Recommendation of optimal payment method based on transaction context; Enables AI-driven workflows for personalized offers and other automated processes; generates text‑based responses to user prompts for financial queries; Continuously ingests internal loan performance metrics and external market signals to monitor credit exposure, covenant compliance, and overall portfolio health.; applies AI‑driven models to verify user identity from biometric traits; Describes general consumer usage of AI; Use of AI in cybersecurity and broader operations to ensure ethical and safe outcomes; Connects to internal systems and automatically executes repair steps for failed transactions; signature comparison and anomaly detection across multiple checks; Reference to generative AI (ChatGPT) as a buzzword; AI-assisted fraud tools used by criminals to identify and exploit vulnerabilities in financial services; Provides banking services that are driven by artificial intelligence; uses predictive neural networks to detect and prevent fraudulent transactions; Detects compromised card numbers listed on dark‑web marketplaces; uses predictive neural networks to analyze transaction patterns and detect fraud; AI analyzes transaction and payment data to detect trends and opportunities, generating actionable insights.; uses AI to generate more accurate cash‑forecasting models and optimize operational decisions; Software agents leverage AI to comprehend business context, recall historical data, reason, and autonomously perform actions.; analyze transaction data; AI-powered agents that interact with customers to facilitate commerce and protect identity, loyalty, and payments; uses predictive analytics to forecast payment behavior, identify early risk signals, and automate reconciliation insights; provides early‑warning intelligence to detect disputes as they are initiated; Real-time sentiment analysis of voice and language; Automates reconciliation and message correction tasks; AI agents evaluate data quality to select merchants for transactions; Classifies, protects, and governs data prior to AI processing; Generates contextual intelligence to equip bankers with relevant customer insights before interactions.; Facilitates adoption of AI tools by providing data protection; Reference to existing chatbot‑style Q&amp;A and document‑processing AI implementations.; Integrates AI tools into software engineering processes to accelerate development and increase productivity; uses predictive neural networks to analyze transaction and location data for fraud detection; General integration of AI into consumer experiences; AI-driven real-time risk scoring and decisioning to assess transaction risk; AI-powered call routing and support tool that handles routine interactions and provides real‑time assistance; Analyzes transaction patterns in real time to detect anomalies; employs machine‑learning algorithms to analyze user and system behavior for fraud patterns; Applies AI techniques to analyze institutional data for insights and predictive outcomes.; Assists in partner portfolio management and operational tasks; AI assists the core system in generating quicker responses/insights; Distinguishes legitimate vs fraudulent behavior and adapts to new fraud tactics; Acts as an assistant to explain error codes and suggest remedial/preventative steps; Automates exception routing, gathers required data, and forwards cases to resolution teams.; AI algorithms for detecting fraudulent activity; enhancing transaction security and delivering personalized shopping experiences; AI analyzes shopping behavior to compare options, select products, place orders, and manage replenishment.; Reduces risk of model leakage and data misuse in AI models; uses AI‑supported automation to streamline reporting, monitoring and data delivery across teams; uses AI to speed up and enhance new capability development; AI program assesses product attributes, merchant policies, and related data to determine shortlist eligibility; identifies, automates, and exploits technology vulnerabilities; routing optimization across payment schemes and alternative payments for agentic transactions; Artificial intelligence, machine learning, and robotics to enhance operational efficiency and analytics for fraud/AML detection; Uses generative AI to redesign customer service interactions, create new product concepts, and automate back‑office tasks; personalizes interactions and modernizes experiences using AI-driven insights; enables voice‑based conversational interactions for tasks such as paying a bill, checking a balance or sending money; uses AI to monitor network traffic and detect anomalous activity; Extracts deep insights from payments data to inform business decisions; Applies neural network algorithms and machine‑learning models to historical transaction data to flag anomalous patterns; Detects suspicious transaction patterns, collects contextual information, triggers remediation actions, and auto‑generates compliance documentation.; general acceleration of technology initiatives; Accelerates deployment of AI solutions through encryption services; AI-powered personalization of offers and experiences; Analyzes transaction and usage data to generate actionable insights</t>
+          <t>AI systems initiate transactions using payment credentials; offers AI‑driven assistance for financial decision‑making and planning; automatic execution of repair steps for failed transactions via internal system integration; AI agent acts on behalf of the shopper to navigate the site and make purchasing decisions; AI-driven image and pattern analysis to detect altered or fraudulent checks.; automated handling of routine calls, texts and chats using AI; Autonomous product discovery, evaluation, and purchase execution; use of generative AI to improve fraud detection models; generative AI for business ideation; identifying, automating, and exploiting technology vulnerabilities; Automated document generation and data extraction for audit, reconciliation, KYC; dig deep into customers’ financial data and offer personalized advice or assistance; Pushes detailed and personalized information for fraud detection, risk assessment, money management, and rewards/offers; broad AI development and integration across product portfolio; Predictive analytics and risk modeling on transaction and customer data; integration of AI into consumer experiences; General claim of AI-driven transformation; Automated loan decisioning and underwriting; Facilitates integration and use of AI tools by protecting data; Uses predictive analytics to forecast stress points, adjust underwriting standards, and plan strategically; AI integrations to understand customers’ needs and recommend appropriate solutions; AI workflows for personalized offers and decisioning; consumer usage of AI tools; recommends the optimal payment method for a transaction; generates content and suggestions for budgeting, expense tracking, investment ideas, and loan information; Generative AI used to reimagine customer service, product design, and back‑office operations; Applies predictive analytics to invoice and payment data to generate insights and early warnings for finance teams.; extracting deep insights from payments data to inform business decisions; obtaining and analyzing payments and transaction data; secure data access and task execution on existing environments; Applies machine learning algorithms to generate predictive insights and personalize experiences; Neural network models analyze transaction data to flag suspicious patterns.; automation of reconciliation and message correction tasks; signature comparison and anomaly detection using AI models; Evaluates products, policies and merchant data to generate a shortlist; general consumer use of AI technologies; AI performs real‑time risk scoring of transaction patterns and customer behavior; automation of check fraud detection using AI and machine learning; generating insights from data using AI algorithms; Mitigates model leakage and data misuse in AI models; analysis of historical payment patterns to choose optimal clearing channels; None (buzzword reference to future AI use); using AI to generate measurable business outcomes; Aggregated data feeds AI models to improve decision speed and accuracy.; AI-driven self‑service help tools (digital assistants) that handle customer queries; AI-driven transformation of customer experience; AI integration with call‑center platform to assist human agents; Predictive modeling and anomaly detection using generative AI and LLMs; AI agents use clean, contextual data to generate recommendations, underwriting decisions, and explainable outcomes; risk scoring based on aggregated customer behavior data using AI; applies machine learning and RPA to analyze large datasets to detect patterns indicative of fraud; AI usage detected in public content; AI‑enabled analytics for data insight; AI‑driven virtual assistant that answers user questions and delivers self‑service tools; applies AI to banking processes and services; Conversational large language model generating text responses; predictive analytics to forecast trends and inform business decisions; real‑time analysis of transaction patterns for fraud detection; AI embedded in engineering workflows to improve productivity; predictive support and real‑time issue resolution for personalized payment servicing; Real-time sentiment analysis of audio and text; uses AI to enable personalization, automation, and real-time decision‑making; provides financial advice to users; AI-assisted tools used by fraudsters to identify and exploit vulnerable points in the financial services chain; AI‑based analysis to detect fraudulent activity; Uses AI to calculate risk scores from historical account data to set automated deposit limit values.; Routing optimization using conversational AI to select payment schemes and alternative payment methods; Autonomous AI agents evaluate, compare and purchase products for the shopper; Large language model serving chat interactions; uses machine learning models to classify transactions as legitimate or fraudulent and continuously update to new fraud patterns; provides intelligent analytics and insights for digital banking experiences; Machine learning models create benchmarks from historical transaction data to detect anomalies.; Uses AI to analyze data for personalized experiences; provides automated insights to streamline payment routing; Large language model powering chat and search; Selects merchants based on the clarity and consistency of their data; Provides data classification, protection, and governance for AI workflows; enables voice‑based interactions for tasks like paying bills, checking balances, or sending money; End-to-end shopping automation (search, compare, apply preferences, purchase); uses AI-driven analytics to spot emerging fraud trends and monitor dark‑web listings of compromised cards, then triggers alerts across channels; Enables privacy‑preserving analytics on encrypted data; AI services are referenced as a trend driving modernization; Software agents that apply AI to understand domain knowledge and perform automated actions; AI‑driven call routing and response automation to accelerate call answering and reduce handle time; Uses biometric recognition (e.g., fingerprint or facial analysis) to authenticate users and protect devices; Consumes structured business logic to compare policies, SLAs and sustainability commitments</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>Apple (Siri), Amazon (Alexa), Fiserv, Microsoft, OpenAI</t>
+          <t>Copilot, OpenAI, OpenAI, Microsoft</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
@@ -1181,7 +1183,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>Vendor has Critical criticality tier with confirmed AI footprint. Data accessed includes "Full customer master, balances and transactions for 1.4 million customers.". Weighted evidence score: 304.8 across 124 valid signal(s). Evidence strength: strong.</t>
+          <t>Vendor has Critical criticality tier with confirmed AI footprint. Data accessed includes "Full customer master, balances and transactions for 1.4 million customers.". Weighted evidence score: 319.8 across 116 valid signal(s). Evidence strength: strong.</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -1485,12 +1487,14 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>"Use any robot, spider, intelligent agent, other automatic device or manual process, or automated systems to search, monitor or copy our web pages, data, content or other materials contained herein, or for any other unauthorized purpose."
+          <t>"The Bank of New York Mellon SA/NV operates in the Netherlands through its Amsterdam branch at Tribes SOM2 Building, Claude Debussylaan 7, 1082 MC Amsterdam, the Netherlands, registered with the Dutch Chamber of Commerce under registration number 34363596."
+Source: https://www.bny.com/corporate/global/en/solutions/platforms/conventional-trust-solutions/escrow-specialty-solutions.html (retrieved 2026-10-10)
+"- Definitions
+ For the purposes of this Policy:
+  - “Artificial Intelligence” means any technology that enables machines to perform tasks that typically require human intelligence, including but not limited to generative AI, machine learning, natural language processing, and computer vision."
 Source: https://www.bny.com/ai-policy (retrieved 2026-10-10)
-"AI-powered document processing"
-Source: https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html (retrieved 2026-10-10)
-"AI-driven workflow optimization"
-Source: https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html (retrieved 2026-10-10)</t>
+"In particular, we may use automated methods of treatment, such as Artificial Intelligence ("AI") and Machine Learning ("ML"), which are a set of technologies programmed to perform tasks and actions that are commonly associated with humans."
+Source: https://www.bny.com/corporate/br/en/privacy-policy.html (retrieved 2026-10-10)</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1500,7 +1504,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>Microsoft, OpenAI, Proprietary (BNY AI Hub)</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -1510,7 +1514,7 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>Vendor has High criticality tier with confirmed AI footprint across corporate solutions (AI document processing and workflow optimization). Data accessed includes "Payment instructions, counterparty names and account identifiers.". Weighted evidence score: 7.6. Model providers include Microsoft Azure / OpenAI.</t>
+          <t>Vendor has High criticality tier with confirmed AI footprint across corporate solutions (AI document processing and workflow optimization). Data accessed includes "Payment instructions, counterparty names and account identifiers.". Weighted evidence score: 24.1. Model providers include Microsoft Azure / OpenAI.</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -2152,7 +2156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H131"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,12 +2229,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>We believe our research will eventually lead to artificial general intelligence, a system that can solve human-level problems.</t>
+          <t>Use ChatGPT to answer questions, write, create images, complete work, and code—all in one place</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>INDICATIVE</t>
+          <t>MARKETING-ONLY</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2267,12 +2271,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Meet Gemini, Google’s AI assistant. Get help with writing, planning, brainstorming, and more.</t>
+          <t>We believe our research will eventually lead to artificial general intelligence, a system that can solve human-level problems</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2309,7 +2313,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Use ChatGPT to answer questions, write, create images, complete work, and code—all in one place.</t>
+          <t>Meet Gemini, Google’s AI assistant. Get help with writing, planning, brainstorming, and more</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2331,27 +2335,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
+          <t>https://www.fiserv.com/en/solutions/risk-compliance/aml-risk-manager.html</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
+          <t>https://www.fiserv.com/en/solutions/risk-compliance/aml-risk-manager.html</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:17.989440+00:00</t>
+          <t>2026-10-10T15:55:53.603656+00:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LinkLive integrates seamlessly with Experience Digital from Fiserv to work in tandem with human call center agents. When financial institutions use this AI-powered tool, 80% of calls are answered within 15 seconds, average handle time is cut by 30 seconds, and customer experience increases by 15%.</t>
+          <t>Leverage AI-driven risk scoring to analyze transaction patterns and customer behavior in real time.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2361,7 +2365,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>e0c16da5e0626951b34c1e145f27b18f2f6d77a1e8234f2a533060bd3d7a8466</t>
+          <t>bbf9f86093b9ffb25ab6aed003eaf13162c0712252e6bdfdd50cf8312e0dbda0</t>
         </is>
       </c>
     </row>
@@ -2373,27 +2377,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/solutions/notifi-real-time-engagement/notifi-detect.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-how-financial-institutions-can-get-the-most-out-of-tech-upgrades.html</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/solutions/notifi-real-time-engagement/notifi-detect.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-how-financial-institutions-can-get-the-most-out-of-tech-upgrades.html</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-10T16:17:07.032951+00:00</t>
+          <t>2026-10-10T15:58:43.020266+00:00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Context-aware scoring Easily see a list of account changes ranked by risk level according to predictive data, including historic mobility patterns and geographic crime dynamics, enabling staff to address higher risk interactions first.</t>
+          <t>AI-enabled platforms, such as Client360, which answers questions in seconds and provides self-service tools and resources 24/7/365.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2403,7 +2407,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0bb738ce5f32c8f734f491ff33dfae60acb4c57047b41cba1000be165c0f89c3</t>
+          <t>193b8a323cc5fa25418e0f44b8f94bb071a83155dd1dd864d6396dcd90763b45</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2439,9 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Powered by machine learning Leverage a predictive scoring model that learns from past experiences with your accounts to ensure constant refinement — Stay ahead of emerging fraud trends while boosting consumer satisfaction.</t>
+          <t>| 
+|---|---|
+|  | Powered by machine learning Leverage a predictive scoring model that learns from past experiences with your accounts to ensure constant refinement — Stay ahead of emerging fraud trends while boosting consumer satisfaction.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2457,37 +2463,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv.html</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_D</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv.html</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:10.845485+00:00</t>
+          <t>2026-10-10T16:18:33.255733+00:00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AI solutions are now bringing automation capabilities to check fraud prevention.</t>
+          <t>Deliver a seamless payment experience with Fiserv
+The Fiserv difference
+CoPilot Portfolio Management
+CoPilot is a powerful partner portfolio management system that gives software providers the tools to onboard business customers and operate more efficiently.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>INDICATIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
+          <t>843134a0576c29ac4f746db21cfe2f5b46c3b6b584699b4786425a3b12b6014a</t>
         </is>
       </c>
     </row>
@@ -2499,37 +2508,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/partner-support.html</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_D</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/partner-support.html</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:10.845485+00:00</t>
+          <t>2026-10-10T16:18:43.822639+00:00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thanks to artificial intelligence and machine learning, image analytics has matured to a point where we can more easily identify whether a suspect check is first party or third party, or whether it was whitewashed or changed in some other way.</t>
+          <t>CoPilot from Fiserv
+A powerful partner portfolio management system that gives software providers the tools to onboard business customers and operate more efficiently.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>INDICATIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
+          <t>8dd58af9ccba196f3230d88f181ec520cb4b0fb65eb082fdd0c96b03eca41f48</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2571,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AI is going to play a major role in check fraud detection, especially the generative AI models that are available to us.</t>
+          <t>once we have your signature, AI models can compare the latest signature with the ones on the last 20 checks, even including the impression depth of the ink, to detect any deviation</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2583,7 +2593,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2593,17 +2603,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:10.845485+00:00</t>
+          <t>2026-10-10T15:59:02.171467+00:00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>With today's technology, once we have your signature, AI models can compare the latest signature with the ones on the last 20 checks, even including the impression depth of the ink, to detect any deviation.</t>
+          <t>It enables confident adoption of cloud services, analytics platforms and AI tools.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2613,7 +2623,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
+          <t>070169cf4dd71519acd1ce65c3b767ff9c68c0dbc5ff7a03d8c856f5ae12fd69</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2635,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2635,17 +2645,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:10.845485+00:00</t>
+          <t>2026-10-10T15:59:02.171467+00:00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>All these data points from various systems help create a customer risk rating.</t>
+          <t>EaaS supports responsible AI adoption by ensuring sensitive data is classified, protected and governed before entering AI workflows.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2655,7 +2665,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
+          <t>070169cf4dd71519acd1ce65c3b767ff9c68c0dbc5ff7a03d8c856f5ae12fd69</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2677,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2677,17 +2687,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:15.552514+00:00</t>
+          <t>2026-10-10T15:59:02.171467+00:00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Their artificial intelligence agent will.</t>
+          <t>That enables privacy-preserving analytics so financial institutions can extract insights without exposing personally identifiable information.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2697,7 +2707,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
+          <t>070169cf4dd71519acd1ce65c3b767ff9c68c0dbc5ff7a03d8c856f5ae12fd69</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2719,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2719,17 +2729,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:15.552514+00:00</t>
+          <t>2026-10-10T15:59:02.171467+00:00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Agentic commerce, in which autonomous AI agents evaluate, compare or even purchase on a shopper’s behalf, is already reshaping digital interactions.</t>
+          <t>The process can assist in reducing the likelihood of model leakage, data misuse or noncompliant outputs.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2739,7 +2749,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
+          <t>070169cf4dd71519acd1ce65c3b767ff9c68c0dbc5ff7a03d8c856f5ae12fd69</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2761,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2761,17 +2771,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:15.552514+00:00</t>
+          <t>2026-10-10T15:59:14.264948+00:00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Instead of a human clicking through a page, an autonomous AI program evaluates your products, your policies and your data, and decides if you make the shortlist.</t>
+          <t>Machine learning helps distinguish between legitimate and fraudulent behaviors while adapting over time to new, previously unseen fraud tactics.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2781,7 +2791,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
+          <t>203ecbe73bbb6d5fa4453b937b5a21ea13c57ac97be86b644d642a3f03808984</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2803,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2803,17 +2813,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:15.552514+00:00</t>
+          <t>2026-10-10T15:59:14.264948+00:00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Global networks and platforms are moving rapidly to support this shift, developing frameworks that authenticate AI agents, validate user intent and protect autonomous transactions.</t>
+          <t>This gives us access to large amounts of data which, when analyzed through machine learning, robotic process automation and other advanced technology, enables us to create a broad view of fraudulent activity.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2823,7 +2833,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
+          <t>203ecbe73bbb6d5fa4453b937b5a21ea13c57ac97be86b644d642a3f03808984</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2845,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2845,17 +2855,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:15.552514+00:00</t>
+          <t>2026-10-10T15:59:23.989694+00:00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>“AI agents do not browse. They do not wander. They do not get lost,” said Brandy Wood, Head of Merchant Acquiring Data and Reporting at Fiserv.</t>
+          <t>Identify check fraud activity with an analysis and forecasting engine that uses neural network algorithms to recognize patterns of suspicious activity, such as deposit fraud and check kiting.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2865,7 +2875,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
+          <t>7fd5d1bd270bd5616598a4e10fbe9d4339457256c77c7cb944be0c13105dbe54</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2887,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2887,17 +2897,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:15.552514+00:00</t>
+          <t>2026-10-10T15:59:23.989694+00:00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AI agents favor businesses whose data is clear, consistent and transaction‑ready.</t>
+          <t>Through machine learning and the use of historical transaction data from your account processing system, a benchmark is established for each account type and used to identify suspicious, out-of-pattern activity.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2907,7 +2917,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
+          <t>7fd5d1bd270bd5616598a4e10fbe9d4339457256c77c7cb944be0c13105dbe54</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2929,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-your-bank-can-evolve-to-face-economic-uncertainty.html</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2929,17 +2939,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-your-bank-can-evolve-to-face-economic-uncertainty.html</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:15.552514+00:00</t>
+          <t>2026-10-10T16:00:08.494427+00:00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AI agents will consume structured business logic directly, comparing return policies, fulfillment SLAs, sustainability commitments and more</t>
+          <t>Leveraging internal data and predictive analytics gives community banks a leg up, allowing them to forecast potential stress points, adjust underwriting standards and plan more strategically for differing economic scenarios.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2949,7 +2959,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
+          <t>9b92194e0871e826ea5d8f7dc895189c41c5fe0389f07d987705a27321935e76</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2971,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-catalyst-for-change.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2971,17 +2981,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-catalyst-for-change.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:04.069624+00:00</t>
+          <t>2026-10-10T16:01:11.998445+00:00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>feed real-time insights to AI engines, fraud monitors, and customer engagement platforms</t>
+          <t>This gives AI agents clean, contextual and auditable data to power relevant recommendations, dynamic underwriting and explainable decision making.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2991,7 +3001,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>29ceae0f8821c07acbc4bed958a564ed64f25010d1998133e51acb1c70e5cf18</t>
+          <t>d6f4fa7e61fa7c60a727651c3187a2da56c34c975f067ea27f434b8978efe06e</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3033,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ChatGPT has become a regular part of everyday conversation.</t>
+          <t>AI is enabling more effective service and fraud detection in call center operations through improved real-time sentiment analysis of the caller’s voice, tone and language.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3045,7 +3055,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/why-isvs-choose-fiserv-as-their-strategic-growth-partner.html</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3055,27 +3065,27 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/why-isvs-choose-fiserv-as-their-strategic-growth-partner.html</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:29.483063+00:00</t>
+          <t>2026-10-10T16:01:49.424620+00:00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ChatGPT reached 100 million active users in just 2 months.</t>
+          <t>Our powerful partner portal, CoPilot, brings it all together in one place.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>INDICATIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
+          <t>116e954ada2929835a68a16c7645e4ad5b23510f6c5734d58ab4e301a7ebcfd5</t>
         </is>
       </c>
     </row>
@@ -3087,27 +3097,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:29.483063+00:00</t>
+          <t>2026-10-10T15:55:37.573244+00:00</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>If you’ve used ChatGPT, you are using an LLM.</t>
+          <t>The cybersecurity landscape is evolving rapidly as bad actors increasingly use artificial intelligence to identify, automate, and exploit technology vulnerabilities at greater speed and scale.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3117,7 +3127,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
+          <t>c8ae42b7ee474576c84822b5f8d2a9e306f7e26ed7e7a10c1198ff5990595d35</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3139,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-is-here-what-merchants-need-to-know-and-do.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3139,17 +3149,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-is-here-what-merchants-need-to-know-and-do.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:17.132596+00:00</t>
+          <t>2026-10-10T15:58:10.845485+00:00</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>With the emergence of AI applications, an AI agent will soon handle that entire process – searching, comparing options, applying preferences and completing the purchase – without the shopper ever touching a traditional eCommerce site.</t>
+          <t>All these data points from various systems help create a customer risk rating</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3159,7 +3169,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2c831be14f46869e03dfb83376b0a58d1af96275c0cb4ec1b8f22e9f657234f2</t>
+          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3181,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-is-here-what-merchants-need-to-know-and-do.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3181,17 +3191,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-is-here-what-merchants-need-to-know-and-do.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:17.132596+00:00</t>
+          <t>2026-10-10T15:58:13.971042+00:00</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>This is why Fiserv is working with conversational AI platforms to introduce routing optimization across schemes and alternative payments for agentic transactions, for both SMBs and enterprise merchants.</t>
+          <t>Provide broader, deeper data and AI-driven insights across industries and technologies</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3201,7 +3211,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2c831be14f46869e03dfb83376b0a58d1af96275c0cb4ec1b8f22e9f657234f2</t>
+          <t>99179c0ac4fcebf059b90e9db72972077025d5446c7a7f1d12a8d091a62770d5</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3223,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-how-financial-institutions-can-get-the-most-out-of-tech-upgrades.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3223,17 +3233,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-how-financial-institutions-can-get-the-most-out-of-tech-upgrades.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:43.020266+00:00</t>
+          <t>2026-10-10T15:58:13.971042+00:00</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AI-enabled platforms, such as Client360, which answers questions in seconds and provides self-service tools and resources 24/7/365.</t>
+          <t>Chiarello made it clear that Fiserv has been, and will continue, investing in AI across the portfolio.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3243,7 +3253,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>193b8a323cc5fa25418e0f44b8f94bb071a83155dd1dd864d6396dcd90763b45</t>
+          <t>99179c0ac4fcebf059b90e9db72972077025d5446c7a7f1d12a8d091a62770d5</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3265,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/enabling-the-acceleration-of-all-things-digital.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-is-here-what-merchants-need-to-know-and-do.html</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3265,17 +3275,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/enabling-the-acceleration-of-all-things-digital.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-is-here-what-merchants-need-to-know-and-do.html</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:00.582236+00:00</t>
+          <t>2026-10-10T15:58:17.132596+00:00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>That means working to improve consumer journeys, personalize interactions and modernize experiences with real-time data, automation tools and AI, to name a few.</t>
+          <t>With the emergence of AI applications, an AI agent will soon handle that entire process – searching, comparing options, applying preferences and completing the purchase – without the shopper ever touching a traditional eCommerce site.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3285,7 +3295,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>f38e2dfa91b34f6c162ce065fce285464704c9e0ac64cce8a50ba1e03f945ab9</t>
+          <t>2c831be14f46869e03dfb83376b0a58d1af96275c0cb4ec1b8f22e9f657234f2</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3307,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/enabling-the-acceleration-of-all-things-digital.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-is-here-what-merchants-need-to-know-and-do.html</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3307,17 +3317,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/enabling-the-acceleration-of-all-things-digital.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-is-here-what-merchants-need-to-know-and-do.html</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:00.582236+00:00</t>
+          <t>2026-10-10T15:58:17.132596+00:00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Complementary groups of data-rich and intelligent tools</t>
+          <t>This is why Fiserv is working with conversational AI platforms to introduce routing optimization across schemes and alternative payments for agentic transactions, for both SMBs and enterprise merchants.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3327,7 +3337,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>f38e2dfa91b34f6c162ce065fce285464704c9e0ac64cce8a50ba1e03f945ab9</t>
+          <t>2c831be14f46869e03dfb83376b0a58d1af96275c0cb4ec1b8f22e9f657234f2</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3349,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/drive-more-commerce-with-carat.html</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3349,17 +3359,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/drive-more-commerce-with-carat.html</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:14.264948+00:00</t>
+          <t>2026-10-10T15:58:54.090582+00:00</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Machine learning helps distinguish between legitimate and fraudulent behaviors while adapting over time to new, previously unseen fraud tactics.</t>
+          <t>leverage biometrics to secure devices</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3369,7 +3379,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>203ecbe73bbb6d5fa4453b937b5a21ea13c57ac97be86b644d642a3f03808984</t>
+          <t>35a48eeb9e0acb60d593968be5c3ad1c16ea3a72e1dd26779275567cb1e042b0</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3391,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/enabling-the-acceleration-of-all-things-digital.html</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3391,17 +3401,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/enabling-the-acceleration-of-all-things-digital.html</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:23.989694+00:00</t>
+          <t>2026-10-10T15:59:00.582236+00:00</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Establishing intelligent deposit limits for deposit accounts can reduce risk for your financial institution while rewarding good accountholders with higher deposit limits. Use historical data from your account processing system to calculate risk scores for each account and determine automated deposit limit values.</t>
+          <t>real-time data, automation tools and AI, to name a few.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3411,7 +3421,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>7fd5d1bd270bd5616598a4e10fbe9d4339457256c77c7cb944be0c13105dbe54</t>
+          <t>f38e2dfa91b34f6c162ce065fce285464704c9e0ac64cce8a50ba1e03f945ab9</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3433,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/enabling-the-acceleration-of-all-things-digital.html</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3433,17 +3443,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/enabling-the-acceleration-of-all-things-digital.html</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:23.989694+00:00</t>
+          <t>2026-10-10T15:59:00.582236+00:00</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Deploy risk analysis and scoring methods using software tools that can identify and ultimately stop advanced check alterations, forgeries, counterfeits, out-of-pattern transactions and kiting activities. With automated workflows to capture suspect items, along with the use of historical images, you’ll be able to improve efficiency by reducing false positives and false negatives across multiple transaction types and channels.</t>
+          <t>Complementary groups of data-rich and intelligent tools</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3453,7 +3463,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7fd5d1bd270bd5616598a4e10fbe9d4339457256c77c7cb944be0c13105dbe54</t>
+          <t>f38e2dfa91b34f6c162ce065fce285464704c9e0ac64cce8a50ba1e03f945ab9</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3475,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3475,17 +3485,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:23.989694+00:00</t>
+          <t>2026-10-10T15:59:14.264948+00:00</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Identify check fraud activity with an analysis and forecasting engine that uses neural network algorithms to recognize patterns of suspicious activity, such as deposit fraud and check kiting. Through machine learning and the use of historical transaction data from your account processing system, a benchmark is established for each account type and used to identify suspicious, out-of-pattern activity.</t>
+          <t>leading technology that identifies fraud trends faster, identifies cards for sale on the dark web, and engages with consumers and financial institutions through multiple channels to provide better protection services</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3495,7 +3505,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>7fd5d1bd270bd5616598a4e10fbe9d4339457256c77c7cb944be0c13105dbe54</t>
+          <t>203ecbe73bbb6d5fa4453b937b5a21ea13c57ac97be86b644d642a3f03808984</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3517,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3517,17 +3527,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:27.102712+00:00</t>
+          <t>2026-10-10T15:59:23.989694+00:00</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Real-time risk scoring and interdiction. Transaction time is short; each payment must be evaluated while the transaction is in progress, so real-time decisioning and risk mitigation actions can take place before the payment is submitted for processing.</t>
+          <t>Deploy risk analysis and scoring methods using software tools that can identify and ultimately stop advanced check alterations, forgeries, counterfeits, out-of-pattern transactions and kiting activities.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3537,7 +3547,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1d3c0019028d36c1ec0c2b754b1434b3669edfc02b414759f5b341a283522232</t>
+          <t>7fd5d1bd270bd5616598a4e10fbe9d4339457256c77c7cb944be0c13105dbe54</t>
         </is>
       </c>
     </row>
@@ -3549,7 +3559,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/future-proofing-treasury.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3559,17 +3569,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/future-proofing-treasury.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:33.380466+00:00</t>
+          <t>2026-10-10T15:59:23.989694+00:00</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Many banks are adding digital assistants and embedding AI-driven self-service help tools in their digital banking platforms to deliver a better experience and reduce traffic at the helpdesk.</t>
+          <t>A broad data pool will enable faster and more accurate decisions about whether to accept or reject a presented check, or place a hold on the deposit.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3579,7 +3589,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>cde3daba1f67e6d096e3f34439c4c5c84f527a9cfa99964f80cd1e121a75fbd6</t>
+          <t>7fd5d1bd270bd5616598a4e10fbe9d4339457256c77c7cb944be0c13105dbe54</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3621,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Advanced analytics – Improved analytics includes enabling all forms of AI.</t>
+          <t>Many banks are adding digital assistants and embedding AI-driven self-service help tools in their digital banking platforms to deliver a better experience and reduce traffic at the helpdesk.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3675,7 +3685,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-your-bank-can-evolve-to-face-economic-uncertainty.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/invoice-to-cash-explained-how-ar-is-becoming-a-strategic-growth-engine.html</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3685,17 +3695,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-your-bank-can-evolve-to-face-economic-uncertainty.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/invoice-to-cash-explained-how-ar-is-becoming-a-strategic-growth-engine.html</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:08.494427+00:00</t>
+          <t>2026-10-10T16:00:16.412082+00:00</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Leveraging internal data and predictive analytics gives community banks a leg up, allowing them to forecast potential stress points, adjust underwriting standards and plan more strategically for differing economic scenarios.</t>
+          <t>automated reconciliation and predictive analytics create a closed loop that gives finance teams real-time visibility, earlier signals and far greater control over outcomes.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3705,7 +3715,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>9b92194e0871e826ea5d8f7dc895189c41c5fe0389f07d987705a27321935e76</t>
+          <t>650b552d95e2c5bdc832e6173028fac158719db7db1d2e98e3e2adba62124e43</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3727,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/invoice-to-cash-explained-how-ar-is-becoming-a-strategic-growth-engine.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/strategic-growth-playbook-5-priorities-for-community-banks.html</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3727,17 +3737,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/invoice-to-cash-explained-how-ar-is-becoming-a-strategic-growth-engine.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/strategic-growth-playbook-5-priorities-for-community-banks.html</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:16.412082+00:00</t>
+          <t>2026-10-10T16:00:59.322995+00:00</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Electronic invoice presentment, self-service portals, integrated payment channels, automated reconciliation and predictive analytics create a closed loop that gives finance teams real-time visibility, earlier signals and far greater control over outcomes.</t>
+          <t>Digitizing loan decisioning and processing can cut approval and underwriting times from weeks to days.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3747,7 +3757,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>650b552d95e2c5bdc832e6173028fac158719db7db1d2e98e3e2adba62124e43</t>
+          <t>77acf24969f9b9fd585c7816a5afa0388deeacc835e2fb5a30408b2028332651</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3769,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/strategic-growth-playbook-5-priorities-for-community-banks.html</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3769,17 +3779,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/strategic-growth-playbook-5-priorities-for-community-banks.html</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:49.718239+00:00</t>
+          <t>2026-10-10T16:00:59.322995+00:00</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>intelligent, data-driven personalization</t>
+          <t>Leveraging data and analytics for smarter decisions: With information at their fingertips, banks can feel empowered to determine the right course of action, from using transaction data to forecast liquidity needs to identifying customers at risk of attrition, and take steps to strengthen relationships.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3789,7 +3799,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>cb7849ecf803cb1eef0a646183a50e456a89ce44550c196d75a3c234d72a0507</t>
+          <t>77acf24969f9b9fd585c7816a5afa0388deeacc835e2fb5a30408b2028332651</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3811,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-catalyst-for-change.html</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3811,17 +3821,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-catalyst-for-change.html</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:11.998445+00:00</t>
+          <t>2026-10-10T16:01:04.069624+00:00</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>This gives AI agents clean, contextual and auditable data to power relevant recommendations, dynamic underwriting and explainable decision making.</t>
+          <t>Real-time data is hard to access, making it difficult to deliver personalized offers or fuel AI workflows.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3831,7 +3841,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>d6f4fa7e61fa7c60a727651c3187a2da56c34c975f067ea27f434b8978efe06e</t>
+          <t>29ceae0f8821c07acbc4bed958a564ed64f25010d1998133e51acb1c70e5cf18</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3853,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-programmable-payments.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3853,17 +3863,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-programmable-payments.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:27.917285+00:00</t>
+          <t>2026-10-10T16:01:21.614612+00:00</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Artificial intelligence and machine learning can play a role in recommending the ideal way to pay in a particular situation, lifting the decision burden from the cardholder while optimizing their cash flow.</t>
+          <t>In fraud detection, AI enables organizations to analyze transaction patterns in real time, making it much easier to surface anomalies.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3873,7 +3883,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>7d1cd46e3c594f945fd880fb57c9d0b00aa495dc2a933d40fbef28f51b9abb7f</t>
+          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3895,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-it-really-takes-to-keep-up-with-the-speed-of-commerce.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3895,17 +3905,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-it-really-takes-to-keep-up-with-the-speed-of-commerce.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:43.026793+00:00</t>
+          <t>2026-10-10T16:01:21.614612+00:00</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AI-driven shopping behaviors are reshaping how products are discovered and purchasing decisions are made, with agentic systems that can compare options, select products, place orders and manage replenishment on behalf of consumers.</t>
+          <t>In back-office operations, AI is automating time-consuming tasks such as reconciliation and message correction, giving human operators more opportunity to focus on strategic, high-value work.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3915,7 +3925,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>bd467288d7aa77c46501432756a5ad595f2e7593e7208fa4978a99cf790d112d</t>
+          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3937,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/why-move-to-the-public-cloud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3937,17 +3947,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/why-move-to-the-public-cloud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:51.034050+00:00</t>
+          <t>2026-10-10T16:01:21.614612+00:00</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>provide the opportunity for data analytics and AI-driven insights</t>
+          <t>Customer experience tools can now provide personalized payment servicing through predictive support and real-time issue resolution.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3957,7 +3967,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>dfd2abc35ffadbc4aedf3794eb57675a3d8ec8e0f5377fa338184cd0595d40cd</t>
+          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
         </is>
       </c>
     </row>
@@ -3969,27 +3979,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tier_A</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-10T15:55:37.573244+00:00</t>
+          <t>2026-10-10T16:01:21.614612+00:00</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>bad actors increasingly use artificial intelligence to identify, automate, and exploit technology vulnerabilities at greater speed and scale</t>
+          <t>AI's ability to extract deep insights from payments data can support smarter business decisions, shaping everything from pricing strategies to liquidity management.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3999,7 +4009,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>c8ae42b7ee474576c84822b5f8d2a9e306f7e26ed7e7a10c1198ff5990595d35</t>
+          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4021,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4021,17 +4031,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:17.989440+00:00</t>
+          <t>2026-10-10T16:01:21.614612+00:00</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AI is no longer novel, it’s part of everyday life for many adults, 70% of whom say they use it a few times a week according to internal Fiserv data.</t>
+          <t>Intelligent routing makes it possible for AI to analyze historical payment patterns to select the optimal clearing channels for transactions.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4041,7 +4051,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>e0c16da5e0626951b34c1e145f27b18f2f6d77a1e8234f2a533060bd3d7a8466</t>
+          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
         </is>
       </c>
     </row>
@@ -4053,7 +4063,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4063,17 +4073,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:17.989440+00:00</t>
+          <t>2026-10-10T16:01:21.614612+00:00</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AI can help institutions make the most of each interaction by taking on routine calls, texts and chats, securely accessing customer data to provide automated, seamless support.</t>
+          <t>Even payment repair is improved, with AI able to connect to internal systems and, when paired with human oversight, execute repair steps automatically for failed transactions, thereby increasing speed and accuracy.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4083,7 +4093,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>e0c16da5e0626951b34c1e145f27b18f2f6d77a1e8234f2a533060bd3d7a8466</t>
+          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4105,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/real-time-data--the-untapped-growth-engine-for-platform-business.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-programmable-payments.html</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4105,17 +4115,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/real-time-data--the-untapped-growth-engine-for-platform-business.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-programmable-payments.html</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:43.395500+00:00</t>
+          <t>2026-10-10T16:01:27.917285+00:00</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>9/10 firms have used GenAI to obtain and analyze payments and transaction data</t>
+          <t>Artificial intelligence and machine learning can play a role in recommending the ideal way to pay in a particular situation, lifting the decision burden from the cardholder while optimizing their cash flow.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4125,7 +4135,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>84d6116d7c56f3ec2213b114ece35a9bd276e16a314513a73c863d98b7371614</t>
+          <t>7d1cd46e3c594f945fd880fb57c9d0b00aa495dc2a933d40fbef28f51b9abb7f</t>
         </is>
       </c>
     </row>
@@ -4137,7 +4147,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4147,17 +4157,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:57.710588+00:00</t>
+          <t>2026-10-10T16:01:29.483063+00:00</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>using AI for financial advice</t>
+          <t>Credit scoring, fraud detection and process automation have long been areas assisted by AI and machine learning, but new advances in generative AI and large language models (LLMs) can take them to the next level.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4167,7 +4177,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
+          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4189,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4189,17 +4199,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:57.710588+00:00</t>
+          <t>2026-10-10T16:01:29.483063+00:00</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AI-powered banking</t>
+          <t>automating time-intensive reporting such as audit reports, reconciliation and initial KYC analysis to understand if a potential customer will be verifiable will shape operations in years to come.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4209,7 +4219,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
+          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4231,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-it-really-takes-to-keep-up-with-the-speed-of-commerce.html</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4231,17 +4241,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-it-really-takes-to-keep-up-with-the-speed-of-commerce.html</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:57.710588+00:00</t>
+          <t>2026-10-10T16:01:43.026793+00:00</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>voice-activated, conversational AI like Siri or Alexa</t>
+          <t>AI-driven shopping behaviors are reshaping how products are discovered and purchasing decisions are made, with agentic systems that can compare options, select products, place orders and manage replenishment on behalf of consumers.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4251,7 +4261,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
+          <t>bd467288d7aa77c46501432756a5ad595f2e7593e7208fa4978a99cf790d112d</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4273,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-it-really-takes-to-keep-up-with-the-speed-of-commerce.html</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4273,17 +4283,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-it-really-takes-to-keep-up-with-the-speed-of-commerce.html</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:57.710588+00:00</t>
+          <t>2026-10-10T16:01:43.026793+00:00</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>generative AI, like the technology behind ChatGPT</t>
+          <t>And as commerce continues to evolve toward agentic models, AI-driven purchasing and new forms of digital interaction, enterprises need infrastructure that is already prepared for those shifts: secure, tokenized, authenticated and designed for machine-initiated transactions as well as human ones.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4293,7 +4303,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
+          <t>bd467288d7aa77c46501432756a5ad595f2e7593e7208fa4978a99cf790d112d</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4315,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-catalyst-for-change.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/why-move-to-the-public-cloud.html</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4315,17 +4325,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-catalyst-for-change.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/why-move-to-the-public-cloud.html</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:04.069624+00:00</t>
+          <t>2026-10-10T16:01:51.034050+00:00</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>and AI-powered services.</t>
+          <t>Moving to a public cloud accessing data from across the organization on a single platform can provide the opportunity for data analytics and AI-driven insights.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4335,7 +4345,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>29ceae0f8821c07acbc4bed958a564ed64f25010d1998133e51acb1c70e5cf18</t>
+          <t>dfd2abc35ffadbc4aedf3794eb57675a3d8ec8e0f5377fa338184cd0595d40cd</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4357,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-catalyst-for-change.html</t>
+          <t>https://www.fiserv.com/en/insights/businesses-and-merchants.html</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4357,17 +4367,18 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-catalyst-for-change.html</t>
+          <t>https://www.fiserv.com/en/insights/businesses-and-merchants.html</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:04.069624+00:00</t>
+          <t>2026-10-10T16:01:56.449520+00:00</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Real-time data is hard to access, making it difficult to deliver personalized offers or fuel AI workflows.</t>
+          <t>Agentic commerce is here: What merchants need to know and do
+How AI-powered agents are already reshaping commerce, and how merchants can prepare to protect identity, loyalty and payments.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4377,7 +4388,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>29ceae0f8821c07acbc4bed958a564ed64f25010d1998133e51acb1c70e5cf18</t>
+          <t>70f21ebf8b872d3414d5a01ad50f36f6dbbb470e5ab9383d2d85d510cbffc2ac</t>
         </is>
       </c>
     </row>
@@ -4389,37 +4400,37 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/in-person-payments.html</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_D</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/in-person-payments.html</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:29.483063+00:00</t>
+          <t>2026-10-10T16:18:36.540068+00:00</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AI is enabling more effective service and fraud detection in call center operations through improved real-time sentiment analysis of the caller’s voice, tone and language.</t>
+          <t>Manage your portfolio with our partner portal, CoPilot from Fiserv, where you can order pre-provisioned devices, track orders and activate your devices.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>INDICATIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
+          <t>3058175eb22db2dce8f16f8b4ae7f7a8b4b4720ae755dcfd4379cdc4a7c2836f</t>
         </is>
       </c>
     </row>
@@ -4431,37 +4442,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/partner-support.html</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_D</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/partner-support.html</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:29.483063+00:00</t>
+          <t>2026-10-10T16:18:43.822639+00:00</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>automating time-intensive reporting such as audit reports, reconciliation and initial KYC analysis to understand if a potential customer will be verifiable will shape operations in years to come.</t>
+          <t>Operate efficiently at scale with our CoPilot partner portfolio management system and manage everything from merchant enrollment to risk monitoring and user support.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>INDICATIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
+          <t>8dd58af9ccba196f3230d88f181ec520cb4b0fb65eb082fdd0c96b03eca41f48</t>
         </is>
       </c>
     </row>
@@ -4473,37 +4484,37 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/solutions/risk-compliance/aml-risk-manager.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tier_A</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/solutions/risk-compliance/aml-risk-manager.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-10T15:55:53.603656+00:00</t>
+          <t>2026-10-10T15:58:10.845485+00:00</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Leverage AI-driven risk scoring to analyze transaction patterns and customer behavior in real time.</t>
+          <t>AI solutions are now bringing automation capabilities to check fraud prevention</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>bbf9f86093b9ffb25ab6aed003eaf13162c0712252e6bdfdd50cf8312e0dbda0</t>
+          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4526,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/4-ways-to-elevate-card-programs-for-both-issuers-and-cardholders.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/real-time-data--the-untapped-growth-engine-for-platform-business.html</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4525,17 +4536,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/4-ways-to-elevate-card-programs-for-both-issuers-and-cardholders.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/real-time-data--the-untapped-growth-engine-for-platform-business.html</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:04.576694+00:00</t>
+          <t>2026-10-10T16:00:43.395500+00:00</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>analytics-backed insights</t>
+          <t>9/10 firms have used GenAI to obtain and analyze payments and transaction data</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4545,7 +4556,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>fda559e724cc2e3ff4c4d2fe09dc6aef85231ca89b4289b3e3537dd932ace24a</t>
+          <t>84d6116d7c56f3ec2213b114ece35a9bd276e16a314513a73c863d98b7371614</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4568,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/4-ways-to-elevate-card-programs-for-both-issuers-and-cardholders.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4567,17 +4578,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/4-ways-to-elevate-card-programs-for-both-issuers-and-cardholders.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:04.576694+00:00</t>
+          <t>2026-10-10T16:00:57.710588+00:00</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Advanced fraud detection systems</t>
+          <t>using AI for financial advice</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4587,7 +4598,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>fda559e724cc2e3ff4c4d2fe09dc6aef85231ca89b4289b3e3537dd932ace24a</t>
+          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4610,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/drive-more-commerce-with-carat.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4609,17 +4620,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/drive-more-commerce-with-carat.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:54.090582+00:00</t>
+          <t>2026-10-10T16:00:57.710588+00:00</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>That’s why Carat delivers advanced security, fraud prevention and optimization tools.</t>
+          <t>AI-powered banking</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4629,7 +4640,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>35a48eeb9e0acb60d593968be5c3ad1c16ea3a72e1dd26779275567cb1e042b0</t>
+          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4652,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4651,17 +4662,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:14.264948+00:00</t>
+          <t>2026-10-10T16:00:57.710588+00:00</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>identifies cards for sale on the dark web</t>
+          <t>voice-activated, conversational AI like Siri or Alexa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4671,7 +4682,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>203ecbe73bbb6d5fa4453b937b5a21ea13c57ac97be86b644d642a3f03808984</t>
+          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4694,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4693,17 +4704,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fiserv-focuses-on-fraud-detection.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:14.264948+00:00</t>
+          <t>2026-10-10T16:00:57.710588+00:00</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>insight from data analysis using the latest technology and expertise can pinpoint suspicious behavior to detect and prevent fraud before it happens</t>
+          <t>generative AI, like the technology behind ChatGPT</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4713,7 +4724,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>203ecbe73bbb6d5fa4453b937b5a21ea13c57ac97be86b644d642a3f03808984</t>
+          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
         </is>
       </c>
     </row>
@@ -4725,27 +4736,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-it/solutions/manage-risk-and-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-it/solutions/manage-risk-and-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/smarter-money-management.html</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-10T16:07:03.125696+00:00</t>
+          <t>2026-10-10T16:00:57.710588+00:00</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>predictive neural networks</t>
+          <t>generative AI’s potential for financial support</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4755,7 +4766,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>359cd9ceab797b44019327610ad2f81b8163d2d388dd8624f8b1e78c31d2d926</t>
+          <t>d600d13ebc00c7a9b513017201c55a7be8ff3474fe6925ca0e5a58d92da9ae79</t>
         </is>
       </c>
     </row>
@@ -4767,27 +4778,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-me/solutions/manage-risk-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-me/solutions/manage-risk-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-10T16:07:47.697392+00:00</t>
+          <t>2026-10-10T16:01:11.998445+00:00</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>predictive neural networks</t>
+          <t>Generative AI has become one of the most powerful tools for reimagining customer service, product design and back-office operations.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4797,7 +4808,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>aba8c3326b3a57c028fa4281e03f8c89f1161e56af59274b887a4844207be79f</t>
+          <t>d6f4fa7e61fa7c60a727651c3187a2da56c34c975f067ea27f434b8978efe06e</t>
         </is>
       </c>
     </row>
@@ -4809,27 +4820,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-me/solutions/manage-risk-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-me/solutions/manage-risk-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-10T16:07:47.697392+00:00</t>
+          <t>2026-10-10T16:01:29.483063+00:00</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>use a mixture of artificial and automated intelligence, machine learning, and robotics</t>
+          <t>ChatGPT has become a regular part of everyday conversation.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4839,7 +4850,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>aba8c3326b3a57c028fa4281e03f8c89f1161e56af59274b887a4844207be79f</t>
+          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
         </is>
       </c>
     </row>
@@ -4851,27 +4862,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-uk/financial-institutions/manage-risk-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-uk/financial-institutions/manage-risk-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-10T16:10:10.056857+00:00</t>
+          <t>2026-10-10T16:01:29.483063+00:00</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>use of global data and predictive neural networks, our solutions make it harder and more challenging for fraudsters.</t>
+          <t>ChatGPT reached 100 million active users in just 2 months.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4881,7 +4892,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2fcb018b0a3d83178be7a0df584ba9fca30b3ac7b3eae7019be03112fc64b053</t>
+          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
         </is>
       </c>
     </row>
@@ -4893,27 +4904,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-uk/financial-institutions/manage-risk-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-uk/financial-institutions/manage-risk-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-10T16:10:10.056857+00:00</t>
+          <t>2026-10-10T16:01:29.483063+00:00</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Our award-winning fraud and Anti-Money Laundering (AML) technologies use a mixture of artificial and automated intelligence, machine learning, and robotics to improve your operational efficiency, deliver rich analytics and strategic evaluation, reduce your costs, and fine-tune risk exposure.</t>
+          <t>If you’ve used ChatGPT, you are using an LLM. If you use Bing Search, you are using an LLM,</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4923,7 +4934,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2fcb018b0a3d83178be7a0df584ba9fca30b3ac7b3eae7019be03112fc64b053</t>
+          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4946,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/who-we-serve/enterprise/reporting-and-analytics.html</t>
+          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4945,17 +4956,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/who-we-serve/enterprise/reporting-and-analytics.html</t>
+          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-10T16:18:23.207046+00:00</t>
+          <t>2026-10-10T16:16:48.520050+00:00</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>early-warning intelligence powered by Fiserv.</t>
+          <t>| 
+|---|---|
+|  | Infrastructure protection Mitigate and manage potential business disruption with behavior analytics, machine learning and professionally managed computing services from Fiserv to secure your infrastructure, back office and data.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4965,7 +4978,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>f61a3c7f790aefdf9680057a8c3043f34700fe432818fe132243d0c291e0d2a2</t>
+          <t>db2b1269d91228c705dabdad0653e298cb023eb103f956b5da090f04a38a3bdc</t>
         </is>
       </c>
     </row>
@@ -4977,27 +4990,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/who-we-serve/enterprise/reporting-and-analytics.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/who-we-serve/enterprise/reporting-and-analytics.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-10T16:18:23.207046+00:00</t>
+          <t>2026-10-10T15:58:15.552514+00:00</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Leverage automation and AI-supported capabilities to reduce manual effort and improve consistency.</t>
+          <t>Their artificial intelligence agent will.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5007,7 +5020,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>f61a3c7f790aefdf9680057a8c3043f34700fe432818fe132243d0c291e0d2a2</t>
+          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5032,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/community-banking-modernizing-with-confidence.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5029,27 +5042,27 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/community-banking-modernizing-with-confidence.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:37.516984+00:00</t>
+          <t>2026-10-10T15:58:15.552514+00:00</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AI acceleration</t>
+          <t>Agentic commerce, in which autonomous AI agents evaluate, compare or even purchase on a shopper’s behalf, is already reshaping digital interactions.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>088efbad3d4fdf3b48fc2734ad45b8aec830f7de6b69889b1287fc3697f93391</t>
+          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5074,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/community-banking-modernizing-with-confidence.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5071,27 +5084,27 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/community-banking-modernizing-with-confidence.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:37.516984+00:00</t>
+          <t>2026-10-10T15:58:15.552514+00:00</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>New capabilities – think AI and cloud – can be accelerators, but should be aligned to intentional business outcomes</t>
+          <t>Instead of a human clicking through a page, an autonomous AI program evaluates your products, your policies and your data, and decides if you make the shortlist.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>088efbad3d4fdf3b48fc2734ad45b8aec830f7de6b69889b1287fc3697f93391</t>
+          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5116,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/community-banking-modernizing-with-confidence.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5113,27 +5126,27 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/community-banking-modernizing-with-confidence.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:37.516984+00:00</t>
+          <t>2026-10-10T15:58:15.552514+00:00</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>pairing the core with AI to get answers faster</t>
+          <t>Transactions may originate from third-party AI systems using cards, tokens or emerging network credentials.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>088efbad3d4fdf3b48fc2734ad45b8aec830f7de6b69889b1287fc3697f93391</t>
+          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5158,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5155,27 +5168,27 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:02.171467+00:00</t>
+          <t>2026-10-10T15:58:15.552514+00:00</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>It enables confident adoption of cloud services, analytics platforms and AI tools</t>
+          <t>AI agents favor businesses whose data is clear, consistent and transaction‑ready.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>070169cf4dd71519acd1ce65c3b767ff9c68c0dbc5ff7a03d8c856f5ae12fd69</t>
+          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5200,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5197,27 +5210,27 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-data-foundations-merchants.html</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:02.171467+00:00</t>
+          <t>2026-10-10T15:58:15.552514+00:00</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>EaaS safely accelerates AI enablement</t>
+          <t>AI agents will consume structured business logic directly, comparing return policies, fulfillment SLAs, sustainability commitments and more</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>070169cf4dd71519acd1ce65c3b767ff9c68c0dbc5ff7a03d8c856f5ae12fd69</t>
+          <t>c9c0188433e144b4e170d1328fed00b34ea1997fccc4764d6e2768f1b4a53321</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5242,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/analytics-teams-real-time-data-accelerate-growth-for-gaming-platforms.html</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5239,27 +5252,27 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/analytics-teams-real-time-data-accelerate-growth-for-gaming-platforms.html</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:02.171467+00:00</t>
+          <t>2026-10-10T15:58:20.276343+00:00</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AI without strong data governance introduces risk</t>
+          <t>using data for predictive analytics and decision making</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>070169cf4dd71519acd1ce65c3b767ff9c68c0dbc5ff7a03d8c856f5ae12fd69</t>
+          <t>6dedcb01a708f7fa0c4017895c7cbd9aeecc8b675ffc30c1b7a0785bfd1e7ec1</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5284,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/community-banking-modernizing-with-confidence.html</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5281,27 +5294,28 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/community-banking-modernizing-with-confidence.html</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:02.171467+00:00</t>
+          <t>2026-10-10T15:58:37.516984+00:00</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>EaaS supports responsible AI adoption by ensuring sensitive data is classified, protected and governed before entering AI workflows</t>
+          <t>Together, these factors make it more critical than ever for banks, credit unions, and fintechs to deliver a truly robust digital experience."
+To capture this opportunity, Stewart Russell says core data and AI are essential and can enable experiences like predictive insights, proactive issue identification, automation and enhanced security.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>070169cf4dd71519acd1ce65c3b767ff9c68c0dbc5ff7a03d8c856f5ae12fd69</t>
+          <t>088efbad3d4fdf3b48fc2734ad45b8aec830f7de6b69889b1287fc3697f93391</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5327,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5323,27 +5337,27 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:02.171467+00:00</t>
+          <t>2026-10-10T15:59:27.102712+00:00</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>That enables privacy-preserving analytics so financial institutions can extract insights without exposing personally identifiable information</t>
+          <t>Now, with access to faster and cheaper computing, as well as use of AI-assisted fraud tools, criminals have elevated their game and shifted their targets to weaker, more profitable points in the financial services chain.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>070169cf4dd71519acd1ce65c3b767ff9c68c0dbc5ff7a03d8c856f5ae12fd69</t>
+          <t>1d3c0019028d36c1ec0c2b754b1434b3669edfc02b414759f5b341a283522232</t>
         </is>
       </c>
     </row>
@@ -5355,7 +5369,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/future-proofing-treasury.html</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5365,27 +5379,27 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/encryption-as-a-service-holds-the-promise-of-modernization.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/future-proofing-treasury.html</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:02.171467+00:00</t>
+          <t>2026-10-10T15:59:33.380466+00:00</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>The process can assist in reducing the likelihood of model leakage, data misuse or noncompliant outputs</t>
+          <t>turn AI, new payment instruments and ecosystem strategies into measurable outcomes.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>070169cf4dd71519acd1ce65c3b767ff9c68c0dbc5ff7a03d8c856f5ae12fd69</t>
+          <t>cde3daba1f67e6d096e3f34439c4c5c84f527a9cfa99964f80cd1e121a75fbd6</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5411,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-financial-institutions-can-compete-digitally-and-win.html</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5407,27 +5421,27 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-financial-institutions-can-compete-digitally-and-win.html</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:21.614612+00:00</t>
+          <t>2026-10-10T15:59:49.238011+00:00</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>In fraud detection, AI enables organizations to analyze transaction patterns in real time, making it much easier to surface anomalies.</t>
+          <t>Large language models can quickly dig deep into customers’ financial data and offer personalized advice or assistance, freeing up human bankers to do more complex tasks.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
+          <t>2b10adf13d9f7a73dc07da19a30f4bc2c629ad214c6cae15ca76b73905d1da90</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5453,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-financial-institutions-can-compete-digitally-and-win.html</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5449,27 +5463,27 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-financial-institutions-can-compete-digitally-and-win.html</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:21.614612+00:00</t>
+          <t>2026-10-10T15:59:49.238011+00:00</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>In back-office operations, AI is automating time-consuming tasks such as reconciliation and message correction, giving human operators more opportunity to focus on strategic, high-value work.</t>
+          <t>70% of young and middle-aged adults use AI a few times each week, according to internal Fiserv research.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
+          <t>2b10adf13d9f7a73dc07da19a30f4bc2c629ad214c6cae15ca76b73905d1da90</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5495,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5491,27 +5505,27 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:21.614612+00:00</t>
+          <t>2026-10-10T16:00:17.989440+00:00</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Customer experience tools can now provide personalized payment servicing through predictive support and real-time issue resolution.</t>
+          <t>AI is no longer novel, it’s part of everyday life for many adults, 70% of whom say they use it a few times a week according to internal Fiserv data.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
+          <t>e0c16da5e0626951b34c1e145f27b18f2f6d77a1e8234f2a533060bd3d7a8466</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5537,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5533,27 +5547,27 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:21.614612+00:00</t>
+          <t>2026-10-10T16:00:17.989440+00:00</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AI's ability to extract deep insights from payments data can support smarter business decisions, shaping everything from pricing strategies to liquidity management.</t>
+          <t>AI can help institutions make the most of each interaction by taking on routine calls, texts and chats, securely accessing customer data to provide automated, seamless support.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
+          <t>e0c16da5e0626951b34c1e145f27b18f2f6d77a1e8234f2a533060bd3d7a8466</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5579,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5575,27 +5589,27 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:21.614612+00:00</t>
+          <t>2026-10-10T16:00:17.989440+00:00</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>An AI-powered payments navigator can act as a dedicated, expert assistant and provide an explanation of the error code, remedial steps and even preventative recommendations.</t>
+          <t>just 42% of Chief Experience Officers plan to leverage AI to transform customer experiences.</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
+          <t>e0c16da5e0626951b34c1e145f27b18f2f6d77a1e8234f2a533060bd3d7a8466</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5621,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5617,27 +5631,27 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:21.614612+00:00</t>
+          <t>2026-10-10T16:00:49.718239+00:00</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Intelligent routing makes it possible for AI to analyze historical payment patterns to select the optimal clearing channels for transactions.</t>
+          <t>intelligent, data-driven personalization</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
+          <t>cb7849ecf803cb1eef0a646183a50e456a89ce44550c196d75a3c234d72a0507</t>
         </is>
       </c>
     </row>
@@ -5649,7 +5663,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5659,27 +5673,27 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:21.614612+00:00</t>
+          <t>2026-10-10T16:01:11.998445+00:00</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Even payment repair is improved, with AI able to connect to internal systems and, when paired with human oversight, execute repair steps automatically for failed transactions, thereby increasing speed and accuracy.</t>
+          <t>McKinsey research shows banks that embed AI into engineering workflows are already seeing about ~40% productivity gains.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
+          <t>d6f4fa7e61fa7c60a727651c3187a2da56c34c975f067ea27f434b8978efe06e</t>
         </is>
       </c>
     </row>
@@ -5711,12 +5725,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Increasingly, an AI agent can handle the sequence: scan recent transaction patterns for early warning signals, identify who’s at risk and push out customized offers – before the customer quietly moves on.</t>
+          <t>The last part – not just identifying but making decisions and taking actions – is what defines “agentic AI” as fundamentally different from chatbot-style Q&amp;A interfaces.</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5753,12 +5767,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>For example, an agent might spot a suspicious pattern, gather the right context, initiate the appropriate action and prepare the documentation a reviewer or regulator expects.</t>
+          <t>Agentic AI goes beyond predefined workflows and rules-based robotic process automation.</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5775,7 +5789,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/drive-more-commerce-with-carat.html</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5785,17 +5799,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/drive-more-commerce-with-carat.html</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:35.805808+00:00</t>
+          <t>2026-10-10T15:58:54.090582+00:00</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Smarter recommendations: agents that combine call transcripts and account activity to surface relevant products or advice, with context a banker can trust.</t>
+          <t>We use machine learning for smarter outcomes</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5805,7 +5819,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>9e68a548aa5556c99d7bd1ef77c4c78f627fb87378bd505d306c91b782595ab2</t>
+          <t>35a48eeb9e0acb60d593968be5c3ad1c16ea3a72e1dd26779275567cb1e042b0</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5831,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5827,17 +5841,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/four-steps-to-better-check-fraud-protection.html</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:35.805808+00:00</t>
+          <t>2026-10-10T15:59:23.989694+00:00</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Operational triage: agents that route exceptions, collect missing information, and move work to resolution instead of creating more queues.</t>
+          <t>Establishing intelligent deposit limits for deposit accounts can reduce risk for your financial institution while rewarding good accountholders with higher deposit limits.</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5847,7 +5861,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>9e68a548aa5556c99d7bd1ef77c4c78f627fb87378bd505d306c91b782595ab2</t>
+          <t>7fd5d1bd270bd5616598a4e10fbe9d4339457256c77c7cb944be0c13105dbe54</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5873,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-financial-institutions-can-compete-digitally-and-win.html</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5869,17 +5883,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-financial-institutions-can-compete-digitally-and-win.html</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:35.805808+00:00</t>
+          <t>2026-10-10T15:59:49.238011+00:00</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Commercial lending support: agents that continuously absorb internal performance data alongside external signals to help manage exposure, covenants and portfolio health.</t>
+          <t>The digital banking platform was designed with AI integrations in mind.</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5889,7 +5903,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>9e68a548aa5556c99d7bd1ef77c4c78f627fb87378bd505d306c91b782595ab2</t>
+          <t>2b10adf13d9f7a73dc07da19a30f4bc2c629ad214c6cae15ca76b73905d1da90</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5915,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5911,27 +5925,27 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:13.971042+00:00</t>
+          <t>2026-10-10T16:00:17.989440+00:00</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Provide broader, deeper data and AI-driven insights across industries and technologies</t>
+          <t>When financial institutions use this AI-powered tool, 80% of calls are answered within 15 seconds, average handle time is cut by 30 seconds, and customer experience increases by 15%.</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>INDICATIVE</t>
+          <t>MARKETING-ONLY</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>99179c0ac4fcebf059b90e9db72972077025d5446c7a7f1d12a8d091a62770d5</t>
+          <t>e0c16da5e0626951b34c1e145f27b18f2f6d77a1e8234f2a533060bd3d7a8466</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5957,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5953,27 +5967,27 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:13.971042+00:00</t>
+          <t>2026-10-10T16:00:17.989440+00:00</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Chiarello made it clear that Fiserv has been, and will continue, investing in AI across the portfolio.</t>
+          <t>LinkLive integrates seamlessly with Experience Digital from Fiserv to work in tandem with human call center agents.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>INDICATIVE</t>
+          <t>MARKETING-ONLY</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>99179c0ac4fcebf059b90e9db72972077025d5446c7a7f1d12a8d091a62770d5</t>
+          <t>e0c16da5e0626951b34c1e145f27b18f2f6d77a1e8234f2a533060bd3d7a8466</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5999,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-how-financial-institutions-can-get-the-most-out-of-tech-upgrades.html</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5995,17 +6009,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/fraud-mitigation-in-an-age-of-real-time-payments.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-how-financial-institutions-can-get-the-most-out-of-tech-upgrades.html</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:27.102712+00:00</t>
+          <t>2026-10-10T15:58:43.020266+00:00</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Now, with access to faster and cheaper computing, as well as use of AI-assisted fraud tools, criminals have elevated their game and shifted their targets to weaker, more profitable points in the financial services chain.</t>
+          <t>AI-powered fraud prevention tools</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6015,7 +6029,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1d3c0019028d36c1ec0c2b754b1434b3669edfc02b414759f5b341a283522232</t>
+          <t>193b8a323cc5fa25418e0f44b8f94bb071a83155dd1dd864d6396dcd90763b45</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6061,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>AI agents – An AI agent is software code that uses AI to understand the business domain and use that understanding to execute actions and achieve specific goals.</t>
+          <t>Advanced analytics – Improved analytics includes enabling all forms of AI.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6069,7 +6083,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-financial-institutions-can-compete-digitally-and-win.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/future-proofing-treasury.html</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6079,17 +6093,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-financial-institutions-can-compete-digitally-and-win.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/future-proofing-treasury.html</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:49.238011+00:00</t>
+          <t>2026-10-10T15:59:33.380466+00:00</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Large language models can quickly dig deep into customers’ financial data and offer personalized advice or assistance, freeing up human bankers to do more complex tasks.</t>
+          <t>AI agents – An AI agent is software code that uses AI to understand the business domain and use that understanding to execute actions and achieve specific goals.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6099,7 +6113,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2b10adf13d9f7a73dc07da19a30f4bc2c629ad214c6cae15ca76b73905d1da90</t>
+          <t>cde3daba1f67e6d096e3f34439c4c5c84f527a9cfa99964f80cd1e121a75fbd6</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6125,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-financial-institutions-can-compete-digitally-and-win.html</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6121,17 +6135,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/is-your-financial-institution-keeping-up-with-digital-evolution.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-financial-institutions-can-compete-digitally-and-win.html</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-10T16:00:17.989440+00:00</t>
+          <t>2026-10-10T15:59:49.238011+00:00</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>just 42% of Chief Experience Officers plan to leverage AI to transform customer experiences.</t>
+          <t>Artificial intelligence is rapidly becoming integrated into every facet of consumers’ lives</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -6141,7 +6155,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>e0c16da5e0626951b34c1e145f27b18f2f6d77a1e8234f2a533060bd3d7a8466</t>
+          <t>2b10adf13d9f7a73dc07da19a30f4bc2c629ad214c6cae15ca76b73905d1da90</t>
         </is>
       </c>
     </row>
@@ -6153,27 +6167,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+          <t>https://www.fiserv.com/en-em/solutions/manage-risk-fraud.html</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_D</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+          <t>https://www.fiserv.com/en-em/solutions/manage-risk-fraud.html</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:11.998445+00:00</t>
+          <t>2026-10-10T16:05:20.639179+00:00</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>banks that embed AI into engineering workflows are already seeing about ~40% productivity gains.</t>
+          <t>Our award-winning fraud and Anti-Money Laundering (AML) technologies use a mixture of artificial and automated intelligence, machine learning, and robotics to improve your operational efficiency, deliver rich analytics and strategic evaluation, reduce your costs, and fine-tune risk exposure.</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -6183,7 +6197,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>d6f4fa7e61fa7c60a727651c3187a2da56c34c975f067ea27f434b8978efe06e</t>
+          <t>037a7bac331d71f63311e156b60e25e3933f913cb6d76b482503d986f7164778</t>
         </is>
       </c>
     </row>
@@ -6195,27 +6209,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en-it/solutions/manage-risk-and-fraud.html</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_D</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en-it/solutions/manage-risk-and-fraud.html</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:29.483063+00:00</t>
+          <t>2026-10-10T16:07:03.125696+00:00</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Credit scoring, fraud detection and process automation have long been areas assisted by AI and machine learning, but new advances in generative AI and large language models (LLMs) can take them to the next level.</t>
+          <t>Our award-winning fraud and Anti-Money Laundering (AML) technologies use a mixture of artificial and automated intelligence, machine learning, and robotics to improve your operational efficiency, deliver rich analytics and strategic evaluation, reduce your costs, and fine-tune risk exposure.</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6225,7 +6239,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
+          <t>359cd9ceab797b44019327610ad2f81b8163d2d388dd8624f8b1e78c31d2d926</t>
         </is>
       </c>
     </row>
@@ -6237,27 +6251,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en-me/solutions/manage-risk-fraud.html</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_D</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.fiserv.com/en-me/solutions/manage-risk-fraud.html</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:29.483063+00:00</t>
+          <t>2026-10-10T16:07:47.697392+00:00</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>I like the word that Microsoft uses: they think of these tools as co-pilots.</t>
+          <t>Our award-winning fraud and Anti-Money Laundering (AML) technologies use a mixture of artificial and automated intelligence, machine learning, and robotics to improve your operational efficiency, deliver rich analytics and strategic evaluation, reduce your costs, and fine-tune risk exposure.</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6267,7 +6281,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
+          <t>aba8c3326b3a57c028fa4281e03f8c89f1161e56af59274b887a4844207be79f</t>
         </is>
       </c>
     </row>
@@ -6279,27 +6293,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+          <t>https://www.fiserv.com/en-pl/financial-institutions/manage-risk-fraud.html</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_D</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+          <t>https://www.fiserv.com/en-pl/financial-institutions/manage-risk-fraud.html</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:31.068758+00:00</t>
+          <t>2026-10-10T16:09:14.693659+00:00</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Over 90% of retailers surveyed now leverage GenAI to analyze transaction data for various purposes.</t>
+          <t>Our award-winning fraud and Anti-Money Laundering (AML) technologies use a mixture of artificial and automated intelligence, machine learning, and robotics to improve your operational efficiency, deliver rich analytics and strategic evaluation, reduce your costs, and fine-tune risk exposure.</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6309,7 +6323,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>56108dc2fba7dfbfd2b48a1eebd3de1eff62387bc8117916a166eca4d481cf93</t>
+          <t>9478dbb9730718ea4f71685c2350e60c496c70df3e26dacfe9e8b52caaf6dc02</t>
         </is>
       </c>
     </row>
@@ -6321,27 +6335,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+          <t>https://www.fiserv.com/en-uk/financial-institutions/manage-risk-fraud.html</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_D</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+          <t>https://www.fiserv.com/en-uk/financial-institutions/manage-risk-fraud.html</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:31.068758+00:00</t>
+          <t>2026-10-10T16:10:10.056857+00:00</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Common applications include data privacy and security (58%), customer segmentation (54%) and forecasting (53%).</t>
+          <t>Our award-winning fraud and Anti-Money Laundering (AML) technologies use a mixture of artificial and automated intelligence, machine learning, and robotics to improve your operational efficiency, deliver rich analytics and strategic evaluation, reduce your costs, and fine-tune risk exposure.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6351,7 +6365,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>56108dc2fba7dfbfd2b48a1eebd3de1eff62387bc8117916a166eca4d481cf93</t>
+          <t>2fcb018b0a3d83178be7a0df584ba9fca30b3ac7b3eae7019be03112fc64b053</t>
         </is>
       </c>
     </row>
@@ -6363,37 +6377,38 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/drive-more-commerce-with-carat.html</t>
+          <t>https://www.fiserv.com/en/about-fiserv/corporate-social-responsibility.html</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_D</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/drive-more-commerce-with-carat.html</t>
+          <t>https://www.fiserv.com/en/about-fiserv/corporate-social-responsibility.html</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:54.090582+00:00</t>
+          <t>2026-10-10T16:10:32.850587+00:00</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>We use machine learning for smarter outcomes, leverage biometrics to secure devices, and continue to deliver tailored experiences to protect both the customer and the merchant.</t>
+          <t>Powering responsible innovation
+A cross-functional governance structure oversees implementation of responsible AI and machine learning capabilities, establishing standards for the appropriate use of new technologies.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>35a48eeb9e0acb60d593968be5c3ad1c16ea3a72e1dd26779275567cb1e042b0</t>
+          <t>9b4430e551d08a82fe17a2c378aa2723c53385af4c002e9a7633e54818fcbc6d</t>
         </is>
       </c>
     </row>
@@ -6405,37 +6420,37 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+          <t>https://www.fiserv.com/en/about-fiserv/terms-of-use.html</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_D</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+          <t>https://www.fiserv.com/en/about-fiserv/terms-of-use.html</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:11.998445+00:00</t>
+          <t>2026-10-10T16:11:41.113831+00:00</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AI-powered services</t>
+          <t>GIVEN THE PROBABILISTIC NATURE OF MACHINE LEARNING, THE INTERACTIVE FEATURES MAY IN SOME SITUATIONS PRODUCE OUTPUT THAT IS INACCURATE, INCORRECT, OFFENSIVE OR OTHERWISE UNDESIRABLE.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>d6f4fa7e61fa7c60a727651c3187a2da56c34c975f067ea27f434b8978efe06e</t>
+          <t>bfa8380add2a09707c87d75789ead3d56ecc14c33b8026f0aadb82881934be0d</t>
         </is>
       </c>
     </row>
@@ -6447,37 +6462,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+          <t>https://www.fiserv.com/en/who-we-serve/enterprise/commerce-control-center.html</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_D</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+          <t>https://www.fiserv.com/en/who-we-serve/enterprise/commerce-control-center.html</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:11.998445+00:00</t>
+          <t>2026-10-10T16:18:11.077288+00:00</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Generative AI has become one of the most powerful tools for reimagining customer service, product design and back-office operations.</t>
+          <t>| 
+|---|---|
+|  | Actionable insights Use AI-powered tools to uncover trends, identify opportunities and make faster, data-driven decisions.</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>d6f4fa7e61fa7c60a727651c3187a2da56c34c975f067ea27f434b8978efe06e</t>
+          <t>d2ec2e00fd8453d92033a40b146dd853dd3869f375c2f4e6315ff8a5cbf594f9</t>
         </is>
       </c>
     </row>
@@ -6489,37 +6506,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
+          <t>https://www.fiserv.com/en/who-we-serve/enterprise/reporting-and-analytics.html</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_D</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
+          <t>https://www.fiserv.com/en/who-we-serve/enterprise/reporting-and-analytics.html</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:35.805808+00:00</t>
+          <t>2026-10-10T16:18:23.207046+00:00</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Relationship intelligence at scale: agents that prepare a banker for the next c</t>
+          <t>| 
+|---|---|
+|  | Advanced analytics and drilldowns Leverage automation and AI-supported capabilities to reduce manual effort and improve consistency.</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>9e68a548aa5556c99d7bd1ef77c4c78f627fb87378bd505d306c91b782595ab2</t>
+          <t>f61a3c7f790aefdf9680057a8c3043f34700fe432818fe132243d0c291e0d2a2</t>
         </is>
       </c>
     </row>
@@ -6531,27 +6550,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-em/solutions/manage-risk-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-em/solutions/manage-risk-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/a-new-weapon-against-an-old-form-of-fraud.html</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-10T16:05:20.639179+00:00</t>
+          <t>2026-10-10T15:58:10.845485+00:00</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>predictive neural networks</t>
+          <t>generative AI will help fortify fraud detection to protect customers and members</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6561,7 +6580,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>037a7bac331d71f63311e156b60e25e3933f913cb6d76b482503d986f7164778</t>
+          <t>f7f97ad0267a2847645c39fae626d818e8efda60077a592aad2a24be4ffcc0d1</t>
         </is>
       </c>
     </row>
@@ -6573,27 +6592,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-em/solutions/manage-risk-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-em/solutions/manage-risk-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/rethinking-customer-loyalty-programs-how-merchants-can-differentiate-drive-roi-and-prepare-for-an-ai-driven-future.html</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-10T16:05:20.639179+00:00</t>
+          <t>2026-10-10T16:00:49.718239+00:00</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>use a mixture of artificial and automated intelligence, machine learning, and robotics to improve your operational efficiency, deliver rich analytics and strategic evaluation, reduce your costs, and fine-tune risk exposure</t>
+          <t>AI-Driven Future</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6603,7 +6622,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>037a7bac331d71f63311e156b60e25e3933f913cb6d76b482503d986f7164778</t>
+          <t>cb7849ecf803cb1eef0a646183a50e456a89ce44550c196d75a3c234d72a0507</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6634,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-how-financial-institutions-can-get-the-most-out-of-tech-upgrades.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6625,27 +6644,27 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/core-banking-modernization-how-financial-institutions-can-get-the-most-out-of-tech-upgrades.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:43.020266+00:00</t>
+          <t>2026-10-10T16:01:11.998445+00:00</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>high-tech buzz of AI-powered fraud prevention tools</t>
+          <t>AI-powered services</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>INDICATIVE</t>
+          <t>MARKETING-ONLY</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>193b8a323cc5fa25418e0f44b8f94bb071a83155dd1dd864d6396dcd90763b45</t>
+          <t>d6f4fa7e61fa7c60a727651c3187a2da56c34c975f067ea27f434b8978efe06e</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6676,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-financial-institutions-can-compete-digitally-and-win.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-is-here-what-merchants-need-to-know-and-do.html</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6667,27 +6686,27 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/how-financial-institutions-can-compete-digitally-and-win.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/agentic-commerce-is-here-what-merchants-need-to-know-and-do.html</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-10T15:59:49.238011+00:00</t>
+          <t>2026-10-10T15:58:17.132596+00:00</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Artificial intelligence is rapidly becoming integrated into every facet of consumers’ lives, and many are feeling very comfortable with it.</t>
+          <t>AI agents acting on behalf of consumers to discover, evaluate and sometimes purchase products automatically.</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>INDICATIVE</t>
+          <t>MARKETING-ONLY</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2b10adf13d9f7a73dc07da19a30f4bc2c629ad214c6cae15ca76b73905d1da90</t>
+          <t>2c831be14f46869e03dfb83376b0a58d1af96275c0cb4ec1b8f22e9f657234f2</t>
         </is>
       </c>
     </row>
@@ -6699,37 +6718,37 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/about-fiserv/corporate-social-responsibility.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/about-fiserv/corporate-social-responsibility.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/transforming-payment-operations-with-ai.html</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-10T16:10:32.850587+00:00</t>
+          <t>2026-10-10T16:01:21.614612+00:00</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>From advancing cybersecurity and ethical AI to upholding human rights and fighting financial crime, we operate with purpose - helping to make the connections we power safer and smarter.</t>
+          <t>Many modern AI solutions are designed to work on top of current environments, securely accessing data and executing tasks.</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>INDICATIVE</t>
+          <t>MARKETING-ONLY</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>9b4430e551d08a82fe17a2c378aa2723c53385af4c002e9a7633e54818fcbc6d</t>
+          <t>fed39b304fc4f3eb4cac204d260607b187be14cded1d646fb67f597ae45b493a</t>
         </is>
       </c>
     </row>
@@ -6741,37 +6760,37 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/about-fiserv/corporate-social-responsibility.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-programmable-payments.html</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/about-fiserv/corporate-social-responsibility.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-programmable-payments.html</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-10T16:10:32.850587+00:00</t>
+          <t>2026-10-10T16:01:27.917285+00:00</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>A cross-functional governance structure oversees implementation of responsible AI and machine learning capabilities, establishing standards for the appropriate use of new technologies.</t>
+          <t>Programmable payment technology can bring intelligence and clarity into the payment process.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>INDICATIVE</t>
+          <t>MARKETING-ONLY</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>9b4430e551d08a82fe17a2c378aa2723c53385af4c002e9a7633e54818fcbc6d</t>
+          <t>7d1cd46e3c594f945fd880fb57c9d0b00aa495dc2a933d40fbef28f51b9abb7f</t>
         </is>
       </c>
     </row>
@@ -6783,7 +6802,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6793,17 +6812,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/what-agentic-ai-means-for-financial-institutions.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:35.805808+00:00</t>
+          <t>2026-10-10T16:01:31.068758+00:00</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Many institutions have tested AI in pockets – like service chatbots and document processing – but haven’t yet run AI in a scalable way that owns outcomes</t>
+          <t>Unlocking GenAI’s Promise in Retail
+A new report offers clues to the retail potential of today’s hottest technology
+Generative artificial intelligence (GenAI) is poised to reshape the retail environment – from enhancing transaction security to delivering more personalized shopping experiences.</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6813,7 +6834,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>9e68a548aa5556c99d7bd1ef77c4c78f627fb87378bd505d306c91b782595ab2</t>
+          <t>56108dc2fba7dfbfd2b48a1eebd3de1eff62387bc8117916a166eca4d481cf93</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6846,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/businesses-and-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6835,17 +6856,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/businesses-and-merchants.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:56.449520+00:00</t>
+          <t>2026-10-10T16:01:31.068758+00:00</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>How AI-powered agents are already reshaping commerce, and how merchants can prepare to protect identity, loyalty and payments.</t>
+          <t>Forward-thinking enterprises that have adopted GenAI are already seeing measurable improvements in customer retention, forecasting precision and strategic decision-making.</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6855,7 +6876,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>70f21ebf8b872d3414d5a01ad50f36f6dbbb470e5ab9383d2d85d510cbffc2ac</t>
+          <t>56108dc2fba7dfbfd2b48a1eebd3de1eff62387bc8117916a166eca4d481cf93</t>
         </is>
       </c>
     </row>
@@ -6867,27 +6888,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-it/solutions/manage-risk-and-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-it/solutions/manage-risk-and-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-10T16:07:03.125696+00:00</t>
+          <t>2026-10-10T16:01:31.068758+00:00</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>use a mixture of artificial and automated intelligence, machine learning, and robotics</t>
+          <t>These are some of the questions explored in a new collaborative study from PYMNTS Intelligence and Fiserv – GenAI Applications in Retail Transaction Analysis: Industry Trends and Insights.</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6897,7 +6918,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>359cd9ceab797b44019327610ad2f81b8163d2d388dd8624f8b1e78c31d2d926</t>
+          <t>56108dc2fba7dfbfd2b48a1eebd3de1eff62387bc8117916a166eca4d481cf93</t>
         </is>
       </c>
     </row>
@@ -6909,27 +6930,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-la/financial-institutions/cash-and-logistics.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-la/financial-institutions/cash-and-logistics.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-10T16:07:19.711088+00:00</t>
+          <t>2026-10-10T16:01:29.483063+00:00</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Artificial intelligence to produce better cash forecasting and improve their operations.</t>
+          <t>Generative AI will broadly impact organizations and functions.</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6939,7 +6960,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>d22e51d8aee16267795ce5787080c6dc933fdd3bc6436e56e90cc74bf3b5118d</t>
+          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6992,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Integrated Currency Manager uses advanced artificial intelligence to assist your forecast of customer demand</t>
+          <t>Integrated Currency Manager uses advanced artificial intelligence to assist your forecast of customer demand so you can determine how much cash to order and ship for each cash point, including ATMs, branches and vaults.</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6993,27 +7014,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-pl/financial-institutions/manage-risk-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-pl/financial-institutions/manage-risk-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-10T16:09:14.693659+00:00</t>
+          <t>2026-10-10T15:58:13.971042+00:00</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>From the use of geo-location technology through to comprehensive risk analytics, strong customer authentication, use of global data and predictive neural networks, our solutions make it harder and more challenging for fraudsters.</t>
+          <t>The explosion of interest in AI, fueled by the recent introduction of ChatGPT from OpenAI, has executives across industries rethinking what generative AI means to their business and how and where to begin adoption.</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -7023,7 +7044,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>9478dbb9730718ea4f71685c2350e60c496c70df3e26dacfe9e8b52caaf6dc02</t>
+          <t>99179c0ac4fcebf059b90e9db72972077025d5446c7a7f1d12a8d091a62770d5</t>
         </is>
       </c>
     </row>
@@ -7035,27 +7056,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-pl/financial-institutions/manage-risk-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/navigating-the-future-industry-trends-in-treasury.html</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en-pl/financial-institutions/manage-risk-fraud.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/navigating-the-future-industry-trends-in-treasury.html</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-10T16:09:14.693659+00:00</t>
+          <t>2026-10-10T16:00:37.092458+00:00</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Our award-winning fraud and Anti-Money Laundering (AML) technologies use a mixture of artificial and automated intelligence, machine learning, and robotics to improve your operational efficiency, deliver rich analytics and strategic evaluation, reduce your costs, and fine-tune risk exposure.</t>
+          <t>There’s also European regulation relating to artificial intelligence.</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7065,7 +7086,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>9478dbb9730718ea4f71685c2350e60c496c70df3e26dacfe9e8b52caaf6dc02</t>
+          <t>bb4fa3a31d04d2db5818341f9546533a05bac0448b590bb7c11aab977edbad4d</t>
         </is>
       </c>
     </row>
@@ -7077,27 +7098,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-10T16:16:48.520050+00:00</t>
+          <t>2026-10-10T16:01:31.068758+00:00</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>intelligent network monitoring</t>
+          <t>Concerns about their own data analytics maturity often hold them back, creating uncertainty around whether they’re equipped to implement GenAI effectively.</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7107,7 +7128,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>db2b1269d91228c705dabdad0653e298cb023eb103f956b5da090f04a38a3bdc</t>
+          <t>56108dc2fba7dfbfd2b48a1eebd3de1eff62387bc8117916a166eca4d481cf93</t>
         </is>
       </c>
     </row>
@@ -7119,27 +7140,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_C</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
+          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-10T16:16:48.520050+00:00</t>
+          <t>2026-10-10T16:01:31.068758+00:00</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>biometric authentication</t>
+          <t>Can organizations harness GenAI’s full potential without first reinforcing their data foundations?</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -7149,7 +7170,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>db2b1269d91228c705dabdad0653e298cb023eb103f956b5da090f04a38a3bdc</t>
+          <t>56108dc2fba7dfbfd2b48a1eebd3de1eff62387bc8117916a166eca4d481cf93</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7182,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
+          <t>https://www.fiserv.com/en-la/financial-institutions/cash-and-logistics.html</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7171,17 +7192,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
+          <t>https://www.fiserv.com/en-la/financial-institutions/cash-and-logistics.html</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-10T16:16:48.520050+00:00</t>
+          <t>2026-10-10T16:07:19.711088+00:00</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>behavior analytics, machine learning</t>
+          <t>Artificial intelligence to produce better cash forecasting and improve their operations.</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -7191,103 +7212,105 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>db2b1269d91228c705dabdad0653e298cb023eb103f956b5da090f04a38a3bdc</t>
+          <t>d22e51d8aee16267795ce5787080c6dc933fdd3bc6436e56e90cc74bf3b5118d</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>V-002</t>
+          <t>V-005</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
+          <t>https://www.bny.com/corporate/global/en/solutions/platforms/conventional-trust-solutions/escrow-specialty-solutions.html</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/solutions/fraud-mitigation.html</t>
+          <t>https://www.bny.com/corporate/global/en/solutions/platforms/conventional-trust-solutions/escrow-specialty-solutions.html</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-10T16:16:48.520050+00:00</t>
+          <t>2026-10-10T16:27:00.696993+00:00</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>behavioral profiling</t>
+          <t>The Bank of New York Mellon SA/NV operates in the Netherlands through its Amsterdam branch at Tribes SOM2 Building, Claude Debussylaan 7, 1082 MC Amsterdam, the Netherlands, registered with the Dutch Chamber of Commerce under registration number 34363596.</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>db2b1269d91228c705dabdad0653e298cb023eb103f956b5da090f04a38a3bdc</t>
+          <t>bb7ecd775df9a351a2870c707ea2887b2d6abf2f0d09727fa0a083eb0918e945</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>V-002</t>
+          <t>V-005</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/who-we-serve/enterprise/commerce-control-center.html</t>
+          <t>https://www.bny.com/ai-policy</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/who-we-serve/enterprise/commerce-control-center.html</t>
+          <t>https://www.bny.com/ai-policy</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-10T16:18:11.077288+00:00</t>
+          <t>2026-10-10T16:24:47.859682+00:00</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Use AI-powered tools to uncover trends, identify opportunities and make faster, data-driven decisions.</t>
+          <t>- Definitions
+ For the purposes of this Policy:
+  - “Artificial Intelligence” means any technology that enables machines to perform tasks that typically require human intelligence, including but not limited to generative AI, machine learning, natural language processing, and computer vision.</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>d2ec2e00fd8453d92033a40b146dd853dd3869f375c2f4e6315ff8a5cbf594f9</t>
+          <t>b31b1f0ef72c6f75f441627dd1e3e12b5305831bc8980275fa4a514304f1d512</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>V-002</t>
+          <t>V-005</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
+          <t>https://www.bny.com/corporate/br/en/privacy-policy.html</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7297,227 +7320,228 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/legal/cybersecurity.html</t>
+          <t>https://www.bny.com/corporate/br/en/privacy-policy.html</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-10T15:55:37.573244+00:00</t>
+          <t>2026-10-10T16:25:18.855469+00:00</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Security and Resilience in the Age of AI</t>
+          <t>In particular, we may use automated methods of treatment, such as Artificial Intelligence ("AI") and Machine Learning ("ML"), which are a set of technologies programmed to perform tasks and actions that are commonly associated with humans.</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>c8ae42b7ee474576c84822b5f8d2a9e306f7e26ed7e7a10c1198ff5990595d35</t>
+          <t>8daf652f9ff98f5490b2c994ecee94efe6b1c4b73f05deb50b496ae4dfe056a7</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>V-002</t>
+          <t>V-005</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/understanding-the-ai-industrial-revolution.html</t>
+          <t>https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:29.483063+00:00</t>
+          <t>2026-10-10T16:27:15.940356+00:00</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Generative AI will broadly impact organizations and functions.</t>
+          <t>Leverage secure, advanced technologies, from digital onboarding and automated data feeds to AI-powered document processing and support for digital issuance.</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>441bda419c4fd48eb0c60e12960379908a85bd7201df2212790a79949e1617c4</t>
+          <t>044f58b49bc463e09bec6e6a7fed94efb02d2a3e79b2dad04fac76f71fb57f21</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>V-002</t>
+          <t>V-005</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/partner-support.html</t>
+          <t>https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tier_D</t>
+          <t>Tier_A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/who-we-serve/integrated-payments-isv/partner-support.html</t>
+          <t>https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-10T16:18:43.822639+00:00</t>
+          <t>2026-10-10T16:27:15.940356+00:00</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CoPilot partner portfolio management system</t>
+          <t>Leverage streamlined onboarding, AI-driven workflow optimization, real-time dashboards and APIs for operational excellence and transparency.</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>8dd58af9ccba196f3230d88f181ec520cb4b0fb65eb082fdd0c96b03eca41f48</t>
+          <t>044f58b49bc463e09bec6e6a7fed94efb02d2a3e79b2dad04fac76f71fb57f21</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>V-002</t>
+          <t>V-005</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
+          <t>https://www.bny.com/corporate/global/en/about-us/newsroom/press-release/bny-and-cummins-college-of-engineering-for-women-launch-shakti-alliance-to-advance-women-in-technology.html</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/accelerating-the-pace-of-innovation.html</t>
+          <t>https://www.bny.com/corporate/global/en/about-us/newsroom/press-release/bny-and-cummins-college-of-engineering-for-women-launch-shakti-alliance-to-advance-women-in-technology.html</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-10T15:58:13.971042+00:00</t>
+          <t>2026-10-13T16:59:25.995005+00:00</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>The explosion of interest in AI, fueled by the recent introduction of ChatGPT from OpenAI, has executives across industries rethinking what generative AI means to their business and how and where to begin adoption.</t>
+          <t>Shakti Alliance will focus on experiential learning, applied research, curriculum enrichment and faculty development to equip students and faculty with the skills, knowledge and industry exposure needed to thrive in an increasingly AI-driven world.</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>99179c0ac4fcebf059b90e9db72972077025d5446c7a7f1d12a8d091a62770d5</t>
+          <t>65c36382c3e2efef0e580feaa5cc05d629aef6e932cfe98f6f5ea0d1b166de6c</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>V-002</t>
+          <t>V-005</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+          <t>https://www.bny.com/corporate/global/en/about-us/newsroom/press-release/bny-and-cummins-college-of-engineering-for-women-launch-shakti-alliance-to-advance-women-in-technology.html</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/the-no-regret-investment-large-banks-and-core-modernization.html</t>
+          <t>https://www.bny.com/corporate/global/en/about-us/newsroom/press-release/bny-and-cummins-college-of-engineering-for-women-launch-shakti-alliance-to-advance-women-in-technology.html</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:11.998445+00:00</t>
+          <t>2026-10-13T16:59:25.995005+00:00</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>AI is only as good as the data it can access.</t>
+          <t>Together, we are creating pathways for the next generation of women engineers to develop hands-on expertise and lead in an AI-powered world.”
+“This collaboration marks an important milestone in the longstanding relationship between CCOEW and BNY,” said Dr.</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>MARKETING-ONLY</t>
+          <t>INDICATIVE</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>d6f4fa7e61fa7c60a727651c3187a2da56c34c975f067ea27f434b8978efe06e</t>
+          <t>65c36382c3e2efef0e580feaa5cc05d629aef6e932cfe98f6f5ea0d1b166de6c</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>V-002</t>
+          <t>V-005</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+          <t>https://www.bny.com/ai-policy</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tier_C</t>
+          <t>Tier_A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://www.fiserv.com/en/insights/articles-and-blogs/unlocking-genais-promise-in-retail.html</t>
+          <t>https://www.bny.com/ai-policy</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-10T16:01:31.068758+00:00</t>
+          <t>2026-10-10T16:24:47.859682+00:00</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Generative artificial intelligence (GenAI) is poised to reshape the retail environment – from enhancing transaction security to delivering more personalized shopping experiences.</t>
+          <t>This Acceptable Use Policy (“Policy”) applies to Your use of all services offered by BNY or third-party products, applications, or functionality that interoperate with services offered by BNY, that incorporate Artificial Intelligence, including proprietary and third-party solutions (each, an “AI Service”).</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -7527,133 +7551,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>56108dc2fba7dfbfd2b48a1eebd3de1eff62387bc8117916a166eca4d481cf93</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>V-005</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>https://www.bny.com/ai-policy</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Tier_A</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>https://www.bny.com/ai-policy</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>2026-10-10T16:24:47.859682+00:00</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Use any robot, spider, intelligent agent, other automatic device or manual process, or automated systems to search, monitor or copy our web pages, data, content or other materials contained herein, or for any other unauthorized purpose.</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>INDICATIVE</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
           <t>b31b1f0ef72c6f75f441627dd1e3e12b5305831bc8980275fa4a514304f1d512</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>V-005</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Tier_A</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>2026-10-10T16:27:15.940356+00:00</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>AI-powered document processing</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>MARKETING-ONLY</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>044f58b49bc463e09bec6e6a7fed94efb02d2a3e79b2dad04fac76f71fb57f21</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>V-005</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Tier_A</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>https://www.bny.com/corporate/global/en/solutions/platforms/corporate-trust-solutions.html</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>2026-10-10T16:27:15.940356+00:00</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>AI-driven workflow optimization</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>MARKETING-ONLY</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>044f58b49bc463e09bec6e6a7fed94efb02d2a3e79b2dad04fac76f71fb57f21</t>
         </is>
       </c>
     </row>
